--- a/GearSage-client/pkgGear/data_raw/megabass_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/megabass_rod_import.xlsx
@@ -461,7 +461,7 @@
         <v>ROD</v>
       </c>
       <c r="I2" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2021/01/main_001_arms_super_leggera_asl-7117x.jpg</v>
+        <v>images/megabass_rods/ASL7117X_main.jpg</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -496,7 +496,7 @@
         <v>ROD</v>
       </c>
       <c r="I3" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2021/01/main_001_destroyer_t.s_ts79x.jpg</v>
+        <v>images/megabass_rods/TS79X_main.jpg</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -531,7 +531,7 @@
         <v>ROD</v>
       </c>
       <c r="I4" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2021/01/main_001_TRIZA_F7-72XTZ.jpg</v>
+        <v>images/megabass_rods/F7-72XTZ_main.jpg</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -566,7 +566,7 @@
         <v>ROD</v>
       </c>
       <c r="I5" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2016/07/main_001_pagani_trad_f1-60xpblank.jpg</v>
+        <v>images/megabass_rods/F1-60XP_main.jpg</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -601,7 +601,7 @@
         <v>ROD</v>
       </c>
       <c r="I6" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2021/01/main_001_arms_super_leggera_spinning_asl-6401xs.jpg</v>
+        <v>images/megabass_rods/ASL6401XS_main.jpg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -636,7 +636,7 @@
         <v>ROD</v>
       </c>
       <c r="I7" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2023/01/main_001_F0halfST-62XTS.jpg</v>
+        <v>images/megabass_rods/F0.1_2st-62XTS_main.jpg</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -671,7 +671,7 @@
         <v>ROD</v>
       </c>
       <c r="I8" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2025/02/EVOLZION-MX40_F5-68ti_main_001.jpg</v>
+        <v>images/megabass_rods/F5.1_2-68ti_main.jpg</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -706,7 +706,7 @@
         <v>ROD</v>
       </c>
       <c r="I9" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2018/04/main_001_great_hunting_gh93-2ms.jpg</v>
+        <v>images/megabass_rods/GH93-2MS_main.jpg</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -741,7 +741,7 @@
         <v>ROD</v>
       </c>
       <c r="I10" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2022/01/main_001_gh-huntsman_ghbf5511-4l.jpg</v>
+        <v>images/megabass_rods/GHBF511-4L_main.jpg</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -776,7 +776,7 @@
         <v>ROD</v>
       </c>
       <c r="I11" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2021/01/main_001_destroyer_p5_f4.1-2-71x.jpg</v>
+        <v>images/megabass_rods/F4.1_2-71X_main.jpg</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,7 +811,7 @@
         <v>ROD</v>
       </c>
       <c r="I12" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2026/01/main_001_f9-711lv-2.jpg</v>
+        <v>images/megabass_rods/F9-711LV_main.jpg</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -846,7 +846,7 @@
         <v>ROD</v>
       </c>
       <c r="I13" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2021/01/main_001_valkyrie_world_expedition_VKC-711XH-4.jpg</v>
+        <v>images/megabass_rods/VKC-711XH-4_main.jpg</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -881,7 +881,7 @@
         <v>ROD</v>
       </c>
       <c r="I14" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2025/12/main_001_great_hunting_ght610-m.jpg</v>
+        <v>images/megabass_rods/GHT610-M_main.jpg</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -916,7 +916,7 @@
         <v>ROD</v>
       </c>
       <c r="I15" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2025/12/main_001_great_hunting_ghbf42-4ul.jpg</v>
+        <v>images/megabass_rods/GHBF42-4UL_main.jpg</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -951,7 +951,7 @@
         <v>ROD</v>
       </c>
       <c r="I16" t="str">
-        <v>https://www.megabass.co.jp/site/wp-content/uploads/2025/12/main_001_great_hunting_glass_composite_gh62-4mlcg.jpg</v>
+        <v>images/megabass_rods/GH62-4ML-XG_main.jpg</v>
       </c>
       <c r="J16" t="str">
         <v/>

--- a/GearSage-client/pkgGear/data_raw/megabass_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/megabass_rod_import.xlsx
@@ -436,8 +436,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>MR1000</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -471,8 +471,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>MR1001</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -506,8 +506,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>MR1002</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -541,8 +541,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>MR1003</v>
       </c>
       <c r="B5" t="str">
         <v/>
@@ -576,8 +576,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>MR1004</v>
       </c>
       <c r="B6" t="str">
         <v/>
@@ -611,8 +611,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>MR1005</v>
       </c>
       <c r="B7" t="str">
         <v/>
@@ -646,8 +646,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>MR1006</v>
       </c>
       <c r="B8" t="str">
         <v/>
@@ -681,8 +681,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>MR1007</v>
       </c>
       <c r="B9" t="str">
         <v/>
@@ -716,8 +716,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>MR1008</v>
       </c>
       <c r="B10" t="str">
         <v/>
@@ -751,8 +751,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>MR1009</v>
       </c>
       <c r="B11" t="str">
         <v/>
@@ -786,8 +786,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>MR1010</v>
       </c>
       <c r="B12" t="str">
         <v/>
@@ -821,8 +821,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>MR1011</v>
       </c>
       <c r="B13" t="str">
         <v/>
@@ -856,8 +856,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>MR1012</v>
       </c>
       <c r="B14" t="str">
         <v/>
@@ -891,8 +891,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>MR1013</v>
       </c>
       <c r="B15" t="str">
         <v/>
@@ -926,8 +926,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>MR1014</v>
       </c>
       <c r="B16" t="str">
         <v/>
@@ -1079,11 +1079,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>MRD10000</v>
+      </c>
+      <c r="B2" t="str">
+        <v>MR1000</v>
       </c>
       <c r="C2" t="str">
         <v>C</v>
@@ -1183,11 +1183,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
+      <c r="A3" t="str">
+        <v>MRD10001</v>
+      </c>
+      <c r="B3" t="str">
+        <v>MR1000</v>
       </c>
       <c r="C3" t="str">
         <v>C</v>
@@ -1284,11 +1284,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="A4" t="str">
+        <v>MRD10002</v>
+      </c>
+      <c r="B4" t="str">
+        <v>MR1000</v>
       </c>
       <c r="C4" t="str">
         <v>C</v>
@@ -1385,11 +1385,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="A5" t="str">
+        <v>MRD10003</v>
+      </c>
+      <c r="B5" t="str">
+        <v>MR1000</v>
       </c>
       <c r="C5" t="str">
         <v>C</v>
@@ -1486,11 +1486,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
+      <c r="A6" t="str">
+        <v>MRD10004</v>
+      </c>
+      <c r="B6" t="str">
+        <v>MR1000</v>
       </c>
       <c r="C6" t="str">
         <v>C</v>
@@ -1587,11 +1587,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
+      <c r="A7" t="str">
+        <v>MRD10005</v>
+      </c>
+      <c r="B7" t="str">
+        <v>MR1000</v>
       </c>
       <c r="C7" t="str">
         <v>C</v>
@@ -1688,11 +1688,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
+      <c r="A8" t="str">
+        <v>MRD10006</v>
+      </c>
+      <c r="B8" t="str">
+        <v>MR1000</v>
       </c>
       <c r="C8" t="str">
         <v>C</v>
@@ -1789,11 +1789,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
+      <c r="A9" t="str">
+        <v>MRD10007</v>
+      </c>
+      <c r="B9" t="str">
+        <v>MR1000</v>
       </c>
       <c r="C9" t="str">
         <v>C</v>
@@ -1890,11 +1890,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
+      <c r="A10" t="str">
+        <v>MRD10008</v>
+      </c>
+      <c r="B10" t="str">
+        <v>MR1001</v>
       </c>
       <c r="C10" t="str">
         <v>C</v>
@@ -1994,11 +1994,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
+      <c r="A11" t="str">
+        <v>MRD10009</v>
+      </c>
+      <c r="B11" t="str">
+        <v>MR1001</v>
       </c>
       <c r="C11" t="str">
         <v>C</v>
@@ -2098,11 +2098,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
+      <c r="A12" t="str">
+        <v>MRD10010</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MR1001</v>
       </c>
       <c r="C12" t="str">
         <v>C</v>
@@ -2202,11 +2202,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
+      <c r="A13" t="str">
+        <v>MRD10011</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MR1001</v>
       </c>
       <c r="C13" t="str">
         <v>S</v>
@@ -2303,11 +2303,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
+      <c r="A14" t="str">
+        <v>MRD10012</v>
+      </c>
+      <c r="B14" t="str">
+        <v>MR1001</v>
       </c>
       <c r="C14" t="str">
         <v>C</v>
@@ -2407,11 +2407,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
+      <c r="A15" t="str">
+        <v>MRD10013</v>
+      </c>
+      <c r="B15" t="str">
+        <v>MR1001</v>
       </c>
       <c r="C15" t="str">
         <v>C</v>
@@ -2508,11 +2508,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
+      <c r="A16" t="str">
+        <v>MRD10014</v>
+      </c>
+      <c r="B16" t="str">
+        <v>MR1001</v>
       </c>
       <c r="C16" t="str">
         <v>C</v>
@@ -2609,11 +2609,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>2</v>
+      <c r="A17" t="str">
+        <v>MRD10015</v>
+      </c>
+      <c r="B17" t="str">
+        <v>MR1001</v>
       </c>
       <c r="C17" t="str">
         <v>C</v>
@@ -2713,11 +2713,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>3</v>
+      <c r="A18" t="str">
+        <v>MRD10016</v>
+      </c>
+      <c r="B18" t="str">
+        <v>MR1002</v>
       </c>
       <c r="C18" t="str">
         <v>C</v>
@@ -2817,11 +2817,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>3</v>
+      <c r="A19" t="str">
+        <v>MRD10017</v>
+      </c>
+      <c r="B19" t="str">
+        <v>MR1002</v>
       </c>
       <c r="C19" t="str">
         <v>S</v>
@@ -2921,11 +2921,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>3</v>
+      <c r="A20" t="str">
+        <v>MRD10018</v>
+      </c>
+      <c r="B20" t="str">
+        <v>MR1002</v>
       </c>
       <c r="C20" t="str">
         <v>S</v>
@@ -3025,11 +3025,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>3</v>
+      <c r="A21" t="str">
+        <v>MRD10019</v>
+      </c>
+      <c r="B21" t="str">
+        <v>MR1002</v>
       </c>
       <c r="C21" t="str">
         <v>C</v>
@@ -3129,11 +3129,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22">
-        <v>3</v>
+      <c r="A22" t="str">
+        <v>MRD10020</v>
+      </c>
+      <c r="B22" t="str">
+        <v>MR1002</v>
       </c>
       <c r="C22" t="str">
         <v>S</v>
@@ -3230,11 +3230,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23">
-        <v>3</v>
+      <c r="A23" t="str">
+        <v>MRD10021</v>
+      </c>
+      <c r="B23" t="str">
+        <v>MR1002</v>
       </c>
       <c r="C23" t="str">
         <v>C</v>
@@ -3331,11 +3331,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24">
-        <v>3</v>
+      <c r="A24" t="str">
+        <v>MRD10022</v>
+      </c>
+      <c r="B24" t="str">
+        <v>MR1002</v>
       </c>
       <c r="C24" t="str">
         <v>S</v>
@@ -3432,11 +3432,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25">
-        <v>3</v>
+      <c r="A25" t="str">
+        <v>MRD10023</v>
+      </c>
+      <c r="B25" t="str">
+        <v>MR1002</v>
       </c>
       <c r="C25" t="str">
         <v>C</v>
@@ -3533,11 +3533,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26">
-        <v>3</v>
+      <c r="A26" t="str">
+        <v>MRD10024</v>
+      </c>
+      <c r="B26" t="str">
+        <v>MR1002</v>
       </c>
       <c r="C26" t="str">
         <v>C</v>
@@ -3634,11 +3634,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27">
-        <v>3</v>
+      <c r="A27" t="str">
+        <v>MRD10025</v>
+      </c>
+      <c r="B27" t="str">
+        <v>MR1002</v>
       </c>
       <c r="C27" t="str">
         <v>C</v>
@@ -3735,11 +3735,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28">
-        <v>4</v>
+      <c r="A28" t="str">
+        <v>MRD10026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>MR1003</v>
       </c>
       <c r="C28" t="str">
         <v>C</v>
@@ -3836,11 +3836,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29">
-        <v>4</v>
+      <c r="A29" t="str">
+        <v>MRD10027</v>
+      </c>
+      <c r="B29" t="str">
+        <v>MR1003</v>
       </c>
       <c r="C29" t="str">
         <v>C</v>
@@ -3937,11 +3937,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30">
-        <v>4</v>
+      <c r="A30" t="str">
+        <v>MRD10028</v>
+      </c>
+      <c r="B30" t="str">
+        <v>MR1003</v>
       </c>
       <c r="C30" t="str">
         <v>C</v>
@@ -4038,11 +4038,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31">
-        <v>5</v>
+      <c r="A31" t="str">
+        <v>MRD10029</v>
+      </c>
+      <c r="B31" t="str">
+        <v>MR1004</v>
       </c>
       <c r="C31" t="str">
         <v>S</v>
@@ -4142,11 +4142,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32">
-        <v>5</v>
+      <c r="A32" t="str">
+        <v>MRD10030</v>
+      </c>
+      <c r="B32" t="str">
+        <v>MR1004</v>
       </c>
       <c r="C32" t="str">
         <v>S</v>
@@ -4246,11 +4246,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33">
-        <v>5</v>
+      <c r="A33" t="str">
+        <v>MRD10031</v>
+      </c>
+      <c r="B33" t="str">
+        <v>MR1004</v>
       </c>
       <c r="C33" t="str">
         <v>S</v>
@@ -4350,11 +4350,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34">
-        <v>6</v>
+      <c r="A34" t="str">
+        <v>MRD10032</v>
+      </c>
+      <c r="B34" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C34" t="str">
         <v>S</v>
@@ -4451,11 +4451,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35">
-        <v>6</v>
+      <c r="A35" t="str">
+        <v>MRD10033</v>
+      </c>
+      <c r="B35" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C35" t="str">
         <v>S</v>
@@ -4552,11 +4552,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36">
-        <v>6</v>
+      <c r="A36" t="str">
+        <v>MRD10034</v>
+      </c>
+      <c r="B36" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C36" t="str">
         <v>C</v>
@@ -4656,11 +4656,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37">
-        <v>6</v>
+      <c r="A37" t="str">
+        <v>MRD10035</v>
+      </c>
+      <c r="B37" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C37" t="str">
         <v>C</v>
@@ -4757,11 +4757,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38">
-        <v>6</v>
+      <c r="A38" t="str">
+        <v>MRD10036</v>
+      </c>
+      <c r="B38" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C38" t="str">
         <v>C</v>
@@ -4858,11 +4858,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39">
-        <v>6</v>
+      <c r="A39" t="str">
+        <v>MRD10037</v>
+      </c>
+      <c r="B39" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C39" t="str">
         <v>C</v>
@@ -4959,11 +4959,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40">
-        <v>6</v>
+      <c r="A40" t="str">
+        <v>MRD10038</v>
+      </c>
+      <c r="B40" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C40" t="str">
         <v>S</v>
@@ -5060,11 +5060,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41">
-        <v>6</v>
+      <c r="A41" t="str">
+        <v>MRD10039</v>
+      </c>
+      <c r="B41" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C41" t="str">
         <v>C</v>
@@ -5161,11 +5161,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42">
-        <v>6</v>
+      <c r="A42" t="str">
+        <v>MRD10040</v>
+      </c>
+      <c r="B42" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C42" t="str">
         <v>C</v>
@@ -5262,11 +5262,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43">
-        <v>6</v>
+      <c r="A43" t="str">
+        <v>MRD10041</v>
+      </c>
+      <c r="B43" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C43" t="str">
         <v>C</v>
@@ -5363,11 +5363,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44">
-        <v>6</v>
+      <c r="A44" t="str">
+        <v>MRD10042</v>
+      </c>
+      <c r="B44" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C44" t="str">
         <v>C</v>
@@ -5464,11 +5464,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45">
-        <v>6</v>
+      <c r="A45" t="str">
+        <v>MRD10043</v>
+      </c>
+      <c r="B45" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C45" t="str">
         <v>S</v>
@@ -5565,11 +5565,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46">
-        <v>6</v>
+      <c r="A46" t="str">
+        <v>MRD10044</v>
+      </c>
+      <c r="B46" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C46" t="str">
         <v>S</v>
@@ -5666,11 +5666,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47">
-        <v>6</v>
+      <c r="A47" t="str">
+        <v>MRD10045</v>
+      </c>
+      <c r="B47" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C47" t="str">
         <v>C</v>
@@ -5767,11 +5767,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48">
-        <v>6</v>
+      <c r="A48" t="str">
+        <v>MRD10046</v>
+      </c>
+      <c r="B48" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C48" t="str">
         <v>C</v>
@@ -5868,11 +5868,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49">
-        <v>6</v>
+      <c r="A49" t="str">
+        <v>MRD10047</v>
+      </c>
+      <c r="B49" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C49" t="str">
         <v>S</v>
@@ -5969,11 +5969,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50">
-        <v>6</v>
+      <c r="A50" t="str">
+        <v>MRD10048</v>
+      </c>
+      <c r="B50" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C50" t="str">
         <v>S</v>
@@ -6070,11 +6070,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51">
-        <v>6</v>
+      <c r="A51" t="str">
+        <v>MRD10049</v>
+      </c>
+      <c r="B51" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C51" t="str">
         <v>C</v>
@@ -6171,11 +6171,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52">
-        <v>6</v>
+      <c r="A52" t="str">
+        <v>MRD10050</v>
+      </c>
+      <c r="B52" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C52" t="str">
         <v>S</v>
@@ -6272,11 +6272,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53">
-        <v>6</v>
+      <c r="A53" t="str">
+        <v>MRD10051</v>
+      </c>
+      <c r="B53" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C53" t="str">
         <v>C</v>
@@ -6373,11 +6373,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54">
-        <v>6</v>
+      <c r="A54" t="str">
+        <v>MRD10052</v>
+      </c>
+      <c r="B54" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C54" t="str">
         <v>C</v>
@@ -6474,11 +6474,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55">
-        <v>6</v>
+      <c r="A55" t="str">
+        <v>MRD10053</v>
+      </c>
+      <c r="B55" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C55" t="str">
         <v>C</v>
@@ -6575,11 +6575,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56">
-        <v>6</v>
+      <c r="A56" t="str">
+        <v>MRD10054</v>
+      </c>
+      <c r="B56" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C56" t="str">
         <v>C</v>
@@ -6676,11 +6676,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57">
-        <v>6</v>
+      <c r="A57" t="str">
+        <v>MRD10055</v>
+      </c>
+      <c r="B57" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C57" t="str">
         <v>C</v>
@@ -6777,11 +6777,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58">
-        <v>6</v>
+      <c r="A58" t="str">
+        <v>MRD10056</v>
+      </c>
+      <c r="B58" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C58" t="str">
         <v>C</v>
@@ -6878,11 +6878,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59">
-        <v>6</v>
+      <c r="A59" t="str">
+        <v>MRD10057</v>
+      </c>
+      <c r="B59" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C59" t="str">
         <v>C</v>
@@ -6979,11 +6979,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60">
-        <v>6</v>
+      <c r="A60" t="str">
+        <v>MRD10058</v>
+      </c>
+      <c r="B60" t="str">
+        <v>MR1005</v>
       </c>
       <c r="C60" t="str">
         <v>S</v>
@@ -7080,11 +7080,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61">
-        <v>7</v>
+      <c r="A61" t="str">
+        <v>MRD10059</v>
+      </c>
+      <c r="B61" t="str">
+        <v>MR1006</v>
       </c>
       <c r="C61" t="str">
         <v>C</v>
@@ -7181,11 +7181,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62">
-        <v>7</v>
+      <c r="A62" t="str">
+        <v>MRD10060</v>
+      </c>
+      <c r="B62" t="str">
+        <v>MR1006</v>
       </c>
       <c r="C62" t="str">
         <v>S</v>
@@ -7282,11 +7282,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63">
-        <v>7</v>
+      <c r="A63" t="str">
+        <v>MRD10061</v>
+      </c>
+      <c r="B63" t="str">
+        <v>MR1006</v>
       </c>
       <c r="C63" t="str">
         <v>S</v>
@@ -7383,11 +7383,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64">
-        <v>7</v>
+      <c r="A64" t="str">
+        <v>MRD10062</v>
+      </c>
+      <c r="B64" t="str">
+        <v>MR1006</v>
       </c>
       <c r="C64" t="str">
         <v>C</v>
@@ -7484,11 +7484,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65">
-        <v>7</v>
+      <c r="A65" t="str">
+        <v>MRD10063</v>
+      </c>
+      <c r="B65" t="str">
+        <v>MR1006</v>
       </c>
       <c r="C65" t="str">
         <v>C</v>
@@ -7585,11 +7585,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66">
-        <v>7</v>
+      <c r="A66" t="str">
+        <v>MRD10064</v>
+      </c>
+      <c r="B66" t="str">
+        <v>MR1006</v>
       </c>
       <c r="C66" t="str">
         <v>C</v>
@@ -7686,11 +7686,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67">
-        <v>7</v>
+      <c r="A67" t="str">
+        <v>MRD10065</v>
+      </c>
+      <c r="B67" t="str">
+        <v>MR1006</v>
       </c>
       <c r="C67" t="str">
         <v>S</v>
@@ -7787,11 +7787,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68">
-        <v>7</v>
+      <c r="A68" t="str">
+        <v>MRD10066</v>
+      </c>
+      <c r="B68" t="str">
+        <v>MR1006</v>
       </c>
       <c r="C68" t="str">
         <v>S</v>
@@ -7888,11 +7888,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69">
-        <v>7</v>
+      <c r="A69" t="str">
+        <v>MRD10067</v>
+      </c>
+      <c r="B69" t="str">
+        <v>MR1006</v>
       </c>
       <c r="C69" t="str">
         <v>C</v>
@@ -7989,11 +7989,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70">
-        <v>7</v>
+      <c r="A70" t="str">
+        <v>MRD10068</v>
+      </c>
+      <c r="B70" t="str">
+        <v>MR1006</v>
       </c>
       <c r="C70" t="str">
         <v>S</v>
@@ -8090,11 +8090,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71">
-        <v>7</v>
+      <c r="A71" t="str">
+        <v>MRD10069</v>
+      </c>
+      <c r="B71" t="str">
+        <v>MR1006</v>
       </c>
       <c r="C71" t="str">
         <v>C</v>
@@ -8191,11 +8191,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72">
-        <v>7</v>
+      <c r="A72" t="str">
+        <v>MRD10070</v>
+      </c>
+      <c r="B72" t="str">
+        <v>MR1006</v>
       </c>
       <c r="C72" t="str">
         <v>C</v>
@@ -8292,11 +8292,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73">
-        <v>7</v>
+      <c r="A73" t="str">
+        <v>MRD10071</v>
+      </c>
+      <c r="B73" t="str">
+        <v>MR1006</v>
       </c>
       <c r="C73" t="str">
         <v>C</v>
@@ -8393,11 +8393,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74">
-        <v>7</v>
+      <c r="A74" t="str">
+        <v>MRD10072</v>
+      </c>
+      <c r="B74" t="str">
+        <v>MR1006</v>
       </c>
       <c r="C74" t="str">
         <v>C</v>
@@ -8494,11 +8494,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75">
-        <v>7</v>
+      <c r="A75" t="str">
+        <v>MRD10073</v>
+      </c>
+      <c r="B75" t="str">
+        <v>MR1006</v>
       </c>
       <c r="C75" t="str">
         <v>S</v>
@@ -8595,11 +8595,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76">
-        <v>8</v>
+      <c r="A76" t="str">
+        <v>MRD10074</v>
+      </c>
+      <c r="B76" t="str">
+        <v>MR1007</v>
       </c>
       <c r="C76" t="str">
         <v>S</v>
@@ -8696,11 +8696,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77">
-        <v>8</v>
+      <c r="A77" t="str">
+        <v>MRD10075</v>
+      </c>
+      <c r="B77" t="str">
+        <v>MR1007</v>
       </c>
       <c r="C77" t="str">
         <v>S</v>
@@ -8797,11 +8797,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78">
-        <v>8</v>
+      <c r="A78" t="str">
+        <v>MRD10076</v>
+      </c>
+      <c r="B78" t="str">
+        <v>MR1007</v>
       </c>
       <c r="C78" t="str">
         <v>S</v>
@@ -8898,11 +8898,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79">
-        <v>9</v>
+      <c r="A79" t="str">
+        <v>MRD10077</v>
+      </c>
+      <c r="B79" t="str">
+        <v>MR1008</v>
       </c>
       <c r="C79" t="str">
         <v>C</v>
@@ -9002,11 +9002,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80">
-        <v>9</v>
+      <c r="A80" t="str">
+        <v>MRD10078</v>
+      </c>
+      <c r="B80" t="str">
+        <v>MR1008</v>
       </c>
       <c r="C80" t="str">
         <v>C</v>
@@ -9106,11 +9106,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81">
-        <v>9</v>
+      <c r="A81" t="str">
+        <v>MRD10079</v>
+      </c>
+      <c r="B81" t="str">
+        <v>MR1008</v>
       </c>
       <c r="C81" t="str">
         <v>C</v>
@@ -9210,11 +9210,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82">
-        <v>9</v>
+      <c r="A82" t="str">
+        <v>MRD10080</v>
+      </c>
+      <c r="B82" t="str">
+        <v>MR1008</v>
       </c>
       <c r="C82" t="str">
         <v>C</v>
@@ -9314,11 +9314,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83">
-        <v>10</v>
+      <c r="A83" t="str">
+        <v>MRD10081</v>
+      </c>
+      <c r="B83" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C83" t="str">
         <v>C</v>
@@ -9415,11 +9415,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84">
-        <v>10</v>
+      <c r="A84" t="str">
+        <v>MRD10082</v>
+      </c>
+      <c r="B84" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C84" t="str">
         <v>S</v>
@@ -9516,11 +9516,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85">
-        <v>10</v>
+      <c r="A85" t="str">
+        <v>MRD10083</v>
+      </c>
+      <c r="B85" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C85" t="str">
         <v>C</v>
@@ -9617,11 +9617,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86">
-        <v>10</v>
+      <c r="A86" t="str">
+        <v>MRD10084</v>
+      </c>
+      <c r="B86" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C86" t="str">
         <v>S</v>
@@ -9718,11 +9718,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87">
-        <v>86</v>
-      </c>
-      <c r="B87">
-        <v>10</v>
+      <c r="A87" t="str">
+        <v>MRD10085</v>
+      </c>
+      <c r="B87" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C87" t="str">
         <v>C</v>
@@ -9819,11 +9819,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88">
-        <v>10</v>
+      <c r="A88" t="str">
+        <v>MRD10086</v>
+      </c>
+      <c r="B88" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C88" t="str">
         <v>C</v>
@@ -9920,11 +9920,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89">
-        <v>88</v>
-      </c>
-      <c r="B89">
-        <v>10</v>
+      <c r="A89" t="str">
+        <v>MRD10087</v>
+      </c>
+      <c r="B89" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C89" t="str">
         <v>S</v>
@@ -10024,11 +10024,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90">
-        <v>89</v>
-      </c>
-      <c r="B90">
-        <v>10</v>
+      <c r="A90" t="str">
+        <v>MRD10088</v>
+      </c>
+      <c r="B90" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C90" t="str">
         <v>C</v>
@@ -10125,11 +10125,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91">
-        <v>10</v>
+      <c r="A91" t="str">
+        <v>MRD10089</v>
+      </c>
+      <c r="B91" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C91" t="str">
         <v>C</v>
@@ -10226,11 +10226,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92">
-        <v>91</v>
-      </c>
-      <c r="B92">
-        <v>10</v>
+      <c r="A92" t="str">
+        <v>MRD10090</v>
+      </c>
+      <c r="B92" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C92" t="str">
         <v>C</v>
@@ -10327,11 +10327,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93">
-        <v>92</v>
-      </c>
-      <c r="B93">
-        <v>10</v>
+      <c r="A93" t="str">
+        <v>MRD10091</v>
+      </c>
+      <c r="B93" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C93" t="str">
         <v>C</v>
@@ -10428,11 +10428,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94">
-        <v>93</v>
-      </c>
-      <c r="B94">
-        <v>10</v>
+      <c r="A94" t="str">
+        <v>MRD10092</v>
+      </c>
+      <c r="B94" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C94" t="str">
         <v>C</v>
@@ -10529,11 +10529,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95">
-        <v>94</v>
-      </c>
-      <c r="B95">
-        <v>10</v>
+      <c r="A95" t="str">
+        <v>MRD10093</v>
+      </c>
+      <c r="B95" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C95" t="str">
         <v>C</v>
@@ -10630,11 +10630,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96">
-        <v>95</v>
-      </c>
-      <c r="B96">
-        <v>10</v>
+      <c r="A96" t="str">
+        <v>MRD10094</v>
+      </c>
+      <c r="B96" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C96" t="str">
         <v>C</v>
@@ -10734,11 +10734,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97">
-        <v>96</v>
-      </c>
-      <c r="B97">
-        <v>10</v>
+      <c r="A97" t="str">
+        <v>MRD10095</v>
+      </c>
+      <c r="B97" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C97" t="str">
         <v>S</v>
@@ -10835,11 +10835,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98">
-        <v>97</v>
-      </c>
-      <c r="B98">
-        <v>10</v>
+      <c r="A98" t="str">
+        <v>MRD10096</v>
+      </c>
+      <c r="B98" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C98" t="str">
         <v>S</v>
@@ -10936,11 +10936,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99">
-        <v>98</v>
-      </c>
-      <c r="B99">
-        <v>10</v>
+      <c r="A99" t="str">
+        <v>MRD10097</v>
+      </c>
+      <c r="B99" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C99" t="str">
         <v>C</v>
@@ -11037,11 +11037,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100">
-        <v>99</v>
-      </c>
-      <c r="B100">
-        <v>10</v>
+      <c r="A100" t="str">
+        <v>MRD10098</v>
+      </c>
+      <c r="B100" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C100" t="str">
         <v>C</v>
@@ -11138,11 +11138,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101">
-        <v>100</v>
-      </c>
-      <c r="B101">
-        <v>10</v>
+      <c r="A101" t="str">
+        <v>MRD10099</v>
+      </c>
+      <c r="B101" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C101" t="str">
         <v>C</v>
@@ -11242,11 +11242,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102">
-        <v>101</v>
-      </c>
-      <c r="B102">
-        <v>10</v>
+      <c r="A102" t="str">
+        <v>MRD10100</v>
+      </c>
+      <c r="B102" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C102" t="str">
         <v>C</v>
@@ -11343,11 +11343,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103">
-        <v>102</v>
-      </c>
-      <c r="B103">
-        <v>10</v>
+      <c r="A103" t="str">
+        <v>MRD10101</v>
+      </c>
+      <c r="B103" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C103" t="str">
         <v>C</v>
@@ -11444,11 +11444,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104">
-        <v>103</v>
-      </c>
-      <c r="B104">
-        <v>10</v>
+      <c r="A104" t="str">
+        <v>MRD10102</v>
+      </c>
+      <c r="B104" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C104" t="str">
         <v>C</v>
@@ -11545,11 +11545,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105">
-        <v>104</v>
-      </c>
-      <c r="B105">
-        <v>10</v>
+      <c r="A105" t="str">
+        <v>MRD10103</v>
+      </c>
+      <c r="B105" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C105" t="str">
         <v>C</v>
@@ -11649,11 +11649,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106">
-        <v>105</v>
-      </c>
-      <c r="B106">
-        <v>10</v>
+      <c r="A106" t="str">
+        <v>MRD10104</v>
+      </c>
+      <c r="B106" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C106" t="str">
         <v>C</v>
@@ -11750,11 +11750,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107">
-        <v>106</v>
-      </c>
-      <c r="B107">
-        <v>10</v>
+      <c r="A107" t="str">
+        <v>MRD10105</v>
+      </c>
+      <c r="B107" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C107" t="str">
         <v>S</v>
@@ -11851,11 +11851,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108">
-        <v>107</v>
-      </c>
-      <c r="B108">
-        <v>10</v>
+      <c r="A108" t="str">
+        <v>MRD10106</v>
+      </c>
+      <c r="B108" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C108" t="str">
         <v>C</v>
@@ -11952,11 +11952,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109">
-        <v>108</v>
-      </c>
-      <c r="B109">
-        <v>10</v>
+      <c r="A109" t="str">
+        <v>MRD10107</v>
+      </c>
+      <c r="B109" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C109" t="str">
         <v>C</v>
@@ -12053,11 +12053,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110">
-        <v>109</v>
-      </c>
-      <c r="B110">
-        <v>10</v>
+      <c r="A110" t="str">
+        <v>MRD10108</v>
+      </c>
+      <c r="B110" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C110" t="str">
         <v>S</v>
@@ -12154,11 +12154,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111">
-        <v>110</v>
-      </c>
-      <c r="B111">
-        <v>10</v>
+      <c r="A111" t="str">
+        <v>MRD10109</v>
+      </c>
+      <c r="B111" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C111" t="str">
         <v>C</v>
@@ -12255,11 +12255,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112">
-        <v>111</v>
-      </c>
-      <c r="B112">
-        <v>10</v>
+      <c r="A112" t="str">
+        <v>MRD10110</v>
+      </c>
+      <c r="B112" t="str">
+        <v>MR1009</v>
       </c>
       <c r="C112" t="str">
         <v>S</v>
@@ -12356,11 +12356,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113">
-        <v>112</v>
-      </c>
-      <c r="B113">
-        <v>11</v>
+      <c r="A113" t="str">
+        <v>MRD10111</v>
+      </c>
+      <c r="B113" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C113" t="str">
         <v>C</v>
@@ -12460,11 +12460,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114">
-        <v>113</v>
-      </c>
-      <c r="B114">
-        <v>11</v>
+      <c r="A114" t="str">
+        <v>MRD10112</v>
+      </c>
+      <c r="B114" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C114" t="str">
         <v>S</v>
@@ -12561,11 +12561,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115">
-        <v>114</v>
-      </c>
-      <c r="B115">
-        <v>11</v>
+      <c r="A115" t="str">
+        <v>MRD10113</v>
+      </c>
+      <c r="B115" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C115" t="str">
         <v>S</v>
@@ -12662,11 +12662,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116">
-        <v>115</v>
-      </c>
-      <c r="B116">
-        <v>11</v>
+      <c r="A116" t="str">
+        <v>MRD10114</v>
+      </c>
+      <c r="B116" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C116" t="str">
         <v>C</v>
@@ -12763,11 +12763,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117">
-        <v>116</v>
-      </c>
-      <c r="B117">
-        <v>11</v>
+      <c r="A117" t="str">
+        <v>MRD10115</v>
+      </c>
+      <c r="B117" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C117" t="str">
         <v>C</v>
@@ -12864,11 +12864,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118">
-        <v>117</v>
-      </c>
-      <c r="B118">
-        <v>11</v>
+      <c r="A118" t="str">
+        <v>MRD10116</v>
+      </c>
+      <c r="B118" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C118" t="str">
         <v>C</v>
@@ -12965,11 +12965,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119">
-        <v>118</v>
-      </c>
-      <c r="B119">
-        <v>11</v>
+      <c r="A119" t="str">
+        <v>MRD10117</v>
+      </c>
+      <c r="B119" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C119" t="str">
         <v>C</v>
@@ -13066,11 +13066,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120">
-        <v>119</v>
-      </c>
-      <c r="B120">
-        <v>11</v>
+      <c r="A120" t="str">
+        <v>MRD10118</v>
+      </c>
+      <c r="B120" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C120" t="str">
         <v>C</v>
@@ -13167,11 +13167,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121">
-        <v>120</v>
-      </c>
-      <c r="B121">
-        <v>11</v>
+      <c r="A121" t="str">
+        <v>MRD10119</v>
+      </c>
+      <c r="B121" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C121" t="str">
         <v>C</v>
@@ -13268,11 +13268,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122">
-        <v>121</v>
-      </c>
-      <c r="B122">
-        <v>11</v>
+      <c r="A122" t="str">
+        <v>MRD10120</v>
+      </c>
+      <c r="B122" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C122" t="str">
         <v>C</v>
@@ -13369,11 +13369,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123">
-        <v>122</v>
-      </c>
-      <c r="B123">
-        <v>11</v>
+      <c r="A123" t="str">
+        <v>MRD10121</v>
+      </c>
+      <c r="B123" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C123" t="str">
         <v>C</v>
@@ -13470,11 +13470,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124">
-        <v>123</v>
-      </c>
-      <c r="B124">
-        <v>11</v>
+      <c r="A124" t="str">
+        <v>MRD10122</v>
+      </c>
+      <c r="B124" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C124" t="str">
         <v>C</v>
@@ -13571,11 +13571,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125">
-        <v>124</v>
-      </c>
-      <c r="B125">
-        <v>11</v>
+      <c r="A125" t="str">
+        <v>MRD10123</v>
+      </c>
+      <c r="B125" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C125" t="str">
         <v>C</v>
@@ -13672,11 +13672,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126">
-        <v>125</v>
-      </c>
-      <c r="B126">
-        <v>11</v>
+      <c r="A126" t="str">
+        <v>MRD10124</v>
+      </c>
+      <c r="B126" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C126" t="str">
         <v>C</v>
@@ -13773,11 +13773,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127">
-        <v>126</v>
-      </c>
-      <c r="B127">
-        <v>11</v>
+      <c r="A127" t="str">
+        <v>MRD10125</v>
+      </c>
+      <c r="B127" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C127" t="str">
         <v>S</v>
@@ -13874,11 +13874,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128">
-        <v>127</v>
-      </c>
-      <c r="B128">
-        <v>11</v>
+      <c r="A128" t="str">
+        <v>MRD10126</v>
+      </c>
+      <c r="B128" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C128" t="str">
         <v>C</v>
@@ -13975,11 +13975,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129">
-        <v>128</v>
-      </c>
-      <c r="B129">
-        <v>11</v>
+      <c r="A129" t="str">
+        <v>MRD10127</v>
+      </c>
+      <c r="B129" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C129" t="str">
         <v>C</v>
@@ -14076,11 +14076,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130">
-        <v>129</v>
-      </c>
-      <c r="B130">
-        <v>11</v>
+      <c r="A130" t="str">
+        <v>MRD10128</v>
+      </c>
+      <c r="B130" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C130" t="str">
         <v>C</v>
@@ -14177,11 +14177,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131">
-        <v>130</v>
-      </c>
-      <c r="B131">
-        <v>11</v>
+      <c r="A131" t="str">
+        <v>MRD10129</v>
+      </c>
+      <c r="B131" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C131" t="str">
         <v>C</v>
@@ -14278,11 +14278,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132">
-        <v>131</v>
-      </c>
-      <c r="B132">
-        <v>11</v>
+      <c r="A132" t="str">
+        <v>MRD10130</v>
+      </c>
+      <c r="B132" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C132" t="str">
         <v>C</v>
@@ -14379,11 +14379,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133">
-        <v>132</v>
-      </c>
-      <c r="B133">
-        <v>11</v>
+      <c r="A133" t="str">
+        <v>MRD10131</v>
+      </c>
+      <c r="B133" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C133" t="str">
         <v>C</v>
@@ -14480,11 +14480,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134">
-        <v>133</v>
-      </c>
-      <c r="B134">
-        <v>11</v>
+      <c r="A134" t="str">
+        <v>MRD10132</v>
+      </c>
+      <c r="B134" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C134" t="str">
         <v>C</v>
@@ -14581,11 +14581,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135">
-        <v>134</v>
-      </c>
-      <c r="B135">
-        <v>11</v>
+      <c r="A135" t="str">
+        <v>MRD10133</v>
+      </c>
+      <c r="B135" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C135" t="str">
         <v>C</v>
@@ -14682,11 +14682,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136">
-        <v>135</v>
-      </c>
-      <c r="B136">
-        <v>11</v>
+      <c r="A136" t="str">
+        <v>MRD10134</v>
+      </c>
+      <c r="B136" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C136" t="str">
         <v>C</v>
@@ -14783,11 +14783,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137">
-        <v>136</v>
-      </c>
-      <c r="B137">
-        <v>11</v>
+      <c r="A137" t="str">
+        <v>MRD10135</v>
+      </c>
+      <c r="B137" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C137" t="str">
         <v>C</v>
@@ -14884,11 +14884,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138">
-        <v>137</v>
-      </c>
-      <c r="B138">
-        <v>11</v>
+      <c r="A138" t="str">
+        <v>MRD10136</v>
+      </c>
+      <c r="B138" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C138" t="str">
         <v>C</v>
@@ -14985,11 +14985,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139">
-        <v>138</v>
-      </c>
-      <c r="B139">
-        <v>11</v>
+      <c r="A139" t="str">
+        <v>MRD10137</v>
+      </c>
+      <c r="B139" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C139" t="str">
         <v>C</v>
@@ -15086,11 +15086,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140">
-        <v>139</v>
-      </c>
-      <c r="B140">
-        <v>11</v>
+      <c r="A140" t="str">
+        <v>MRD10138</v>
+      </c>
+      <c r="B140" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C140" t="str">
         <v>C</v>
@@ -15187,11 +15187,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141">
-        <v>140</v>
-      </c>
-      <c r="B141">
-        <v>11</v>
+      <c r="A141" t="str">
+        <v>MRD10139</v>
+      </c>
+      <c r="B141" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C141" t="str">
         <v>C</v>
@@ -15288,11 +15288,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142">
-        <v>141</v>
-      </c>
-      <c r="B142">
-        <v>11</v>
+      <c r="A142" t="str">
+        <v>MRD10140</v>
+      </c>
+      <c r="B142" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C142" t="str">
         <v>S</v>
@@ -15389,11 +15389,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143">
-        <v>142</v>
-      </c>
-      <c r="B143">
-        <v>11</v>
+      <c r="A143" t="str">
+        <v>MRD10141</v>
+      </c>
+      <c r="B143" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C143" t="str">
         <v>C</v>
@@ -15490,11 +15490,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144">
-        <v>143</v>
-      </c>
-      <c r="B144">
-        <v>11</v>
+      <c r="A144" t="str">
+        <v>MRD10142</v>
+      </c>
+      <c r="B144" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C144" t="str">
         <v>C</v>
@@ -15591,11 +15591,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145">
-        <v>144</v>
-      </c>
-      <c r="B145">
-        <v>11</v>
+      <c r="A145" t="str">
+        <v>MRD10143</v>
+      </c>
+      <c r="B145" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C145" t="str">
         <v>C</v>
@@ -15692,11 +15692,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146">
-        <v>145</v>
-      </c>
-      <c r="B146">
-        <v>11</v>
+      <c r="A146" t="str">
+        <v>MRD10144</v>
+      </c>
+      <c r="B146" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C146" t="str">
         <v>C</v>
@@ -15793,11 +15793,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147">
-        <v>146</v>
-      </c>
-      <c r="B147">
-        <v>11</v>
+      <c r="A147" t="str">
+        <v>MRD10145</v>
+      </c>
+      <c r="B147" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C147" t="str">
         <v>C</v>
@@ -15894,11 +15894,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148">
-        <v>147</v>
-      </c>
-      <c r="B148">
-        <v>11</v>
+      <c r="A148" t="str">
+        <v>MRD10146</v>
+      </c>
+      <c r="B148" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C148" t="str">
         <v>S</v>
@@ -15995,11 +15995,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149">
-        <v>148</v>
-      </c>
-      <c r="B149">
-        <v>11</v>
+      <c r="A149" t="str">
+        <v>MRD10147</v>
+      </c>
+      <c r="B149" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C149" t="str">
         <v>S</v>
@@ -16096,11 +16096,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150">
-        <v>149</v>
-      </c>
-      <c r="B150">
-        <v>11</v>
+      <c r="A150" t="str">
+        <v>MRD10148</v>
+      </c>
+      <c r="B150" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C150" t="str">
         <v>C</v>
@@ -16197,11 +16197,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151">
-        <v>150</v>
-      </c>
-      <c r="B151">
-        <v>11</v>
+      <c r="A151" t="str">
+        <v>MRD10149</v>
+      </c>
+      <c r="B151" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C151" t="str">
         <v>S</v>
@@ -16298,11 +16298,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152">
-        <v>151</v>
-      </c>
-      <c r="B152">
-        <v>11</v>
+      <c r="A152" t="str">
+        <v>MRD10150</v>
+      </c>
+      <c r="B152" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C152" t="str">
         <v>C</v>
@@ -16399,11 +16399,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153">
-        <v>152</v>
-      </c>
-      <c r="B153">
-        <v>11</v>
+      <c r="A153" t="str">
+        <v>MRD10151</v>
+      </c>
+      <c r="B153" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C153" t="str">
         <v>C</v>
@@ -16500,11 +16500,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154">
-        <v>153</v>
-      </c>
-      <c r="B154">
-        <v>11</v>
+      <c r="A154" t="str">
+        <v>MRD10152</v>
+      </c>
+      <c r="B154" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C154" t="str">
         <v>C</v>
@@ -16601,11 +16601,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155">
-        <v>154</v>
-      </c>
-      <c r="B155">
-        <v>11</v>
+      <c r="A155" t="str">
+        <v>MRD10153</v>
+      </c>
+      <c r="B155" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C155" t="str">
         <v>C</v>
@@ -16702,11 +16702,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156">
-        <v>155</v>
-      </c>
-      <c r="B156">
-        <v>11</v>
+      <c r="A156" t="str">
+        <v>MRD10154</v>
+      </c>
+      <c r="B156" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C156" t="str">
         <v>C</v>
@@ -16803,11 +16803,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157">
-        <v>156</v>
-      </c>
-      <c r="B157">
-        <v>11</v>
+      <c r="A157" t="str">
+        <v>MRD10155</v>
+      </c>
+      <c r="B157" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C157" t="str">
         <v>C</v>
@@ -16904,11 +16904,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158">
-        <v>157</v>
-      </c>
-      <c r="B158">
-        <v>11</v>
+      <c r="A158" t="str">
+        <v>MRD10156</v>
+      </c>
+      <c r="B158" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C158" t="str">
         <v>S</v>
@@ -17005,11 +17005,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159">
-        <v>158</v>
-      </c>
-      <c r="B159">
-        <v>11</v>
+      <c r="A159" t="str">
+        <v>MRD10157</v>
+      </c>
+      <c r="B159" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C159" t="str">
         <v>C</v>
@@ -17106,11 +17106,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160">
-        <v>159</v>
-      </c>
-      <c r="B160">
-        <v>11</v>
+      <c r="A160" t="str">
+        <v>MRD10158</v>
+      </c>
+      <c r="B160" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C160" t="str">
         <v>C</v>
@@ -17207,11 +17207,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161">
-        <v>160</v>
-      </c>
-      <c r="B161">
-        <v>11</v>
+      <c r="A161" t="str">
+        <v>MRD10159</v>
+      </c>
+      <c r="B161" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C161" t="str">
         <v>C</v>
@@ -17308,11 +17308,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162">
-        <v>161</v>
-      </c>
-      <c r="B162">
-        <v>11</v>
+      <c r="A162" t="str">
+        <v>MRD10160</v>
+      </c>
+      <c r="B162" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C162" t="str">
         <v>C</v>
@@ -17409,11 +17409,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163">
-        <v>162</v>
-      </c>
-      <c r="B163">
-        <v>11</v>
+      <c r="A163" t="str">
+        <v>MRD10161</v>
+      </c>
+      <c r="B163" t="str">
+        <v>MR1010</v>
       </c>
       <c r="C163" t="str">
         <v>C</v>
@@ -17510,11 +17510,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164">
-        <v>163</v>
-      </c>
-      <c r="B164">
-        <v>12</v>
+      <c r="A164" t="str">
+        <v>MRD10162</v>
+      </c>
+      <c r="B164" t="str">
+        <v>MR1011</v>
       </c>
       <c r="C164" t="str">
         <v>C</v>
@@ -17614,11 +17614,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165">
-        <v>164</v>
-      </c>
-      <c r="B165">
-        <v>12</v>
+      <c r="A165" t="str">
+        <v>MRD10163</v>
+      </c>
+      <c r="B165" t="str">
+        <v>MR1011</v>
       </c>
       <c r="C165" t="str">
         <v>C</v>
@@ -17718,11 +17718,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166">
-        <v>165</v>
-      </c>
-      <c r="B166">
-        <v>12</v>
+      <c r="A166" t="str">
+        <v>MRD10164</v>
+      </c>
+      <c r="B166" t="str">
+        <v>MR1011</v>
       </c>
       <c r="C166" t="str">
         <v>C</v>
@@ -17822,11 +17822,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167">
-        <v>166</v>
-      </c>
-      <c r="B167">
-        <v>12</v>
+      <c r="A167" t="str">
+        <v>MRD10165</v>
+      </c>
+      <c r="B167" t="str">
+        <v>MR1011</v>
       </c>
       <c r="C167" t="str">
         <v>C</v>
@@ -17926,11 +17926,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168">
-        <v>167</v>
-      </c>
-      <c r="B168">
-        <v>12</v>
+      <c r="A168" t="str">
+        <v>MRD10166</v>
+      </c>
+      <c r="B168" t="str">
+        <v>MR1011</v>
       </c>
       <c r="C168" t="str">
         <v>C</v>
@@ -18030,11 +18030,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169">
-        <v>168</v>
-      </c>
-      <c r="B169">
-        <v>12</v>
+      <c r="A169" t="str">
+        <v>MRD10167</v>
+      </c>
+      <c r="B169" t="str">
+        <v>MR1011</v>
       </c>
       <c r="C169" t="str">
         <v>C</v>
@@ -18134,11 +18134,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170">
-        <v>169</v>
-      </c>
-      <c r="B170">
-        <v>12</v>
+      <c r="A170" t="str">
+        <v>MRD10168</v>
+      </c>
+      <c r="B170" t="str">
+        <v>MR1011</v>
       </c>
       <c r="C170" t="str">
         <v>C</v>
@@ -18238,11 +18238,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171">
-        <v>170</v>
-      </c>
-      <c r="B171">
-        <v>12</v>
+      <c r="A171" t="str">
+        <v>MRD10169</v>
+      </c>
+      <c r="B171" t="str">
+        <v>MR1011</v>
       </c>
       <c r="C171" t="str">
         <v>C</v>
@@ -18342,11 +18342,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172">
-        <v>171</v>
-      </c>
-      <c r="B172">
-        <v>12</v>
+      <c r="A172" t="str">
+        <v>MRD10170</v>
+      </c>
+      <c r="B172" t="str">
+        <v>MR1011</v>
       </c>
       <c r="C172" t="str">
         <v>S</v>
@@ -18446,11 +18446,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173">
-        <v>172</v>
-      </c>
-      <c r="B173">
-        <v>12</v>
+      <c r="A173" t="str">
+        <v>MRD10171</v>
+      </c>
+      <c r="B173" t="str">
+        <v>MR1011</v>
       </c>
       <c r="C173" t="str">
         <v>S</v>
@@ -18550,11 +18550,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174">
-        <v>173</v>
-      </c>
-      <c r="B174">
-        <v>12</v>
+      <c r="A174" t="str">
+        <v>MRD10172</v>
+      </c>
+      <c r="B174" t="str">
+        <v>MR1011</v>
       </c>
       <c r="C174" t="str">
         <v>C</v>
@@ -18654,11 +18654,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175">
-        <v>174</v>
-      </c>
-      <c r="B175">
-        <v>12</v>
+      <c r="A175" t="str">
+        <v>MRD10173</v>
+      </c>
+      <c r="B175" t="str">
+        <v>MR1011</v>
       </c>
       <c r="C175" t="str">
         <v>S</v>
@@ -18758,11 +18758,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176">
-        <v>175</v>
-      </c>
-      <c r="B176">
-        <v>13</v>
+      <c r="A176" t="str">
+        <v>MRD10174</v>
+      </c>
+      <c r="B176" t="str">
+        <v>MR1012</v>
       </c>
       <c r="C176" t="str">
         <v>C</v>
@@ -18859,11 +18859,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177">
-        <v>176</v>
-      </c>
-      <c r="B177">
-        <v>13</v>
+      <c r="A177" t="str">
+        <v>MRD10175</v>
+      </c>
+      <c r="B177" t="str">
+        <v>MR1012</v>
       </c>
       <c r="C177" t="str">
         <v>C</v>
@@ -18960,11 +18960,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178">
-        <v>177</v>
-      </c>
-      <c r="B178">
-        <v>13</v>
+      <c r="A178" t="str">
+        <v>MRD10176</v>
+      </c>
+      <c r="B178" t="str">
+        <v>MR1012</v>
       </c>
       <c r="C178" t="str">
         <v>C</v>
@@ -19061,11 +19061,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179">
-        <v>178</v>
-      </c>
-      <c r="B179">
-        <v>14</v>
+      <c r="A179" t="str">
+        <v>MRD10177</v>
+      </c>
+      <c r="B179" t="str">
+        <v>MR1013</v>
       </c>
       <c r="C179" t="str">
         <v>C</v>
@@ -19162,11 +19162,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180">
-        <v>179</v>
-      </c>
-      <c r="B180">
-        <v>14</v>
+      <c r="A180" t="str">
+        <v>MRD10178</v>
+      </c>
+      <c r="B180" t="str">
+        <v>MR1013</v>
       </c>
       <c r="C180" t="str">
         <v>S</v>
@@ -19263,11 +19263,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181">
-        <v>180</v>
-      </c>
-      <c r="B181">
-        <v>14</v>
+      <c r="A181" t="str">
+        <v>MRD10179</v>
+      </c>
+      <c r="B181" t="str">
+        <v>MR1013</v>
       </c>
       <c r="C181" t="str">
         <v>S</v>
@@ -19364,11 +19364,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182">
-        <v>181</v>
-      </c>
-      <c r="B182">
-        <v>14</v>
+      <c r="A182" t="str">
+        <v>MRD10180</v>
+      </c>
+      <c r="B182" t="str">
+        <v>MR1013</v>
       </c>
       <c r="C182" t="str">
         <v>C</v>
@@ -19465,11 +19465,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183">
-        <v>182</v>
-      </c>
-      <c r="B183">
-        <v>14</v>
+      <c r="A183" t="str">
+        <v>MRD10181</v>
+      </c>
+      <c r="B183" t="str">
+        <v>MR1013</v>
       </c>
       <c r="C183" t="str">
         <v>S</v>
@@ -19566,11 +19566,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184">
-        <v>183</v>
-      </c>
-      <c r="B184">
-        <v>14</v>
+      <c r="A184" t="str">
+        <v>MRD10182</v>
+      </c>
+      <c r="B184" t="str">
+        <v>MR1013</v>
       </c>
       <c r="C184" t="str">
         <v>C</v>
@@ -19667,11 +19667,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185">
-        <v>184</v>
-      </c>
-      <c r="B185">
-        <v>14</v>
+      <c r="A185" t="str">
+        <v>MRD10183</v>
+      </c>
+      <c r="B185" t="str">
+        <v>MR1013</v>
       </c>
       <c r="C185" t="str">
         <v>S</v>
@@ -19768,11 +19768,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186">
-        <v>185</v>
-      </c>
-      <c r="B186">
-        <v>15</v>
+      <c r="A186" t="str">
+        <v>MRD10184</v>
+      </c>
+      <c r="B186" t="str">
+        <v>MR1014</v>
       </c>
       <c r="C186" t="str">
         <v>C</v>
@@ -19869,11 +19869,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187">
-        <v>186</v>
-      </c>
-      <c r="B187">
-        <v>15</v>
+      <c r="A187" t="str">
+        <v>MRD10185</v>
+      </c>
+      <c r="B187" t="str">
+        <v>MR1014</v>
       </c>
       <c r="C187" t="str">
         <v>C</v>

--- a/GearSage-client/pkgGear/data_raw/megabass_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/megabass_rod_import.xlsx
@@ -439,8 +439,8 @@
       <c r="A2" t="str">
         <v>MR1000</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="B2">
+        <v>7</v>
       </c>
       <c r="C2" t="str">
         <v>ARMS SUPER LEGGERA</v>
@@ -474,8 +474,8 @@
       <c r="A3" t="str">
         <v>MR1001</v>
       </c>
-      <c r="B3" t="str">
-        <v/>
+      <c r="B3">
+        <v>7</v>
       </c>
       <c r="C3" t="str">
         <v>DESTROYER T.S</v>
@@ -509,8 +509,8 @@
       <c r="A4" t="str">
         <v>MR1002</v>
       </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="B4">
+        <v>7</v>
       </c>
       <c r="C4" t="str">
         <v>TRIZA</v>
@@ -544,8 +544,8 @@
       <c r="A5" t="str">
         <v>MR1003</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="B5">
+        <v>7</v>
       </c>
       <c r="C5" t="str">
         <v>Pagani TRAD</v>
@@ -579,8 +579,8 @@
       <c r="A6" t="str">
         <v>MR1004</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="B6">
+        <v>7</v>
       </c>
       <c r="C6" t="str">
         <v>ARMS SUPER LEGGERA SPINNING</v>
@@ -614,8 +614,8 @@
       <c r="A7" t="str">
         <v>MR1005</v>
       </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="B7">
+        <v>7</v>
       </c>
       <c r="C7" t="str">
         <v>OROCHI X10</v>
@@ -649,8 +649,8 @@
       <c r="A8" t="str">
         <v>MR1006</v>
       </c>
-      <c r="B8" t="str">
-        <v/>
+      <c r="B8">
+        <v>7</v>
       </c>
       <c r="C8" t="str">
         <v>EVOLUZION</v>
@@ -684,8 +684,8 @@
       <c r="A9" t="str">
         <v>MR1007</v>
       </c>
-      <c r="B9" t="str">
-        <v/>
+      <c r="B9">
+        <v>7</v>
       </c>
       <c r="C9" t="str">
         <v>GREATHUNTING RIVER&amp;LAKE EDITION</v>
@@ -719,8 +719,8 @@
       <c r="A10" t="str">
         <v>MR1008</v>
       </c>
-      <c r="B10" t="str">
-        <v/>
+      <c r="B10">
+        <v>7</v>
       </c>
       <c r="C10" t="str">
         <v>GREATHUNTING HUNTSMAN</v>
@@ -754,8 +754,8 @@
       <c r="A11" t="str">
         <v>MR1009</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
+      <c r="B11">
+        <v>7</v>
       </c>
       <c r="C11" t="str">
         <v>Brand New DESTROYER</v>
@@ -789,8 +789,8 @@
       <c r="A12" t="str">
         <v>MR1010</v>
       </c>
-      <c r="B12" t="str">
-        <v/>
+      <c r="B12">
+        <v>7</v>
       </c>
       <c r="C12" t="str">
         <v>LEVANTE</v>
@@ -824,8 +824,8 @@
       <c r="A13" t="str">
         <v>MR1011</v>
       </c>
-      <c r="B13" t="str">
-        <v/>
+      <c r="B13">
+        <v>7</v>
       </c>
       <c r="C13" t="str">
         <v>VALKYRIE World Expedition</v>
@@ -859,8 +859,8 @@
       <c r="A14" t="str">
         <v>MR1012</v>
       </c>
-      <c r="B14" t="str">
-        <v/>
+      <c r="B14">
+        <v>7</v>
       </c>
       <c r="C14" t="str">
         <v>GREATHUNTING TRACKING BUDDY</v>
@@ -894,8 +894,8 @@
       <c r="A15" t="str">
         <v>MR1013</v>
       </c>
-      <c r="B15" t="str">
-        <v/>
+      <c r="B15">
+        <v>7</v>
       </c>
       <c r="C15" t="str">
         <v>GREATHUNTING MOUNTAIN STREAM EDITION</v>
@@ -929,8 +929,8 @@
       <c r="A16" t="str">
         <v>MR1014</v>
       </c>
-      <c r="B16" t="str">
-        <v/>
+      <c r="B16">
+        <v>7</v>
       </c>
       <c r="C16" t="str">
         <v>GreatHunting X-GLASS COMPOSITE</v>
@@ -1072,10 +1072,10 @@
         <v>Description</v>
       </c>
       <c r="AH1" t="str">
-        <v>Other.1</v>
+        <v>Extra Spec 1</v>
       </c>
       <c r="AI1" t="str">
-        <v>Other.2</v>
+        <v>Extra Spec 2</v>
       </c>
     </row>
     <row r="2">
@@ -1179,7 +1179,10 @@
         <v>High power versatile model from the boat or shore, heavy cover and any depth. Advances is speedy searching capability. Application include Bigbait, heavy weight spinnerbait, wild header, large crank such as Granade and big crank. Transform angler's arm to lethal weapon. Flagship model of ARMS series. * The photograph is a prototype.</v>
       </c>
       <c r="AH2" t="str">
-        <v>オフセットハンドル</v>
+        <v>Other.1: オフセットハンドル</v>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1282,6 +1285,12 @@
       <c r="AG3" t="str">
         <v>The ASL6402X is a combat-style bait finesse model designed to pitch small rubber jig and weightless soft plastic with accuracy and speed. Also excels at presenting small, lightweight plugs such as SHADING-X and X-80 Jr. when traditional Spinning set-ups fall short of heavier cover. * The photograph is a prototype.</v>
       </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1383,6 +1392,12 @@
       <c r="AG4" t="str">
         <v>Built to master spinnerbait cover hacking, weed cutting and quick search by vibration and deep cranks with excellent castability for long distance. Supple tip combined with strong butt section along with high sensitivity. Sub-use  recommendation is no sinker heavy weight plastics into covers. * The photograph is a prototype.</v>
       </c>
+      <c r="AH4" t="str">
+        <v/>
+      </c>
+      <c r="AI4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -1484,6 +1499,12 @@
       <c r="AG5" t="str">
         <v>Designed to fish frog on mats and jig and worm in heavy cover. High-powered blank model is now introducing in ARMS series. Also ideal for bigbait such as I-SLIDE and super deep structure applications with its advanced controllability. * The photograph is a prototype.</v>
       </c>
+      <c r="AH5" t="str">
+        <v/>
+      </c>
+      <c r="AI5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -1585,6 +1606,12 @@
       <c r="AG6" t="str">
         <v>The ASL700XG is the first ever glass composite model to debut in the storied ARMS legacy. With an extremely lightweight and powerful blank, the 7004XG allows for advanced control of fast-moving lures. Ideal for a large variety of applications, ranging from 1/4 plugs to 1oz. size deep crankbaits. The ASL7004XG’s pace-setting blank sets the stage for future fast-moving applications. * The photograph is a prototype.</v>
       </c>
+      <c r="AH6" t="str">
+        <v/>
+      </c>
+      <c r="AI6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -1686,6 +1713,12 @@
       <c r="AG7" t="str">
         <v>Equipped with double-footed guides along the length of its powerful blank, the ASL7208X is the ultimate monster hunting special. Ideal for bigbaits, jigs, punching and heavy mat frogging, this is the debut of the ARMS Super Leggera heavy-duty. With unforgiving strength packaged in a lightweight frame, the 7208X brings a perfect balance to elevate monster hunting to the next level of performance. * The photograph is a prototype.</v>
       </c>
+      <c r="AH7" t="str">
+        <v/>
+      </c>
+      <c r="AI7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -1787,6 +1820,12 @@
       <c r="AG8" t="str">
         <v>Reminiscent of rare classic model "ONETEN Stick". Smooth bent action excels in castability and controllability. Ideal applications include jerkbait, topwater, shallow running crankbait, spinnerbait and vibration. Fast-moving versatility model. * The photograph is a prototype.</v>
       </c>
+      <c r="AH8" t="str">
+        <v/>
+      </c>
+      <c r="AI8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1888,6 +1927,12 @@
       <c r="AG9" t="str">
         <v>Just an inch short of 7 foot feels much shorter in your hand and offers excellent controllability. Fast taper blank design becomes regular taper when heavy load applies to secure your catch to the boat every time. Designed for all types of light plugs and its versatility allows finesse application in to the cover. * The photograph is a prototype.</v>
       </c>
+      <c r="AH9" t="str">
+        <v/>
+      </c>
+      <c r="AI9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -1989,8 +2034,11 @@
       <c r="AG10" t="str">
         <v>This super strong shaft is a step above the TS78X+, and is capable of fully casting super heavyweight lures. It easily accommodates 30-35 cm class big bait, swimbait, and magnum-sized spoons. The overwhelming torsional rigidity and load bearing strength of the DNA graphite will never give in to the monstrous foes you encounter.</v>
       </c>
+      <c r="AH10" t="str">
+        <v>Other.2: オフセットハンドル</v>
+      </c>
       <c r="AI10" t="str">
-        <v>オフセットハンドル</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -2093,8 +2141,11 @@
       <c r="AG11" t="str">
         <v>Anglers in pursuit of the catch of a lifetime demand equipment that performs at the highest-level day in and day out, allowing anglers to maximize slim bite windows and scarce opportunities to land those record-class fish. Megabass gladly accepted this challenge, developing a rod built purely for the baits, techniques, control, and power to land the next world record. For the TS78X, we started from scratch, discarding the design and production concepts behind past bass rods. For the material, we utilized the DNA-SLX graphite system developed for battling tuna, yielding a high-torque blank that is the embodiment of sheer power. This blank can fully cast 200g+ big baits, combined with the lifting-power to pull 20+ pound trophies from the depths. Featuring double-footed guides, each foot is carefully double-wrapped, improving durability, and protecting the blank from any possible damage the metal could exact under extra-heavy load. The TS78X has a special hood that locks the reel in place, securing another key component that will determine the outcome of the fight. The taper action is fast. Despite being such a powerful rod, it is equipped with a surprisingly sensitive tip, allowing for a wider-range of rod work to impart action to giant baits. Taking bank anglers and storage during transport into consideration, the TS-78X is built with a heavy-duty grip-joint. This allows the rod to be taken apart for trips, without sacrificing any strength or durability.</v>
       </c>
+      <c r="AH11" t="str">
+        <v>Other.2: オフセットハンドル</v>
+      </c>
       <c r="AI11" t="str">
-        <v>オフセットハンドル</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -2197,8 +2248,11 @@
       <c r="AG12" t="str">
         <v>While the TS78X is made purely to catch world record fish, the TS77X CASINO has a more reserved design. Made for anglers who pursue their dreams using more than giant baits, the TS77X highly for super-deep crankbaits and magnum spoons. The all double-footed guide system is perfectly reinforced with double wrapping, for powerful control and long-term durability. These tough specifications were created with battles against 70 cm + class monsters in mind.</v>
       </c>
+      <c r="AH12" t="str">
+        <v>Other.2: オフセットハンドル</v>
+      </c>
       <c r="AI12" t="str">
-        <v>オフセットハンドル</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -2301,6 +2355,12 @@
       <c r="AG13" t="str">
         <v>This high-powered long shaft spinning rod is not only great for deep fishing with 1oz+ down-shot rigs (a.k.a. drop-shot), but also works well when coupled with large spinning reels to cover a wide area quickly with deep cranking. The top of the rear grip features a flat-cut arm hold, letting you cope with the sudden, unexpected movements of big bass.</v>
       </c>
+      <c r="AH13" t="str">
+        <v/>
+      </c>
+      <c r="AI13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -2402,8 +2462,11 @@
       <c r="AG14" t="str">
         <v>The “Man of the Heavens” was born with the sole purpose of targeting world records. This ultra-strong shaft can fully cast giant, 40 cm+ bait. The tip section features exquisite tension derived through extensive field testing. It stands up superbly to pulling resistance, and allows for the user to freely control giant bait. The destructive torque of the TS82X lets you instantly pierce the jaws of monster fish with thick hooks and bring them under your control with overwhelming power.</v>
       </c>
+      <c r="AH14" t="str">
+        <v>Other.2: オフセットハンドル</v>
+      </c>
       <c r="AI14" t="str">
-        <v>オフセットハンドル</v>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -2506,6 +2569,12 @@
       <c r="AG15" t="str">
         <v>The TS711 BLACK JACK was developed specifically for deep-zone approaches requiring super long casts. Overwhelming blank power allows for bombing casts of 2+oz. lure, maximizing angler effort to increase distances without extra energy. Designed for a variety of applications, ranging from magnum-sized Crankbaits, heavy Spinnerbaits like the Venom, large Swimbaits and umbrella rigs. Fully armed with double-footed guides, carefully fixed along the blank with double thread wrapping for durability. Long grip length for all-day heavyweight retrieval. Built for mortal combat with monster bass.</v>
       </c>
+      <c r="AH15" t="str">
+        <v/>
+      </c>
+      <c r="AI15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -2607,6 +2676,12 @@
       <c r="AG16" t="str">
         <v>Built to target the deep zones of big lakes, TS72X POKER big game rod was developed to deploy big jigs with precision, power, and unmatched feel. The TS series utilizes a powerful multi-axis blank for devastating lifting power. Improved rod balance allows anglers to control jigs with precision and minimal fatigue throughout the day.</v>
       </c>
+      <c r="AH16" t="str">
+        <v/>
+      </c>
+      <c r="AI16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -2708,8 +2783,11 @@
       <c r="AG17" t="str">
         <v>While using 20-30 cm long and heavy big bait to target deep zones, the ability of the TS78X+ to instantaneously lift hooked monsters to the surface is breathtaking. It is highly suited for large cranks and heavyweight Alabama rigs.</v>
       </c>
+      <c r="AH17" t="str">
+        <v>Other.2: オフセットハンドル</v>
+      </c>
       <c r="AI17" t="str">
-        <v>オフセットハンドル</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -2812,8 +2890,11 @@
       <c r="AG18" t="str">
         <v>The TRIZA DRAGOON is equipped with the “Exclusive Tip.” The customization patterns include the ① “Regular Taper” tip and the ② “Fast Taper” tip which allow for a wide array of fishing methods. The ① “Regular Taper” tip is perfect for powerful fishing using big baits and swim baits. It realizes high torque games that far surpass what past multi-piece rods were capable of. The ② “Fast Taper” tip turns the DRAGOON into a jig and Texas rod that’s expertly suited for striking at heavy cover. The unique design of the tip effectively transmits power to the second belly section, generating the tension needed for jig and worm fishing, as well as achieving excellent sensitivity and vibration transmission characteristics. With one base rod, the DRAGOON transforms to excel at many different applications. * The photograph is a prototype.</v>
       </c>
+      <c r="AH18" t="str">
+        <v>Other.2: エクスクルーシブティップ対応モデル</v>
+      </c>
       <c r="AI18" t="str">
-        <v>エクスクルーシブティップ対応モデル</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -2916,8 +2997,11 @@
       <c r="AG19" t="str">
         <v>Using cutting edge processes, Megabass finesse rod technology has been incorporated into a multi-piece rod. The TRIZA’s unique Triangle construction has created yet another masterpiece rod. That rod is the HIBALI. This extra fine spinning rod is designed for delicate, thrilling approaches with super lightweight finesse rigs. The HIBALI’s unique fine tip makes extreme delicate shaking possible, and the precision tip section has been designed to reliably hook even the gentlest of short bites. Despite being a delicate shaft, the three-piece Triangle construction exhibits astonishing torque and rigidity from the belly section through the butt section, allowing you to comfortably handle surprise attacks from big fish. This completely new finesse shaft not only surpasses the performance of past three-piece shafts but exceeds the performance of previous one piece ultralight rods. The HIBALI has arrived. * The photograph is a prototype.</v>
       </c>
+      <c r="AH19" t="str">
+        <v>Other.2: エクスクルーシブティップ対応モデル</v>
+      </c>
       <c r="AI19" t="str">
-        <v>エクスクルーシブティップ対応モデル</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -3020,8 +3104,11 @@
       <c r="AG20" t="str">
         <v>The TRIZA’s much anticipated finesse function model, the YAMASEMI, is a light action game rod that vastly expands the world of light games. The ① “Fast” tip customization using tubular carbon exhibits delicate, high sensitivity, performance finesse bass fishing using small rubber jigs and jig heads. It’s well suited for not only bass fishing, but also expands the stage to saltwater mebaru games. The ② “Solid” tip customization allows for high performance down shot bass fishing. It’s well suited for insect pattern fishing and professional competitive finesse games comparable to that achieved with tournament rods. It’s well suited not only for bass fishing but expands the stage to saltwater aji games as well. * The photograph is a prototype.</v>
       </c>
+      <c r="AH20" t="str">
+        <v>Other.2: エクスクルーシブティップ対応モデル</v>
+      </c>
       <c r="AI20" t="str">
-        <v>エクスクルーシブティップ対応モデル</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -3124,8 +3211,11 @@
       <c r="AG21" t="str">
         <v>The SPARNA is a versatile, light model that excels at the long-distance casting and control of shads, mini cranks, middleweight topwaters, and long-distance bait finesse. The sharp, super lightweight, high elasticity shaft gives a great casting feel with lightweight lures and has extreme accuracy for pinpoint attacks thank to the stable Triangle construction. The overwhelmingly high sensitivity blows past multi-joint rods out of water and transmits information about the position of the lure and the surrounding environment clearly back to the hands of the angler through the natural wood reel seat. This new light action special rod features superbly accurate control and sensitivity. * The photograph is a prototype.</v>
       </c>
+      <c r="AH21" t="str">
+        <v>Other.2: エクスクルーシブティップ対応モデル</v>
+      </c>
       <c r="AI21" t="str">
-        <v>エクスクルーシブティップ対応モデル</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -3228,6 +3318,12 @@
       <c r="AG22" t="str">
         <v>The LOPROS is a versatile spinning rod that can handle anything from fishing with lightweight hard plugs to all types of finesse rigs. The extreme long-distance approach made possible by the 7’ shaft dramatically increases the productive zones of lures such as shads and small minnows, driving up bite chances. The LOPROS is highly suited for many methods, from boat-based dragging to lift-and-fall with mini vibration bait from shore. Developed to be a long-distance rod with excellent controllability, its unique high elasticity high tension construction exhibits sensitivity that far surpasses that of other multi piece rods. It delicately controls finesse rigs such as neko rigs and down shots, accurately senses terrain changes and instantly transmits shorts bites back to the angler. The high-tension blank makes solid hook setting possible even over long distances. The LOPROS creates opportunity under tough conditions. It can be stowed away compactly and is very convenient to have on hand. This long approach spinning rod is perfect for the angler searching for a convenient multipurpose model. * The photograph is a prototype.</v>
       </c>
+      <c r="AH22" t="str">
+        <v/>
+      </c>
+      <c r="AI22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -3329,6 +3425,12 @@
       <c r="AG23" t="str">
         <v>The STYM PALIDES is a heavy action multi-piece rod designed to comfortably handle heavy cover games that challenged past multi-piece rods. It’s well suited for a wide variety of approaches including 3/8oz jigs, Texas rigs, and fast-moving games in wide open fields. The special layered construction of the STYM PALIDES creates a crisp, well-balanced blank that generates overwhelming torque. The STYM PALIDES has achieved shaft performance on par with one-piece rods. It has the power needed to pierce the jaws of monster fish with the thick hooks of Texas rigs and rubber jigs and to forcefully pull them out of cover. It can handle deep cranks and large spinner baits which have a lot of pulling resistance with ease. This special heavy versatile rod is the culmination of extreme bass fishing technology. * The photograph is a prototype.</v>
       </c>
+      <c r="AH23" t="str">
+        <v/>
+      </c>
+      <c r="AI23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -3430,6 +3532,12 @@
       <c r="AG24" t="str">
         <v>The high-tension spinning model AGEHA is the embodiment of global angling brought on by mobile rods. The high tension “Medium Fast” taper has left past multi-piece rods in the dust and achieves a smooth bending taper like that of a one-piece shaft. There are over 600 hours of engineering effort poured into the AGEHA. This next-generation power spinning model’s performance covers everything from light rigs and small vibes to small minnow plugs. The robust belly tension and powerful butt section unseen in past multi-piece rods have greatly widened its range of abilities. This multi-piece high power concept is unique to the AGEHA, allowing for versatile performance against a broad range of targets in many scenarios from big trout games to seabass games. This masterpiece rod can handle fishing against all targets at a high level. * The photograph is a prototype.</v>
       </c>
+      <c r="AH24" t="str">
+        <v/>
+      </c>
+      <c r="AI24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -3531,6 +3639,12 @@
       <c r="AG25" t="str">
         <v>The AELLO has been designed with a well-tensioned, natural bending taper that allows for intuitive, direct control of poppers and pencil baits for a new type of finesse bass fishing. It effortlessly performs rhythmic dog walk action, and delicate, pinpoint topwater actions. The three-piece Triangle design suited for technical rod work generates sharp tension and plentiful torque from the belly through to the butt section. This keeps the rod stable, true, and eliminates the dull feeling of past slow taper rods. The AELLO can also act as a super lightweight bait finesse rod used to attacking around cover-areas. This ultra-fine spec rod is designed to precisely control lures according to the angler’s intention, with the blank bending to the limit to land target fish. * The photograph is a prototype.</v>
       </c>
+      <c r="AH25" t="str">
+        <v/>
+      </c>
+      <c r="AI25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -3632,6 +3746,12 @@
       <c r="AG26" t="str">
         <v>The THUNDERBIRD is a versatile model suited for a wide variety of uses from fast moving lures to topwater plugs to worming. The full parabolic bend features a well-tensioned intuitive blank curve that blows away past multi-piece rods. It effectively converts the lure’s weight into inertia during casting for smooth long-distance casting performance. The taper has excellent tracking properties and will automatically hook up short bites during high speed retrieves with crank baits and spinner baits. The THUNDERBIRD is highly adaptable to many types of fishing including no-sinker rigs with heavy worms and chatter bait in weed bottom areas and around cover. This versatile model serves as the core of the TRIZA series. * The photograph is a prototype.</v>
       </c>
+      <c r="AH26" t="str">
+        <v/>
+      </c>
+      <c r="AI26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -3733,6 +3853,12 @@
       <c r="AG27" t="str">
         <v>The GRILS breaks through the limitations of past multipiece rods, featuring shaft performance equal to that of one-piece rods. TRIZA’s Triangle design allows for agile control with middleweight fast moving games using crank baits, vibration baits, minnows, spinner baits and more. The 6’8” high tension shaft has excellent casting performance and is extremely effective at efficient wide area search approaches. The agile control of the TRIZA makes for responsive minnow twitches and lift and falls with vibration bait. The GRILS combines flexible elasticity with high sensitivity. It exhibits excellent structure evasion when cranking or spinner baiting. This model realizes delicate yet bold fast-moving games. * The photograph is a prototype.</v>
       </c>
+      <c r="AH27" t="str">
+        <v/>
+      </c>
+      <c r="AI27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -3834,6 +3960,12 @@
       <c r="AG28" t="str">
         <v>低弾性カーボン特有の柔らかな粘りのあるブランクスが生み出すのは、移動距離を抑えたライブリーなアクション。しなやかなティップと粘りのあるベリーによってリズミカルなロッドワークを実現し、ルアー自身の持つポテンシャルを最大限に引き出します。ドッグウォーク、テーブルターン、ポッピング、ダイビングなど、あらゆるアクションメソッドを高次元で実現します。 使用オススメルアー : POPXシリーズ、 POPMAXシリーズ、BALSAMAXシリーズ、DOG-Xシリーズ、Gatta-Xシリーズ、SCREAM-Xシリーズ</v>
       </c>
+      <c r="AH28" t="str">
+        <v/>
+      </c>
+      <c r="AI28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -3935,6 +4067,12 @@
       <c r="AG29" t="str">
         <v>繊細でシャープなブランクスのリザーバードッグは、シビアなプレゼンテーションが求められる小規模エリアにおいてピンスポットへのタイトアプローチが可能。軽快なロッドワークによって、キレのあるレスポンシブなルアーアクションを生み出します。身体の可動域が制限されるフローターゲームにおいても、高次元のトップウォーターゲームを展開します。 使用オススメルアー : DOG-Xシリーズ、POPXシリーズ、XPODシリーズ、Gatta-Xシリーズ、SCREAM-Xシリーズ</v>
       </c>
+      <c r="AH29" t="str">
+        <v/>
+      </c>
+      <c r="AI29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -4036,6 +4174,12 @@
       <c r="AG30" t="str">
         <v>人的プレッシャーに左右されやすいトップウォーターフィッシングにおいて、絶対的なアドバンテージとなるロングディスタンスプローチが可能。大型プラグをシングルハンドでキャスト可能な、しなやかさと強さを両立したブランクスに設計しています。 また、粘りのある強靭なバッドパワーによって、不意なモンスターとのファイトでも相手に主導権を与えません。 使用オススメルアー : X-PLOSEシリーズ、POPMAXシリーズ、XPODシリーズ、SCREAM-Xシリーズ、Gatta-Xシリーズ、GONGシリーズ</v>
       </c>
+      <c r="AH30" t="str">
+        <v/>
+      </c>
+      <c r="AI30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -4138,7 +4282,10 @@
         <v>徹底的にフィネスゲームを極めた「喰わせ」のスペシャリスト。操作性、感度をかつてなき極限まで高めた6’4”のブランクスはまさにARMS。バットからティップまですべてのセクションが腕の延長となってアングラーの意思をスムーズに伝達。水中のルアーを意のままにアクションさせます。フィネスロッドの常識を覆す究極のロッド、ASL6401XSが新たなフィネスゲームの扉を開きます。 ※価格はオプションの内容により異なります。</v>
       </c>
       <c r="AH31" t="str">
-        <v>End Blancer Material : MARBLE WOOD</v>
+        <v>Other.1: End Blancer Material : MARBLE WOOD</v>
+      </c>
+      <c r="AI31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -4242,7 +4389,10 @@
         <v>卓越したキャストフィールと軽快な操作感を併せ持つ、次世代マルチスピニングロッド。ライトリグはもちろんタイニープラグまでをディスタンスに関係なく緻密に操作可能。長さを感じさせないロッドバランスと強靭なバットパワーが、鋭く攻撃的なフィネスゲームを展開。6’7”という絶妙なシャフトレングスから生まれるハイトルクがビッグフィッシュを確実にランディングに持ち込みます。 ※価格はオプションの内容により異なります。</v>
       </c>
       <c r="AH32" t="str">
-        <v>End Blancer Material : MAHOGANY WOOD</v>
+        <v>Other.1: End Blancer Material : MAHOGANY WOOD</v>
+      </c>
+      <c r="AI32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -4346,7 +4496,10 @@
         <v>メガバス・スピニングロッドの名竿、F3-610XSの操作性や軽量感はそのままに、長さを2インチアップ。ティップまで一貫した張りを持たせたASL7003XSは、軽量リグの一点シェイクとライトプラッギングという、相反するメソッドを両立。アームズスーパーレジェーラ・スピニングのフラッグシップシャフトとして次世代のバーサタリティアプローチを実現します。 ※価格はオプションの内容により異なります。</v>
       </c>
       <c r="AH33" t="str">
-        <v>End Blancer Material : TEAK WOOD</v>
+        <v>Other.1: End Blancer Material : TEAK WOOD</v>
+      </c>
+      <c r="AI33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -4449,6 +4602,12 @@
       <c r="AG34" t="str">
         <v>KIRISAME COMPETITION is an extreme finesse model developed for the ultra-tough tournaments of Japan. The solid tip, made with Megabass' latest construction method, is sensitive to the most delicate bites, enabling ultra-precise rod work and improved hookup ratios. From the tip, the blank seamlessly transitions to finish with a high-torque butt section that delivers F2 level power. Integrating these disparate elements into a single shaft, X10 enables a truly unique angling experience. This is a finesse spinning model that takes pride in bringing the subtle details of no-sinker rigs, neko rigs, dropshots and small plugs to brilliant life.</v>
       </c>
+      <c r="AH34" t="str">
+        <v/>
+      </c>
+      <c r="AI34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -4550,6 +4709,12 @@
       <c r="AG35" t="str">
         <v>The JADE PYTHON, the renowned high-power spinning model, has been revitalized with X10 organic fiber. The X10 material reinforces the rigidity of the butt section, which allows anglers to attack tangled timber and intricate bushes with lightweight rigs. In addition to its high-torque characteristics, the new JADE PYTHON benefits from the X10’s lightweight construction for nimble handling and integrated feel.  With the kind of sensitivity that enables the angler to trace bottom composition with clarity, JADE PYTHON stands out in subtle transition areas, sparse cover and complicated structure where navigations happens by feel. JADE PYTHON also excels in long distance applications with minnows, shad, and small vibrations in windy situations where baitcasting equipment often under-delivers. A masterpiece of high-torque spinning is reborn for modern waters.</v>
       </c>
+      <c r="AH35" t="str">
+        <v/>
+      </c>
+      <c r="AI35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -4652,7 +4817,10 @@
         <v>Like its namesake, ANACONDA is built to overwhelm record-class targets with relentless torque and power.  Ideally suited for punching and frogging in super heavy cover areas, long distance games with big swimbaits, and approaches with magnum baits up to 7 oz., ANACONDA is ready to take the fight to bass fishing destinations around the world.  ANACONDA is a full-contact, extra-heavy rod that sends big baits to the farthest reaches with ease, boldly challenging monsters used to lurking just out of reach. X10 blanks are strong and lightweight, enabling superb balance to reduce angler fatigue on the frontlines.</v>
       </c>
       <c r="AH36" t="str">
-        <v>オフセットハンドル</v>
+        <v>Other.1: オフセットハンドル</v>
+      </c>
+      <c r="AI36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -4755,6 +4923,12 @@
       <c r="AG37" t="str">
         <v>The KIRISAME BAIT FINESSE is a long-distance finesse special. Equipped with a Megabass original solid tip, the blank exhibits the willing “give” necessary to trick finicky feeders grown wise to line tension. The X10’s taut belly section quickly converts angler energy into sure hooksets, while the X10’s organic fiber taps into a tenacious strength that can pull fighting fish away from structure. The KIRISAME is a confidence-inspiring bait finesse rod with reach and agility, enabling anglers to make long, nimble casts from the shoreline.</v>
       </c>
+      <c r="AH37" t="str">
+        <v/>
+      </c>
+      <c r="AI37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -4856,6 +5030,12 @@
       <c r="AG38" t="str">
         <v>The SWAMP SURVIVOR is a power-playing frog and swimbait model designed for heavy vegetation areas. The X10 displays high shaft rigidity and outstanding maneuverability. In the frog game, this translates into devastatingly quick and powerful hooksets and the kind of relentless power that can overcome the struggles of deep-cover monsters. In open water around weed edges, standing timber, and other cover, the SURVIVOR is a perfect choice for big baits and swimbaits, displaying ample power to keep hard-won bites free of entanglement.  Finished with double-footed guides, SWAMP SURVIVOR is fully armed for versatile power games.</v>
       </c>
+      <c r="AH38" t="str">
+        <v/>
+      </c>
+      <c r="AI38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -4957,6 +5137,12 @@
       <c r="AG39" t="str">
         <v>The jig and Texas rig model from the original Destroyer® series has been reimagined in the Orochi X10. Designed alongside Hirokazu Kawabe, one of Japan's leading football jig experts, the BEARING DOWN reveals a new dimension of jig fishing. Realizing the full potential of X10 blank design, the F5.1/2-69XT exhibits high blank tension and refined sensitivity, anchored by a deeply torquey butt section. The X10’s formidable power-to-weight ratio inspires confidence and control, while the blank’s precision tip section enables minute angler input and the kind of sensitivity required to ascend the podium. Further, BEARING DOWN is an extremely powerful choice when fishing downhill in deep reservoirs.</v>
       </c>
+      <c r="AH39" t="str">
+        <v/>
+      </c>
+      <c r="AI39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -5058,6 +5244,12 @@
       <c r="AG40" t="str">
         <v>The MEDUSA finesse spinning rod is a bottom-contact special with a highly sensitive solid tip and deep wellspring of lifting power to secure hard-won bites. Perfect for sparse cover approaches using light rigs, deep water drop-shotting, no-sinker rigs and long-distance searches with light plugs, MEDUSA’s solid tip yields invitingly to short bites for new hooking opportunities. Anchored by a deceptively strong butt section, X10 blanks deliver decisive hooksets and sure control throughout the fight. MEDUSA is a long-distance and deep-approach model equipped with a solid tip to deliver delicate sensitivity and convert light bites to conquer the toughest fields.</v>
       </c>
+      <c r="AH40" t="str">
+        <v/>
+      </c>
+      <c r="AI40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -5159,6 +5351,12 @@
       <c r="AG41" t="str">
         <v>The SWAMP SURVIVOR is a power-playing frog and swimbait model designed for heavy vegetation areas. The X10 displays high shaft rigidity and outstanding maneuverability. In the frog game, this translates into devastatingly quick and powerful hooksets and the kind of relentless power that can overcome the struggles of deep-cover monsters. In open water around weed edges, standing timber, and other cover, the SURVIVOR is a perfect choice for big baits and swimbaits, displaying ample power to keep hard-won bites free of entanglement. Finished with double-footed guides, SWAMP SURVIVOR is fully armed for versatile power games.</v>
       </c>
+      <c r="AH41" t="str">
+        <v/>
+      </c>
+      <c r="AI41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -5260,6 +5458,12 @@
       <c r="AG42" t="str">
         <v>The JABBERWOCK, once the core of the Destroyer's mid-weight versatile rods, has been reborn with X10 blank technology for the modern era.  Ideally suited for aggressive, fast-moving tactics with the VISION ONETEN series, DEEP-X series, vibrations, spinnerbaits, and bladed jigs, as well as long distance games with medium to large topwater plugs such as the I-WING, angler presentations can be controlled delicately or boldly at long distances.  JABBERWOCK exhibits a sharp, fast-taper design that contributes to high sensitivity at low loads. At high loads, the bend curve deepens, shifting to a regular taper to absorb surging targets and quick load-changes. The JABBERWOCK, once the benchmark for versatility, has reawakened as a key player in the Orochi X10 series.</v>
       </c>
+      <c r="AH42" t="str">
+        <v/>
+      </c>
+      <c r="AI42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -5361,6 +5565,12 @@
       <c r="AG43" t="str">
         <v>Based on the renowned ELSEIL, the original spirit has been reimagined with X10 technology to provide even greater application range. The X10’s superior dampening performance reduces the axial shake so often experienced in longer shafts, refining the blank’s feedback to the angler, and reducing fatigue. The SUPER ELSEIL’s high-tension carbon tip and medium-fast taper is perfect for fast-moving lures, no-sinker soft baits and lightweight rigs. Crisp shaft performance is a welcome ally when fishing spinnerbaits, jerkbaits or reaction baits in and around weed bottom areas, providing the sharpness necessary to cut free of weeds and trigger the bite.Under high loads, the blank bends deep into its strong mid-section for sure control. The SUPER ELSEIL brings sharp versatility to the X10 series.</v>
       </c>
+      <c r="AH43" t="str">
+        <v/>
+      </c>
+      <c r="AI43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -5462,6 +5672,12 @@
       <c r="AG44" t="str">
         <v>The KIRISAME BAIT FINESSE is a long-distance finesse special. Equipped with a Megabass original solid tip, the blank exhibits the willing “give” necessary to trick finicky feeders grown wise to line tension. The X10’s taut belly section quickly converts angler energy into sure hooksets, while the X10’s organic fiber taps into a tenacious strength that can pull fighting fish away from structure. The KIRISAME is a confidence-inspiring bait finesse rod with reach and agility, enabling anglers to make long, nimble casts from the shoreline.</v>
       </c>
+      <c r="AH44" t="str">
+        <v/>
+      </c>
+      <c r="AI44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -5563,6 +5779,12 @@
       <c r="AG45" t="str">
         <v>The YAMAKAGASHI is a multi-faceted rod that brings lightweight versatility to any location. The X10's supple, dynamic blanks allow anglers to utilize such varied approaches as no-sinker and jig-head rigs, drop-shotting, and twitching light topwater plugs and shads. The X10 organic fiber’s dampening properties reduces unwanted blank-shake, allowing anglers to perform crisp and rhythmic rod work that falls into an easy cadence. The X10's high maneuverability and precision angler feel allow minute lure control for precision approaches. The highly responsive YAMAKAGASHI is an extremely-versatile spinning model with outsized power and control.</v>
       </c>
+      <c r="AH45" t="str">
+        <v/>
+      </c>
+      <c r="AI45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -5664,6 +5886,12 @@
       <c r="AG46" t="str">
         <v>The MEDUSA finesse spinning rod is a bottom-contact special with a highly sensitive solid tip and deep wellspring of lifting power to secure hard-won bites. Perfect for sparse cover approaches using light rigs, deep water drop-shotting, no-sinker rigs and long-distance searches with light plugs, MEDUSA’s solid tip yields invitingly to short bites for new hooking opportunities. Anchored by a deceptively strong butt section, X10 blanks deliver decisive hooksets and sure control throughout the fight. MEDUSA is a long-distance and deep-approach model equipped with a solid tip to deliver delicate sensitivity and convert light bites to conquer the toughest fields.</v>
       </c>
+      <c r="AH46" t="str">
+        <v/>
+      </c>
+      <c r="AI46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -5765,6 +5993,12 @@
       <c r="AG47" t="str">
         <v>The DESTRUCTION 66 is a compact powerhouse built for highly technical big bait games. Armed with double-footed guides, the X10 blank produces superior torque for strong shaft performance that does not retreat under load. Delivering quick, decisive hooksets that can penetrate the thick jaws of monsters, the deeply powerful shaft can withstand powerful surges and maintain control throughout the fight.  Demonstrating excellent controllability of 2oz.-class baits such as the i-SLIDE 187R and MEGADOG-X, the DESTRUCTION 66 is comfortable handling large swimbaits, heavyweight bladed jigs and spinnerbaits day in and day out. Also adept at close-quarters frogging, the compact shaft enables pinpoint cast and control to maximize the productivity of small, open water pockets in dense cover.</v>
       </c>
+      <c r="AH47" t="str">
+        <v/>
+      </c>
+      <c r="AI47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -5866,6 +6100,12 @@
       <c r="AG48" t="str">
         <v>The DESTRUCTION 66 is a compact powerhouse built for highly technical big bait games. Armed with double-footed guides, the X10 blank produces superior torque for strong shaft performance that does not retreat under load. Delivering quick, decisive hooksets that can penetrate the thick jaws of monsters, the deeply powerful shaft can withstand powerful surges and maintain control throughout the fight. Demonstrating excellent controllability of 2oz.-class baits such as the i-SLIDE 187R and MEGADOG-X, the DESTRUCTION 66 is comfortable handling large swimbaits, heavyweight bladed jigs and spinnerbaits day in and day out. Also adept at close-quarters frogging, the compact shaft enables pinpoint cast and control to maximize the productivity of small, open water pockets in dense cover.</v>
       </c>
+      <c r="AH48" t="str">
+        <v/>
+      </c>
+      <c r="AI48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -5967,6 +6207,12 @@
       <c r="AG49" t="str">
         <v>HIBAKARI dials up the versatility of finesse spinning, enabling long distance castability to send lightweight rigs to the realms of target fish, taking over in high-wind situations that often relegate baitcasting reels to the sidelines.  X10 organic fiber offers excellent vibration control to limit axial shaft shake and delivers surprising lifting power to overturn the conventional wisdom of lightweight rods. HIBAKARI is best suited to distance fishing using a variety of lightweight rigs over a wide area and is also adept at finesse plugging with small minnow baits and tiny crankbaits.</v>
       </c>
+      <c r="AH49" t="str">
+        <v/>
+      </c>
+      <c r="AI49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -6068,6 +6314,12 @@
       <c r="AG50" t="str">
         <v>The JADE PYTHON, the renowned high-power spinning model, has been revitalized with X10 organic fiber. The X10 material reinforces the rigidity of the butt section, which allows anglers to attack tangled timber and intricate bushes with lightweight rigs. In addition to its high-torque characteristics, the new JADE PYTHON benefits from the X10’s lightweight construction for nimble handling and integrated feel. With the kind of sensitivity that enables the angler to trace bottom composition with clarity, JADE PYTHON stands out in subtle transition areas, sparse cover and complicated structure where navigations happens by feel. JADE PYTHON also excels in long distance applications with minnows, shad, and small vibrations in windy situations where baitcasting equipment often under-delivers. A masterpiece of high-torque spinning is reborn for modern waters.</v>
       </c>
+      <c r="AH50" t="str">
+        <v/>
+      </c>
+      <c r="AI50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -6169,6 +6421,12 @@
       <c r="AG51" t="str">
         <v>The CLIFFHANGER, a bait finesse ally trusted by discerning specialists, has been further refined with X10 blank technology. These extra-dimensional blanks, created together with Hirokazu Kawabe, a leading professional tournament angler, deliver intuitive and precise operability and extremely high cast accuracy, virtually eliminating any interference between angler and target. Megabass's unique guide setting, which employs the smallest diameter micro guides in the X10 lineup, contributes to its ultra-sensitive characteristics, transmitting tentative short bites with brilliant clarity. It can be used not only with small baits such as mini cranks and neko rigs, but also with finesse shad plugs. This is a competition-spec model built to take the fight to the forefront of bait finesse.</v>
       </c>
+      <c r="AH51" t="str">
+        <v/>
+      </c>
+      <c r="AI51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -6270,6 +6528,12 @@
       <c r="AG52" t="str">
         <v>HIBAKARI dials up the versatility of finesse spinning, enabling long distance castability to send lightweight rigs to the realms of target fish, taking over in high-wind situations that often relegate baitcasting reels to the sidelines. X10 organic fiber offers excellent vibration control to limit axial shaft shake and delivers surprising lifting power to overturn the conventional wisdom of lightweight rods. HIBAKARI is best suited to distance fishing using a variety of lightweight rigs over a wide area and is also adept at finesse plugging with small minnow baits and tiny crankbaits.</v>
       </c>
+      <c r="AH52" t="str">
+        <v/>
+      </c>
+      <c r="AI52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -6371,6 +6635,12 @@
       <c r="AG53" t="str">
         <v>Drawing inspiration from the Destroyer® BANDERSNATCH, the F5-70XT is designed to dominate the power fishing game with medium to heavyweight lures. Re-engineered with X10 blank material to bring its updated specs to modern waters, BANDERSNATCH is made for anglers who challenge big fish with aggressive deep cranking, larger topwaters, swimbaiting, and slow-rolling heavy spinner baits. The X10's lightweight and torquey characteristics deliver an intuitive feel with a high power-to-weight ratio, delivering the aggressiveness required to cover fish with 3/8oz. jigs and Texas rigs. BANDERSNATCH is a versatile medium-heavy challenger, built for monster approaches.</v>
       </c>
+      <c r="AH53" t="str">
+        <v/>
+      </c>
+      <c r="AI53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -6472,6 +6742,12 @@
       <c r="AG54" t="str">
         <v>The BUSHADDER is a quick-strike jig shaft that fearlessly sends jigs and Texas rigs into impregnable brush areas, dense laydowns, and labyrinthine structure.  This is a precision American cover attack model born of Megabass’ tournament-tested expertise, delivering “tip-up” balance that naturally supports pendulum casts, the sensitivity to paint a vivid picture of bottom contours and composition, and the intuitive control that comes with integrated equipment.  X10 blanks offer the kind of relentless performance to deliver hammer-quick hooksets and tap a wellspring of power to haul targets from complex cover situations without sacrificing the initiative. This is an aggressively tuned, pure competition-spec jig game special.</v>
       </c>
+      <c r="AH54" t="str">
+        <v/>
+      </c>
+      <c r="AI54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -6573,6 +6849,12 @@
       <c r="AG55" t="str">
         <v>Drawing inspiration from the Destroyer® BANDERSNATCH, the F5-70XT is designed to dominate the power fishing game with medium to heavyweight lures. Re-engineered with X10 blank material to bring its updated specs to modern waters, BANDERSNATCH is made for anglers who challenge big fish with aggressive deep cranking, larger topwaters, swimbaiting, and slow-rolling heavy spinner baits.  The X10's lightweight and torquey characteristics deliver an intuitive feel with a high power-to-weight ratio, delivering the aggressiveness required to cover fish with 3/8oz. jigs and Texas rigs. BANDERSNATCH is a versatile medium-heavy challenger, built for monster approaches.</v>
       </c>
+      <c r="AH55" t="str">
+        <v/>
+      </c>
+      <c r="AI55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -6674,6 +6956,12 @@
       <c r="AG56" t="str">
         <v>Like its namesake, ANACONDA is built to overwhelm record-class targets with relentless torque and power. Ideally suited for punching and frogging in super heavy cover areas, long distance games with big swimbaits, and approaches with magnum baits up to 7 oz., ANACONDA is ready to take the fight to bass fishing destinations around the world. ANACONDA is a full-contact, extra-heavy rod that sends big baits to the farthest reaches with ease, boldly challenging monsters used to lurking just out of reach. X10 blanks are strong and lightweight, enabling superb balance to reduce angler fatigue on the frontlines.</v>
       </c>
+      <c r="AH56" t="str">
+        <v/>
+      </c>
+      <c r="AI56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -6775,6 +7063,12 @@
       <c r="AG57" t="str">
         <v>The RAPID VIPER is built for fast-moving medium to small sized lures and light Texas rigs, empowering anglers with a sense of featherweight maneuverability. The X10's ultra-lightweight blanks transmit a perfect balance of tension and forgiveness and generate outsized castability to expand the precision attack range of lightweight lures. The essence of the RATTLE VIPER lies in the union of light cranking and light softbait games within a single rod. Its dynamic performance makes it a preferred tool for bank fishing, where selection is often restricted by mobility.</v>
       </c>
+      <c r="AH57" t="str">
+        <v/>
+      </c>
+      <c r="AI57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -6876,6 +7170,12 @@
       <c r="AG58" t="str">
         <v>The RAPID VIPER is built for fast-moving medium to small sized lures and light Texas rigs, empowering anglers with a sense of featherweight maneuverability. The X10's ultra-lightweight blanks transmit a perfect balance of tension and forgiveness and generate outsized castability to expand the precision attack range of lightweight lures. The essence of the RATTLE VIPER lies in the union of light cranking and light softbait games within a single rod. Its dynamic performance makes it a preferred tool for bank fishing, where selection is often restricted by mobility.</v>
       </c>
+      <c r="AH58" t="str">
+        <v/>
+      </c>
+      <c r="AI58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -6977,6 +7277,12 @@
       <c r="AG59" t="str">
         <v>Based on the renowned ELSEIL, the original spirit has been reimagined with X10 technology to provide even greater application range. The X10’s superior dampening performance reduces the axial shake so often experienced in longer shafts, refining the blank’s feedback to the angler, and reducing fatigue.  The SUPER ELSEIL’s high-tension carbon tip and medium-fast taper is perfect for fast-moving lures, no-sinker soft baits and lightweight rigs. Crisp shaft performance is a welcome ally when fishing spinnerbaits, jerkbaits or reaction baits in and around weed bottom areas, providing the sharpness necessary to cut free of weeds and trigger the bite. Under high loads, the blank bends deep into its strong mid-section for sure control. The SUPER ELSEIL brings sharp versatility to the X10 series.</v>
       </c>
+      <c r="AH59" t="str">
+        <v/>
+      </c>
+      <c r="AI59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -7078,6 +7384,12 @@
       <c r="AG60" t="str">
         <v>The YAMAKAGASHI is a multi-faceted rod that brings lightweight versatility to any location. The X10's supple, dynamic blanks allow anglers to utilize such varied approaches as no-sinker and jig-head rigs, drop-shotting, and twitching light topwater plugs and shads. The X10 organic fiber’s dampening properties reduces unwanted blank-shake, allowing anglers to perform crisp and rhythmic rod work that falls into an easy cadence. The X10's high maneuverability and precision angler feel allow minute lure control for precision approaches. The highly responsive YAMAKAGASHI is an extremely-versatile spinning model with outsized power and control.</v>
       </c>
+      <c r="AH60" t="str">
+        <v/>
+      </c>
+      <c r="AI60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -7179,6 +7491,12 @@
       <c r="AG61" t="str">
         <v>A legendary heavyweight versatile shaft, DIABLO faithfully lives up to its legacy. Its distinctively supple titanium-powered elasticity effortlessly handles contact baits like bladed jigs, jigs, and light Texas rigs in shallow cover. This unique rod feel, unmatched by pure carbon rods, blends moderate flexibility with outstanding sensitivity—signature characteristics of the DIABLO lineage. Thanks to its MX40 Super Titanium Hybrid Shaft, it offers ample elasticity during casting and lure control, ensuring unmatched comfort and performance. Whether you’re throwing large crankbaits, spinnerbaits, or swimbaits, DIABLO performs across a wide range of fast-moving tactics. The smooth, uninterrupted bend curve provides exceptional torque that exceeds its class, allowing you to secure bites without prematurely telegraphing line tension to the target. The newest iteration of the acclaimed DIABLO continues to push the boundaries of heavy-action versatility.</v>
       </c>
+      <c r="AH61" t="str">
+        <v/>
+      </c>
+      <c r="AI61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -7280,6 +7598,12 @@
       <c r="AG62" t="str">
         <v>LYCAON MS is a dedicated model for mid-strolling with lightweight jigheads. It is specially tuned for the unique tempo of rod work required to generate the desired rolling swim action, thanks to a taper that makes it easy to create and maintain rhythmic slack in the line. Its guide sizing and layout are meticulously designed to generate continuous slack-line movement—essential for technical mid-strolling techniques. The new Slant Bridge system enables stress-free, technical casting from a wide range of angles, allowing rigs to be delivered deep beneath overhangs or into complex structure. During mid-strolling, the Slant Bridge also functions as a perfect counterbalance, making continuous tip-up rod manipulation easier. In advanced finesse spinning games, it supports smooth operation with heightened control. A long-awaited model crafted for expert anglers who build their game around mid-strolling.</v>
       </c>
+      <c r="AH62" t="str">
+        <v/>
+      </c>
+      <c r="AI62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -7381,6 +7705,12 @@
       <c r="AG63" t="str">
         <v>Named after the legendary lightning-splitting sword, LAIKIRI is the flagship spinning model of the EVOLUZION series. Engineered for superior long-casting performance with light rigs and 1/20z class shad and minnow plugs, its titanium-reinforced blank surpasses traditional spinning rods in strength, rigidity, resilience, and responsiveness. Ergonomically balanced by the Slant Bridge grip, this 7’3” rod handles smoothly with compact movements, enabling anglers to swiftly cover vast water expanses without fatigue. The light tip allows for nimble reaction, turning this long rod into a precision strike in open terrain. The LAIKIRI introduces a new standard for power spinning rods, offering lightning-fast responsiveness, extraordinary distance, and dominating strength. With LAIKIRI, a new chapter in long-distance power spinning begins.</v>
       </c>
+      <c r="AH63" t="str">
+        <v/>
+      </c>
+      <c r="AI63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -7482,6 +7812,12 @@
       <c r="AG64" t="str">
         <v>The legendary topwater rod EXPADA—a standout in the Evoluzion series—has been upgraded with the MX40 Super Titanium Hybrid Shaft, enhancing its signature spring-back feel. It amplifies the dynamic performance of surface lures, elevating the dog-walking of the DOG-X series and the stationary twitch of the POPX into more expressive, lively actions. This special blank allows anyone to animate surface plugs with ease and vitality. It also delivers overwhelming long-distance castability, far surpassing the conventional range of ultralight action rods. The titanium shaft enables precise manipulation of distant plugs and supports deep, sweeping hooksets that ensure reliable hookups even at range. Delicate enough to handle finesse plugs like the SIGLETT and KARASHI series, EXPADA is an indispensable go-to for long-distance topwater and bait finesse games.</v>
       </c>
+      <c r="AH64" t="str">
+        <v/>
+      </c>
+      <c r="AI64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -7583,6 +7919,12 @@
       <c r="AG65" t="str">
         <v>DAMIEN is built for precision-heavy games, such as technical frog fishing and heavyweight lures requiring intensive angler input and control. Its triple-six configuration embodies a new golden ratio—a power spec designed purely for dominant heavy action. The 6’6” length improves rod handling and casting accuracy, enabling pinpoint casts deep into thick cover. Its F6 power class gives it the muscle to dissect complex structure and accurately probe tight zones with baits like the MAGDRAFT series, i-SLIDE 187R, and i-WING135, where cast precision is crucial. The MX40 Super Titanium Hybrid Shaft brings surprising lightness and responsive control to even the heaviest lures, enhancing the fine-tuned performance needed to trigger bites. Its abundant torque overpowers even the most determined fighters. Despite its shorter length, this 6’6” super titanium shaft outcasts many 7’ carbon rods, enabling seamless, long-distance casts with minimal fatigue. Designed for expert anglers who demand absolute control over big baits and close-quarter casting, DAMIEN offers intuitive handling and exceptional accuracy—a new breed of high-powered performance.</v>
       </c>
+      <c r="AH65" t="str">
+        <v/>
+      </c>
+      <c r="AI65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -7684,6 +8026,12 @@
       <c r="AG66" t="str">
         <v>NORTH WALL is a full-contact bait finesse special, built to deliver long-distance cover approaches with lightweight rigs. Its ultra-sensitive tip pairs with a deeply loading taper to provide smooth, stress-free finesse performance. The 6’8” shaft—crafted from MX40 Super Titanium Hybrid material—launches light rigs with impressive distances, all while maintaining the kind of intuitive feedback and control that makes you forget how far out you’re fishing. Despite its F2.1/2 power rating, NORTH WALL packs a deceptively powerful butt section and high torque that only increases with bend—giving you the strength to pull unexpected giants from heavy cover and guide them decisively to the net. This is a finesse-versatile rod that fully expresses the dynamic potential of super titanium shaft construction.</v>
       </c>
+      <c r="AH66" t="str">
+        <v/>
+      </c>
+      <c r="AI66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -7785,6 +8133,12 @@
       <c r="AG67" t="str">
         <v>The TSUBAMEGAESHI is a versatile, long-distance spinning rod featuring a smooth, masterfully engineered variable taper that transitions seamlessly from medium-fast to regular action. Built for finesse approaches like drop-shotting, Neko, and wacky rigs, this rod offers unmatched adaptability across varied conditions and extended ranges. Its sensitive tip captures even the faintest short strikes, while the MX40 Super Titanium Hybrid shaft resilience feels as if it strengthens progressively under load, ensuring sweeping hooksets deliver deep hook penetration. Combining responsive maneuverability with the robust backbone of Super Titanium, this rod equips anglers to aggressively dissect expansive water, establishing itself as an essential long-distance finesse tool for challenging conditions.</v>
       </c>
+      <c r="AH67" t="str">
+        <v/>
+      </c>
+      <c r="AI67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -7886,6 +8240,12 @@
       <c r="AG68" t="str">
         <v>LYCAON LD specializes in comfortable, long-distance approaches with lightweight rigs. Its 6’10” MX40 Super Titanium Hybrid Shaft excels at broad, multi-purpose softbait presentations, while also offering high-level responsiveness for finesse plugs such as the SIGLETT, KARASHI, and SHADING-X R 55 series. The rod’s Super Titanium fibers deliver exceptional elasticity under load, effortlessly setting hooks into wary trophy fish and generating surprising torque to confidently win extended battles. A refined evolution of the classic Destroyer spinning model LYCAON, this super titanium-enhanced variant sets a new benchmark for finesse versatility.</v>
       </c>
+      <c r="AH68" t="str">
+        <v/>
+      </c>
+      <c r="AI68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -7987,6 +8347,12 @@
       <c r="AG69" t="str">
         <v>This is the evolved version of CLIFFHANGER, a Japanese classic in the world of bait finesse rods. In bait finesse games using small rubber jigs and light rigs, its uniquely arranged micro guide system delivers pinpoint accuracy for targeting tight spots with precision. It consistently translates delicate bites and subtle changes in line tension during the fall into clear feedback, enabling a highly detailed and responsive approach. Equipped with the ergonomically enhanced Slant Bridge (PAT.P.), it expands wrist mobility and allows for fluid, high-freedom casting techniques—whether backhand, underhand, or skipping—supporting confident casts from any position or angle. Its supple midsection excels in small plug applications like the SHADING-X R and NANAHAN series. The result is a remarkably nimble and comfortable light-action game experience with high control and sensitivity.</v>
       </c>
+      <c r="AH69" t="str">
+        <v/>
+      </c>
+      <c r="AI69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -8088,6 +8454,12 @@
       <c r="AG70" t="str">
         <v>The HEDGEHOG SYRINGE merges the iconic solid-tip sensitivity of the historic HEDGEHOG series with the cutting-edge titanium shaft technology of EVOLUZION. Its solid tip is optimized to reliably detect and trigger bites during the most demanding short-strike windows—ideal for small rubber jigs, dropshots, and neko rigs that would otherwise be too light for a rod of this power. The rod’s high-density MX40 and super titanium fibers visibly reinforce the belly and butt sections, delivering crisp, reinforced tension for instantaneous hooksets and the kind of deep, powerful flex that absorbs the fight of relentless big bass—resulting in richly controlled torque. Unlike conventional solid tip rods made of pure carbon, the titanium’s spring back elasticity allows effortless long casts even with lightweight rigs, offering both comfort and control in your cast.</v>
       </c>
+      <c r="AH70" t="str">
+        <v/>
+      </c>
+      <c r="AI70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -8189,6 +8561,12 @@
       <c r="AG71" t="str">
         <v>The ultimate medium-light, fast-moving rod masterpiece, SUPER GRIFFON, fully inherits the legacy of its storied predecessors, setting the definitive standard for light cranking rods. True to its name, the new COMPETIZIONE is specifically crafted for competitive anglers seeking an edge in tournament scenarios involving lightweight, fast-moving presentations. Its precisely balanced Super Titanium belly section, characterized by the ideal tension between stiffness and resilience, consistently delivers comfortable, accurate long-distance casts and sweeping hooksets with lightweight plugs. The distinctive variable taper blank captures reaction bites effortlessly, ensuring secure hookups. The MX40 Super Titanium Hybrid Shaft offers torque performance beyond its stated power rating, enhancing lure control and superior maneuverability around cover during intense battles. Renowned for its agile responsiveness, the SUPER GRIFFON excels at managing a broad range of lures, including vibration baits, compact spinnerbaits, topwater plugs, and jerkbaits, all with unparalleled versatility and precision. Without question, SUPER GRIFFON remains the pinnacle of medium-light rod performance.</v>
       </c>
+      <c r="AH71" t="str">
+        <v/>
+      </c>
+      <c r="AI71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -8290,6 +8668,12 @@
       <c r="AG72" t="str">
         <v>A refined second-coming of the original double-helix DTi ELSEIL, this latest model adopts a higher taper design and comprehensive upgrades, fully prepared to tackle a wider variety of conditions. In addition to ELSEIL’s renowned multi-performance capabilities, it now delivers crisper and more responsive lure control. The newly designed high-taper Super Titanium shaft reduces unwanted blank shake, enhancing sharpness, vibration damping, and sensitivity, thus achieving unparalleled underwater clarity and enabling next-level fast-moving lure presentations. Furthermore, the ELSEIL now expands into finesse-oriented territories previously left uncharted by its predecessors, such as high-density softbaits and light-jigs. This new-era ELSEIL delivers crisp rod work that belies its length and introduces a new feel—simultaneously delicate, powerful, and sharp—far beyond longer conventional medium-heavy rods.</v>
       </c>
+      <c r="AH72" t="str">
+        <v/>
+      </c>
+      <c r="AI72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -8391,6 +8775,12 @@
       <c r="AG73" t="str">
         <v>The DESTRUCTION embodies otherworldly power and absolute angler control. Its high-taper MX40 Super Titanium Hybrid Shaft produces massive torque, bringing remarkable stability to big-bait techniques, deep cranking, and heavy spinnerbait presentations. The exceptional vibration transmission properties of Super Titanium significantly enhance bite detection sensitivity, ensuring anglers sense even the lightest strikes in fast-moving games. Its advanced shape-memory titanium structure increases rigidity and shaft tension under load, providing an unparalleled direct connection during punching and swim-jig tactics, where instantaneous transmission and feedback are critical. Built to secure lightning-fast hooksets and muscle big bass out of heavy cover, its overwhelming torque empowers the angler to land monsters with unmatched authority. The DESTRUCTION is the ultimate hyper-performance model, purpose-built for extreme anglers seeking dominating power and precision.</v>
       </c>
+      <c r="AH73" t="str">
+        <v/>
+      </c>
+      <c r="AI73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -8492,6 +8882,12 @@
       <c r="AG74" t="str">
         <v>Praised across competitive scenes in Japan, the U.S., and worldwide, the acclaimed jerkbait rod masterpiece, ONETEN STICK, now debuts in the Evoluzion lineup—fully armed with a Super Titanium shaft and the latest Slant Bridge. By meticulously analyzing every ergonomic nuance of jerkbait techniques—from standard tip-down jerks to controlled “pops” of the rod—this specialized shaft delivers superior performance tailored specifically for jerkbait applications, ensuring exceptional comfort and ease of use. The MX40 Super Titanium Hybrid Shaft, characterized by its unique spring-like elasticity, significantly increases the darting distance of ONETEN actions, while simultaneously enhancing the blank’s rapid spring-back recovery rate to create direct, intuitive lure control. This specialized rod is engineered to give anglers absolute mastery over jerkbait presentations.</v>
       </c>
+      <c r="AH74" t="str">
+        <v/>
+      </c>
+      <c r="AI74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -8593,6 +8989,12 @@
       <c r="AG75" t="str">
         <v>The legendary HEDGEHOG STINGER, now enhanced with Super Titanium, redefines cover-finesse spinning tactics. Merging a specialized solid-tip developed by the HEDGEHOG series with the robust titanium blank of Evoluzion, this rod offers unmatched strength and sensitivity for fishing tight cover. Designed to excel in situations where finesse is necessary, but retreat is not an option—whether targeting thick timber, tangled bushes, or laydowns—using its intense torque to wrench big fish from cover with overwhelming force. Its solid tip detects subtle bites with stunning clarity and the MX40 Super Titanium Hybrid shaft ensures quick, dominating hooksets. The HEDGEHOG STINGER’s refined strength, now elevated by titanium construction, marks a significant evolution in cover-finesse spinning, earning its place as a true “Game Changer.”</v>
       </c>
+      <c r="AH75" t="str">
+        <v/>
+      </c>
+      <c r="AI75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -8694,6 +9096,12 @@
       <c r="AG76" t="str">
         <v>Within the GREAT HUNTING series, the KAMUI EGOISTA features the longest shaft and boasts the toughest specs. This is a specialized monster hunting shaft designed to target large trout such as salmon masu and whitespotted char. Using heavy lures to search the main currents, KAMUI EGOISTA senses subtle contact and soft bites, while having the power reliably land targets despite the pressure of current and power of big trout.  Of course, it’s not just about power. The KAMUI EGOISTA features a lightweight and well-balanced design based on human ergonomics, a unique lightweight guide setting, and is packed with state-of-the-art Megabass technologies.</v>
       </c>
+      <c r="AH76" t="str">
+        <v/>
+      </c>
+      <c r="AI76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -8795,6 +9203,12 @@
       <c r="AG77" t="str">
         <v>The BLACK POOL features a high-performance shaft that makes it possible to attack the masu salmon and satsuki masu of rivers, and the rainbow trout and brown trout of lakes—all with one shaft. The 7’7” length makes it very adaptable to both wading and boat use and is comfortably suited for the accuracy required for long-distance approaches. The crisp, flexible blank delivers ultra-high sensitivity to allow for pinpoint minnow games in rivers and backwaters, as well as highly-accurate tracking while spoon fishing in lakes. This shaft will respond to wide-ranging strategies of anglers with surprising precision.</v>
       </c>
+      <c r="AH77" t="str">
+        <v/>
+      </c>
+      <c r="AI77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -8896,6 +9310,12 @@
       <c r="AG78" t="str">
         <v>While retaining the same power and action, the EGOISTA features an additional 9-inch reach over the BLACK POOL. The 8’4” length is a powerful weapon when long-distance casting in lakes and wide rivers, as well as when reeling in large trout around bushes and breakwaters.  These thin yet sharp and powerful blanks are highly suited for a variety of approaches, from surface drifting with floating minnows, to the midrange, to spooning during the cold seasons. Please experience trophy trout hunting performance for yourself!</v>
       </c>
+      <c r="AH78" t="str">
+        <v/>
+      </c>
+      <c r="AI78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -8998,7 +9418,10 @@
         <v>This is Yuki Ito's special game rod for targeting wide-eyed amago, also known as "tanabira," which roam the currents of Kiso, Shinshu. Tailor-made by MPW (Megabass Performance Works) to Ito’s exacting specifications, the GHBF511-4L features super high-density Ivory Rosewood for its "precise lure management," "continuous high-speed snap work," and "instantaneous bite detection (hand sensitivity)" to target and capture the elusive tanabira. The rod is designed with a tip-down balance for a twitch-heavy technique and is set to larger and stronger stream specifications. Standing in the current that nurtures the tanabira, the rod comfortably enables twitching of heavy sinking minnows such as the GH65 day after day. It is specially geared for reaction fishing to trigger bites in tight windows, deliver lightning hooksets, and unleash the power needed to pull trophies from the strong current. The torquey shaft of the "Tanabira Special" delivers a wider power range and precision control to allow anglers to approach diverse waters with dynamic confidence.</v>
       </c>
       <c r="AH79" t="str">
-        <v>Handle Type : SHORT</v>
+        <v>Other.1: Handle Type : SHORT</v>
+      </c>
+      <c r="AI79" t="str">
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -9102,7 +9525,10 @@
         <v>GHBF53-3UL is a versatile model at the core of the HUNTSMAN series, designed with a stronger power matrix than the GHBF48-3UL to cover faster currents and larger fish. Bringing high controllability to heavier sinking minnows, it performs comfortable continuous twitching in strong currents even with lures that have a lot of pulling resistance. The intuitive control and ergonomic fit become an extension of the arm, enabling active casts with a snap of the wrist. A strong butt section with high torque handles not only big native trout, but also rockfish over 40 cm. With stress-free ergonomics, smooth castability, and the capability to bring a wider range of lure weights to life, the GHBF53-3UL is built for repeated backcountry excursions.</v>
       </c>
       <c r="AH80" t="str">
-        <v>Handle Type : SHORT</v>
+        <v>Other.1: Handle Type : SHORT</v>
+      </c>
+      <c r="AI80" t="str">
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -9206,7 +9632,10 @@
         <v>GHBF60-4L is a long-distance model designed to bring the fight not only to headwaters, but also larger streams. The high-density wood and longer grip shift the rod’s balance point to a tip-up posture, enabling sharp upward twitch work in shallow areas and comfortable wrist casts. The unique rifle-back form of the grip encourages a fighting stance that allows the angler to lock his/her wrist to the end of the handle when interacting with monster fish. Delicate fast tip action is the result of the pursuit of precise lure control. The belly and butt sections, designed with a unique variable matrix to produce high torque, provide the power to pull 60 cm class rainbows from strong currents. This is a power-playing model for native trout games, tested and released after repeated encounters with large silvered amago, enoha, wild rainbows and browns.</v>
       </c>
       <c r="AH81" t="str">
-        <v>Handle Type : MIDDLE</v>
+        <v>Other.1: Handle Type : MIDDLE</v>
+      </c>
+      <c r="AI81" t="str">
+        <v/>
       </c>
     </row>
     <row r="82">
@@ -9310,7 +9739,10 @@
         <v>The GHBF48-3UL is a compact model for remote headwaters that often require climbing to access. The HUNTSMAN's modern shaft feels like an extension of your arm, allowing you to comfortably deploy lure offerings from all positions and angles. Its compact castability enables aggressive approaches to key areas even when it is difficult to secure a foothold or traditional backswing space. The butt section, displaying a tautness that is unimaginable from such a slim blank, provides the crisp backbone for twitching, while the high-tension belly section precisely controls the bite and fight of mountain stream fish. The rod has a powerful lifting ability that exceeds the standard of an ultralight rod, allowing anglers to tackle upper-class fish from high footholds with confidence.</v>
       </c>
       <c r="AH82" t="str">
-        <v>Handle Type : SHORT</v>
+        <v>Other.1: Handle Type : SHORT</v>
+      </c>
+      <c r="AI82" t="str">
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -9413,6 +9845,12 @@
       <c r="AG83" t="str">
         <v>The F4.1/2-71X THE DARK SLEEPER is the key to the stubborn lock of dormant deep fish, enabling precision presentation of light Texas rigs, bottom-tracing swimbaits, bladed swim jigs and worms. The exquisite tension of the 7’ blank is tuned for that improbable balance of sensitive rod work and overwhelming lifting power, swiftly translating whip-quick hooksets into culls from the deep. 5-D GRAPHITE SYSTEM transfers load with studied ease, allowing THE DARK SLEEPER’s fast taper design to draw the fight into the blank’s powerful mid-section to dominate surging targets. Not limited solely to high-precision deep approaches, the F4.1/2-71X also demonstrates excellent light Texas and small jig pitching performance amongst light cover.</v>
       </c>
+      <c r="AH83" t="str">
+        <v/>
+      </c>
+      <c r="AI83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -9514,6 +9952,12 @@
       <c r="AG84" t="str">
         <v>Drawing its inspiration from the F3-610XS, one of the most successful spinning models in Megabass' storied history, the F3-611XS LANDSAT applies the advances of 5-D Graphite to the finesse tool of choice for serious anglers the world over. Developed for applications like drop-shotting and neko rigging, the LANDSAT's sensitivity and control provides a birds-eye view of the battle unfolding in the depths, delivering insight that can separate one bite from the next. The 5-D GRAPHITE SYSTEM's refined patterning and layering process results in a lighter and more powerful rod that bends with unimaginable smoothness, encouraging intuitive control. The LANDSAT is a dexterous finesse companion true to its roots, sure to delight diehard Megabass connoisseurs and first-time converts alike.</v>
       </c>
+      <c r="AH84" t="str">
+        <v/>
+      </c>
+      <c r="AI84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -9615,6 +10059,12 @@
       <c r="AG85" t="str">
         <v>The F7-70X TEQUILA OF BACCARAC is an extra-heavy powered regular taper rod ideally suited to the challenges of versatile monster hunting. With the 5-D GRAPHITE SYSTEM’s high-tension and high-torque power coursing through its veins, the F7-70X displays a tenacious ability to control swimbaits, big baits and larger frogs like the BIG GABOT in and around heavy cover. Impeccably balanced, resolutely powerful and surprisingly versatile, the TEQUILA OF BACCARAC is an unparalleled monster hunter.</v>
       </c>
+      <c r="AH85" t="str">
+        <v/>
+      </c>
+      <c r="AI85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -9716,6 +10166,12 @@
       <c r="AG86" t="str">
         <v>The F1.1/2-72XS BABY PLUGGING is tuned for finesse hardbaits, leveraging 5-D Graphite to decrease unwanted blank twist and reverberation, and increase power and controllability. Ideally suited to small minnow plugs and crankbaits, the F1.1/2-72XS exhibits exquisite retrieve tension and feel, allowing for thrilling light-bite plugging games.</v>
       </c>
+      <c r="AH86" t="str">
+        <v/>
+      </c>
+      <c r="AI86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -9817,6 +10273,12 @@
       <c r="AG87" t="str">
         <v>Named in honor of the storied "X-Bites" Japanese fishing program, the F5.1/2-72X rises to the challenge of extreme conditions and unspeakably tough bites. The extra-fast taper of THE X-BITES commands bottom contact rigs in the depths with supreme confidence, delivering pinpoint feedback to heighten angler awareness and lure presentation. In addition to staple ½ and ¾oz weights, THE X-BITES is able to handle lighter Texas rigs in deeper water, adding a subtly devastating option to fill out limits on tough days. The rod’s lightweight and balanced design, coupled with intense sensitivity, delivers the kind of performance that will conquer the toughest competitions.</v>
       </c>
+      <c r="AH87" t="str">
+        <v/>
+      </c>
+      <c r="AI87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -9918,6 +10380,12 @@
       <c r="AG88" t="str">
         <v>The F4-66X CYCLONE has endured from the first Destroyer® launch, a unique distinction that serves as a reference point for iterative refinement. Harnessing the 5-D Graphite System to further the concept of compact versatility and outsize performance, the new CYCLONE is the lightest, most responsively dynamic version yet. The featherweight 6'6" shaft and perfect balance makes the rod feel a foot shorter in hand, making for confidence-inspiring controllability. From small spinnerbaits to soft stickbaits and medium-sized plugs like the POPMAX and GIANT DOG-X, the CYCLONE continues to punch above its weight class, delivering inspired control and crisp feedback. For anglers seeking to tap into Megabass’ rich DNA, the CYCLONE is a new benchmark in Yuki Ito’s angling vision.</v>
       </c>
+      <c r="AH88" t="str">
+        <v/>
+      </c>
+      <c r="AI88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -10020,7 +10488,10 @@
         <v>If you’re looking to deploy 1/16oz. ultra-light rigs with more distance, accuracy and control than ever before, the F2.1/2-77XS ZANGETSU is the answer. This deadly long-distance caster leverages the unique properties of the blank’s 5D graphite system to generate full-torque flexibility. Engineered to load deeply in the cast--even with light rigs--ZANGETSU unleashes angler energy to deploy light offerings to the farthest reaches. This unique ability is adapted from the COOKAI, a distance-defying surfcasting rod powered by a saltwater-tuned 5D graphite system. ZANGETSU’s leading-edge blanks and unique guide settings transmit the subtle motion of lures and rigs to your hand with intuitive clarity, offering excellent handling of light rigs and small shad plugs alike. Crafted with particular attention to the blank’s surface hardness, ZANGETSU delivers surprising sensitivity, securing subtle bites in harsh winter and early spring with a sure sweep hookset.</v>
       </c>
       <c r="AH89" t="str">
-        <v>オフセットハンドル</v>
+        <v>Other.1: オフセットハンドル</v>
+      </c>
+      <c r="AI89" t="str">
+        <v/>
       </c>
     </row>
     <row r="90">
@@ -10123,6 +10594,12 @@
       <c r="AG90" t="str">
         <v>The F5-70X MAD BULL comfortably corrals the hard-charging action of deep crankbaits, vibrations and medium-sized swimbaits, and subdues recklessly fighting fish with the surprising strength of its 5-D blank. Regular taper design, supercharged with the 5-D’s high-tension construction, provides a wellspring of readily available power, enabling confident angling even in mat cover pockets requiring subtle precision.</v>
       </c>
+      <c r="AH90" t="str">
+        <v/>
+      </c>
+      <c r="AI90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -10224,6 +10701,12 @@
       <c r="AG91" t="str">
         <v>A dedicated mushi, or “bug” pattern bait finesse rod, the F0st-66X SIGLETT excels in ultra-finesse topwater games. Improved solid-tip design imparts otherworldly sensitivity and feel, transmitting the exquisitely detailed minutiae of micro insect lures for precision control. Solid-tip characteristics allow for rolling casts of featherweight lures and micro-shake rod work. Under load, the blank transitions effortlessly to the mid-section to behave like a regular taper rod throughout the fight. Further, the delicate responsiveness of the solid tip captures even the lightest topwater bites, yielding instantly to allow plugs to travel deep into predator throats for sure hooking. Ideal for open water and light cover applications where spinning tackle hesitates.</v>
       </c>
+      <c r="AH91" t="str">
+        <v/>
+      </c>
+      <c r="AI91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -10325,6 +10808,12 @@
       <c r="AG92" t="str">
         <v>Finally, the HIEN finds a new raison d’être, powered by the next-generation blank process of 5-D. The unique patterning and layering process of 5-D enables variable action taper to unfold with impossible smoothness, eliminating the subtly harsh feel of taper transitions under load. Thus, the HIEN concept reemerges as the new F3-610X BAIT FINESSE, showcasing its delicate fast action tip for precision control and strong mid-section for confident power. Dialed-in to bait finesse cover approaches, long-distance shad plugging, and light cranking, the next-generation HIEN has arrived.</v>
       </c>
+      <c r="AH92" t="str">
+        <v/>
+      </c>
+      <c r="AI92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -10426,6 +10915,12 @@
       <c r="AG93" t="str">
         <v>The F6.1/2-67X TACHYON SHAFT is a Yuki Ito Builders Spec model produced in limited quantities, for one purpose and one purpose only—to deliver the fastest, hardest-hitting hookset possible. Inspired by the original Destroyer® G-AX, first developed for legendary jig angler and JB World Champion, Ide, the TACHYON SHAFT is the realization of that historic project made possible with modern technology. Harnessing the 5-D GRAPHITE SYSTEM, the TACHYON SHAFT brings the reaction speed and power of world-class jig angling within reach. In recent years, an approach using bait finesse and lighter rigs in Japan has become common, but the reaction bite produced by heavy rubber jigs and Texas rigs will always have its place in angler hearts and trophy-class diets. Experience the TACHYON SHAFT, the realization of Ito and Ide’s long-held dream in jig fishing.</v>
       </c>
+      <c r="AH93" t="str">
+        <v/>
+      </c>
+      <c r="AI93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -10527,6 +11022,12 @@
       <c r="AG94" t="str">
         <v>The legendary F5-66X, known for its dominance in Lake Biwa's North Lake and reservoirs across Japan throughout the late 1990’s, is reborn for tomorrow’s anglers. Reimagined with the latest 5D graphite system, the new F5-66X BEARING DOWN cuts through modern fields with compact outperformance. The BEARING DOWN’s bristling shaft tension distinguishes it from other high-elasticity graphite examples, exhibiting whip-quick responsiveness and a surprising wellspring of torque under high casting and fighting loads. Built to handle a wide range of techniques, including 3/8oz. jigs, Texas rigs, free rigs, heavy-cover spinnerbaiting, weed-cutting blade bait searches, and no-sinker soft baits in pinpoint cover, BEARING DOWN delivers a compact weapon to enable creative, trendsetting approaches in the toughest conditions. This Yuki Ito spec model is named for its unimaginable strength, known to break down reels during testing before its debut in 1996.</v>
       </c>
+      <c r="AH94" t="str">
+        <v/>
+      </c>
+      <c r="AI94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -10628,6 +11129,12 @@
       <c r="AG95" t="str">
         <v>By focusing on the characteristics that allow the POPX to realize its full potential, the F1-63X became a rare masterwork that unlocks untold potential across the small-plugging world. The POPX STICK draws on the uniquely crisp “spring-back” action of the 5-D GRAPHITE SYSTEM to overcome the soft sluggishness of conventional light action rods. Where past light-action rods bend deep into the blank with wobbly responsiveness and clumsy control, the POPX STICK brings virtually lossless transmission to small plugs, communicating the precise rhythm and energy of each “twitch” to impart irresistible action. Further, the improved blank integrity of POPX STICK reduces blank twist and instability throughout the cast, allowing more precise and powerful placement to conjure key bites.</v>
       </c>
+      <c r="AH95" t="str">
+        <v/>
+      </c>
+      <c r="AI95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -10730,7 +11237,10 @@
         <v>The storied SEVENELEVEN is one of the founding Destroyer® models that has proudly stood the test of time for over a quarter-century. Early friends of Yuki Ito, the Randy Blaukat and the late Aaron Martens, both factored heavily in design and development and relied on the SEVENELEVEN to compete in tournaments across the US. The SEVENELEVEN entered the scene with what was at the time one of the longest rods in tournament regulation. It excelled in close combat with light Texas rigs or jigs in shore cover, contributed as a limit maker with small to medium-sized search baits in wide shallow areas, and dredged kickers from the depths cranking. This tournament-born weapon builds on its legacy with the latest Megabass rod building expertise to power the legends of tomorrow.</v>
       </c>
       <c r="AH96" t="str">
-        <v>オフセットハンドル</v>
+        <v>Other.1: オフセットハンドル</v>
+      </c>
+      <c r="AI96" t="str">
+        <v/>
       </c>
     </row>
     <row r="97">
@@ -10833,6 +11343,12 @@
       <c r="AG97" t="str">
         <v>The F5st-65XS KIRISAME KAMEYAMA SPECIAL is the ultimate spinning tool for finesse cover situations and deep, open water nose-hooking. The medium-fast taper is finished with a solid carbon STINGER TIP for unimaginable sensitivity in a F5-power rod. This unique marriage of opposites allows for the presentation of lighter rigs that would only be possible with rods underpowered for the task at hand. The KAMEYAMA SPECIAL is built to target deep rockpiles, gnarly submerged timber, brush, and structure infested with treacherously sharp quagga mussels. With this "heavyweight finesse" spinning setup, delicate rigs can be cast into heavy cover with confidence. The STINGER TIP allows for subtle lure manipulation and crisp sensitivity, while the F5-powered blank has the backbone to decisively haul hard-won catches from cover. *As with all STINGER TIPS, please be especially mindful of tip storage and high-sticking, as this professionally tuned tool will not forgive misuse. If cared for properly, the STINGER TIP will deliver unrivaled performance, year after year.</v>
       </c>
+      <c r="AH97" t="str">
+        <v/>
+      </c>
+      <c r="AI97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -10934,6 +11450,12 @@
       <c r="AG98" t="str">
         <v>When developing the F2-66XS WHIPPET, the Megabass design team set out to explore the concept behind the F2-64XS, a spinning rod beloved for the better part of 25 years. The resulting 5-D Graphite prototypes came in nearly 35% lighter and with significantly more torque, leading to the addition of 2" to the blank's length and minor adjustments to more fully realize the F2-64XS' original potential. The WHIPPET is a multi-purpose, "whip-like" performer, boasting agile blank recovery, lightness and powerful torque to enable multi-purpose finesse applications.</v>
       </c>
+      <c r="AH98" t="str">
+        <v/>
+      </c>
+      <c r="AI98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -11035,6 +11557,12 @@
       <c r="AG99" t="str">
         <v>Reimagining the CLIFF HANGER finesse masterpiece with 5-D GRAPHITE, Yuki Ito developed the ultimate utility bait finesse rod: F2-60X CLIFFHANGER THRILLING. Such a rod must strive for lightweight performance and test the limits of extreme engineering; display excellent precision castability to pierce gaps in cover; carry outsized load-bearing strength and lifting power; and above all, inspire technical angling to new heights. The F2-60X delivers on all fronts, displaying an astonishingly high power to weight ratio. The extraordinary level of featherweight performance far exceeds the RACING CONDITION of the past, expanding the bait finesse stage by leaps and bounds.</v>
       </c>
+      <c r="AH99" t="str">
+        <v/>
+      </c>
+      <c r="AI99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -11136,6 +11664,12 @@
       <c r="AG100" t="str">
         <v>The F3.1/2-70X Z-CRANK ELSEIL is an achievement in purpose-built cranking, arising from Yuki Ito’s dual-expertise as a lure and rod designer. Applying the insight gained most recently from the SUPER-Z, Ito set out to trim the fat from conventional cranking sticks, delivering a blank that gives with supple smoothness, yet exhibits quick recovery and the highest power-to-weight ratio in its class. This drives longer casts, confident control, and the ability to "pop" lures free of grass—all without sacrificing the effortless "give" required to capture cranking bites. The Z-CRANK ELSEIL excels with fast-moving lures such as the SUPER-Z, VIBRATION-X DYNA, SMATRA, S-CRANK 1.2 and VISION ONETEN Jr. The new lightweight, fast-moving special F3.1/2-70X demonstrates the kind of performance only possible when rods are developed by the same designers as the lures for which they are intended.</v>
       </c>
+      <c r="AH100" t="str">
+        <v/>
+      </c>
+      <c r="AI100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -11238,7 +11772,10 @@
         <v>The KIRISAME BAIT STRATEGIST brings the delicate finesse tactics previously relegated to spinning tackle to the world of high-performance multi-piece baitcasting, expanding the adventure angler’s toolkit to meet tomorrow’s challenges. The latest 5D graphite system not only results in a lighter, stronger and more sensitive shaft, but most importantly, delivers the kind of silky-smooth load transfer required of light-line applications. Boasting an extended shaft with exquisite balance, the 7'3" length offers nimbly intuitive handling comparable to a traditional 6'3" class rod. The ergonomic carbon fiber grip dials up angler feel, transmitting even the slightest vibrations captured by the Fst-73X’s solid carbon Stinger Tip. The KIRISAME BAIT STRATEGIST is made to deliver your favorite finesse spinning approaches in a baitcasting form factor, enabling a new dimension of angler approach. Convenient 3-piece construction with grip joint for easy transport on your next adventure.</v>
       </c>
       <c r="AH101" t="str">
-        <v>オフセットハンドル</v>
+        <v>Other.1: オフセットハンドル</v>
+      </c>
+      <c r="AI101" t="str">
+        <v/>
       </c>
     </row>
     <row r="102">
@@ -11341,6 +11878,12 @@
       <c r="AG102" t="str">
         <v>The F6-69X SUPER DESTROYER is perhaps the epitome of the series, harnessing the successive technologies of each generation to challenge preconceptions of heavy-action angling. Built on a compact 6'9" frame, the 5-D GRAPHITE SYSTEM harnesses greater power per inch to deliver quick, destructive hooksets and submission-inducing lifting power. The SUPER DESTROYER's outstanding balance is geared towards a tip-up ready posture, the perfect battle stance for lure manipulation and lightning-fast hooksets. Not only does the shorter overall length contribute to faster hooksets, it also increases maneuverability, close-quarters control, and opens up new angling avenues to challenge traditional heavy-cover games.</v>
       </c>
+      <c r="AH102" t="str">
+        <v/>
+      </c>
+      <c r="AI102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -11442,6 +11985,12 @@
       <c r="AG103" t="str">
         <v>The F4-65X ONETEN STICK is built specifically for Japanese-style jerkbaiting, leveraging revolutionary 5-D graphite construction to elevate the jerkbait platform to new heights. At 6'5", the length has been perfectly calibrated for maximum jerk impact with minimal effort, requiring less angler input to hit slack line and set your jerkbaits to dancing. 5-D construction makes for a refreshingly responsive blank, snapping back to attention with a whip-quickness that makes dialing-in jerkbait cadence a pure joy. A set of larger-diameter guides are employed to add tip weight for ease of downward-jerking, in addition to reducing the effect of ice buildup in the winter months. Further, larger diameter rings provide a visual que—just watch for the line to reverberate and shake, and you know you have executed a proper slack-line jerk. To many professional anglers, there is only one jerkbait—the VISION ONETEN. It stands to reason there is only one ONETEN STICK for Japanese jerkbaiting.</v>
       </c>
+      <c r="AH103" t="str">
+        <v/>
+      </c>
+      <c r="AI103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -11543,6 +12092,12 @@
       <c r="AG104" t="str">
         <v>The F2.1/2-611X KASUMI SIX ELEVEN is built for delicate approaches from raised angling vantages along bridges, canals, and steep-walled waterways, and long-distance running and gunning to cover key spots with speed and precision. Perfect for shad plugs, minnows, light crankbaits, small rubber jigs and bait finesse, the KASUMI SIX ELEVEN displays overwhelming attack power, long range utility, and versatility. When it is time for topwater approaches, the crisply responsive 5-D blank propels screaming casts, delivers pinpoint accuracy, and enables subtle angler control to impart irresistible action.</v>
       </c>
+      <c r="AH104" t="str">
+        <v/>
+      </c>
+      <c r="AI104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -11645,7 +12200,10 @@
         <v>The bank-fishing special, F7.1/2-90X ICBM, is a super long-distance weapon developed for the trophy-hunting anglers lining the shores of Lake Biwa. The 9' shaft harnesses the potential of 5-D GRAPHITE, displaying furious energy to unleash moon-shot casts and uncanny sensitivity to develop sonar-like maps with each bottom-contacting retrieve. The ICBM stands above other rods in its class, delivering an intuitive feel that belies its daunting length.</v>
       </c>
       <c r="AH105" t="str">
-        <v>オフセットハンドル</v>
+        <v>Other.1: オフセットハンドル</v>
+      </c>
+      <c r="AI105" t="str">
+        <v/>
       </c>
     </row>
     <row r="106">
@@ -11748,6 +12306,12 @@
       <c r="AG106" t="str">
         <v>The F5-68X BLADE derives its name both from the blade bait category and its ability to cut weeds and reeds with sharp power. Imbued with the unique blank tension of the 5-D GRAPHITE SYSTEM, the BLADE’s medium-fast taper is ideally suited to spinnerbaits, bladed swim jigs, Texas rigs and jigs deployed where cover contact is inevitable. The BLADE is tuned to maximize direct lure feedback, transmitting the subtle vibrations necessary for intuitive adjustments on the water. A shaft that accurately conveys even slight changes in vibration is an active participant in elevating your game, enabling a particularly aggressive cover approach.</v>
       </c>
+      <c r="AH106" t="str">
+        <v/>
+      </c>
+      <c r="AI106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -11849,6 +12413,12 @@
       <c r="AG107" t="str">
         <v>Born to meet the challenge of Japan's toughest fields, the F0st-62XS KIRISAME ULTIMATE is the extreme expression of ultralight finesse, dialing sensitivity to the maximum setting with a solid carbon STINGER TIP and the extrasensory abilities of 5-D Graphite. The KIRISAME ULTIMATE enables ultralight presentations down to 2lb test, with the kind of silky-smooth responsiveness required to absorb sudden fights without straining line to the breaking point. The integrity of the new 5-D blank construction method further reduces unwanted blank twist and heavy reverberations, delivering focused, ultralight sensitivity and control.</v>
       </c>
+      <c r="AH107" t="str">
+        <v/>
+      </c>
+      <c r="AI107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -11950,6 +12520,12 @@
       <c r="AG108" t="str">
         <v>As its namesake suggests, the F7.1/2-75X MONSTROUS is built for otherworldly bites and big baits like the MAGDRAFT, MEGADOG-X, i-SLIDE, GORHAM, SPINE-X, i-WING, and VATALION. Our proprietary 5D graphite system delivers a high-power shaft with surprising lightweight agility. With a uniquely intuitive feel, MONSTROUS enables the angler to operate big baits with delicate precision and overwhelming power to capture and secure monster bites. The rod features a robust all-double-footed guide setting with TITANIUM frames. The guide arrangement and thread wrapping technique pursue a lightweight balance comparable to single foot guide models. When you’re after a monster that will be etched in your memory forever, the otherworldly performance of the F7.1/2-75X MONSTROUS delivers.</v>
       </c>
+      <c r="AH108" t="str">
+        <v/>
+      </c>
+      <c r="AI108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -12051,6 +12627,12 @@
       <c r="AG109" t="str">
         <v>Delivering monster torque, the F6-66X KILLER CODE is a close-quarters precision tool for larger baits like the i-WING 135 that often require longer, heavier rods. In the search for the ideal blend of tension, torque, and length, the "666" rod number code has emerged again, showcasing its unique ability to place and control heavyweight lures. The 6'6" length delivers truly outsize power, drawing upon the 5-D GRAPHITE SYSTEM to stop monsters in their tracks and deliver them to the surface. Compact blank and regular taper offer highly maneuverable presentation of swimbaits, big baits and frogs, bringing overwhelming performance to tight cast windows and pinpoint target areas.</v>
       </c>
+      <c r="AH109" t="str">
+        <v/>
+      </c>
+      <c r="AI109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -12152,6 +12734,12 @@
       <c r="AG110" t="str">
         <v>The F1st-66XS KIRISAME is the new standard KIRISAME of the 5-D Graphite era. With a STINGER TIP and upgraded blank, KIRISAME is a master of light finesse rigs, scoring highly across all finesse benchmarks throughout its development. The extra fast tip displays excellent “give,” absorbing light bites and imparting tantalizing action alike. Improved cut-patterning and layering process of the 5-D GRAPHITE SYSTEM ensures an impossibly smooth taper transition into the mid-section, where the blank’s tenacious torque enables long casts, strong lifting power, and decisive sweeping hooksets. The KIRISAME is the new global standard of finesse utility.</v>
       </c>
+      <c r="AH110" t="str">
+        <v/>
+      </c>
+      <c r="AI110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -12253,6 +12841,12 @@
       <c r="AG111" t="str">
         <v>The GRAVEL CODE pushes the limits of bait finesse, with a high-powered, aggressively tapered blank made possible by our proprietary 5D graphite. The tip is delicately sensitive, gently welcoming the lightest pickup bites without alerting targets, while the butt section delivers a torquey power equivalent to that of a medium-powered F4.1/2 class. This unique finesse high-tension shaft allows you to expertly present finesse presentations in areas where conventional BFS rods lack the power to land bites. At low loads, the F2.1/2-62X GRAVEL CODE exhibits a tip-only bend like an extra-fast taper, but when combined with a true BFS reel, anyone can experience the rapid-fire cast performance of our 5D graphite blanks. While GRAVEL CODE excels at casting light rigs and aggressively targeting pinpoint cover areas with bait finesse tactics, it is also a deadly option for deep fishing in winter, early spring, and late autumn.</v>
       </c>
+      <c r="AH111" t="str">
+        <v/>
+      </c>
+      <c r="AI111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -12354,6 +12948,12 @@
       <c r="AG112" t="str">
         <v>The F3.1/2-72XS WIND BUSTER is the "go-to" choice to confront a vast and varied field, offering an ideal balance of length and power to handle finesse softbaits and smaller hardbaits alike-especially when tough headwinds make lures difficult to cast with baitcasting setups. Powered by the 5-D GRAPHITE SYSTEM, the WIND BUSTER displays crisp blank recovery performance and unexpected torque, enlivening presentations from shaky heads to jerkbaits. Medium-fast taper uncoils with silky-smoothness, transitioning load to where it is borne best, allowing for both delicate rod work and domineering performance as the situation dictates.</v>
       </c>
+      <c r="AH112" t="str">
+        <v/>
+      </c>
+      <c r="AI112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -12456,7 +13056,10 @@
         <v>MEGALATHAN is a high-power battle rod built for extreme angling applications. Developed by Project ZERO, led by Yuki Ito with direct input from U.S. tournament professionals, this formidable monster-hunter delivers world-class torque and crushing power, dominating big bait scenarios. Designed to cover the full spectrum of technical big-game applications—including oversized swimbaits; pitching, flipping, and punching into heavy cover; and magnum bait games up to 6 oz— MEGALATHAN meets the demands of tomorrow’s trophy anglers. To challenge kaiju-class targets, it is equipped with robust double-footed guides and double-wrapped for maximum durability. Despite its immense power, MEGALATHAN exhibits an exquisite rod balance that minimizes fatigue even during consecutive days of relentless big-game fishing. A new-generation weapon that delivers monster-class power with surprising comfort and control.</v>
       </c>
       <c r="AH113" t="str">
-        <v>オフセットハンドル</v>
+        <v>Other.1: オフセットハンドル</v>
+      </c>
+      <c r="AI113" t="str">
+        <v/>
       </c>
     </row>
     <row r="114">
@@ -12559,6 +13162,12 @@
       <c r="AG114" t="str">
         <v>The reengineered F3-611LVS WHIPSNAKE expands global usability through refined blank engineering and iterative performance-tuning. The standard-setting, versatile WHIPSNAKE is designed to handle the full range of light-rig applications, including jighead rigs, drop shots, and Neko rigs. Its finely tuned tip section delivers exceptional precision and control across all finesse presentations, while the high-tension midsection ensures decisive hooksets and one-sided fights. A reinforced butt section generates upgraded torque to quickly lift and control big bass, elevating every section of the X-Graphite blank to the next performance tier. The result is a stress-free spinning platform that redefines the global standard for competitive spinning techniques.</v>
       </c>
+      <c r="AH114" t="str">
+        <v/>
+      </c>
+      <c r="AI114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -12660,6 +13269,12 @@
       <c r="AG115" t="str">
         <v>The F3.1/2-70LVS SHAKYHEAD, a veteran of the U.S. tournament scene, has been refined and updated with the latest X-Graphite engineering technology for a new generation of anglers. Preserving the unyielding ethos and fast-action heritage of its predecessors, the new SHAKYHEAD is a master rig manipulator built to coax even the wariest of feeders.  SHAKYHEAD delivers precise control, strong hookset and fish-fighting performance, and excels in its namesake shaky head, FFS mid-strolling and deep drop-shot applications. The powerful blank also supports cover finesse fishing, confidently pitching finesse rigs and small jigs into cover for high-percentage bites, providing a trusted weapon to podium-bound anglers.</v>
       </c>
+      <c r="AH115" t="str">
+        <v/>
+      </c>
+      <c r="AI115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -12761,6 +13376,12 @@
       <c r="AG116" t="str">
         <v>A bottom contact powerhouse focused on techniques that demand uncompromising hookset performance, the PERFECT PITCH roams heavy cover in pursuit of lurking monsters. From football jigs and Texas rigs to chatterbaits, swim jigs, and big spinnerbaits worked over weedy bottoms, the F7-73LV excels in high-power, high-pressure scenarios. The responsive, high-resolution tip section and high-tension belly enabled by the blank’s X-Graphite construction deliver exquisite tip control and sensitivity, detecting even tentative bites. That feedback is immediately translated into decisive hooksets, driven home by a powerful butt section capable of taking the fight to big bass. Despite its formidable power, PERFECT PITCH maintains superb reel-mounted balance, delivering light, agile handling for knockout hooksets.</v>
       </c>
+      <c r="AH116" t="str">
+        <v/>
+      </c>
+      <c r="AI116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -12862,6 +13483,12 @@
       <c r="AG117" t="str">
         <v>The F4-69LVS SHAMSHIR is a competition-grade spinning rod designed to meet the dynamic needs of jerkbait professionals and secure fickle bites even under brutal conditions. Built to confidently work small- to medium-sized minnows and shads such as the VISION ONETEN, ONETEN Jr., X-80, VISION95, and SHADING-X, the rod’s new X-Graphite System and fine-tuning achieve an ideal balance of absorption and spring-back blank recovery.  This specialized blank damping characteristic dramatically amplifies jerkbait darting range while enabling ergonomic, fatigue-free rod work, delivering a refined and balanced experience. The rod’s mild tip section absorbs aggressive strikes on jerkbaits and weightless stickbaits to improve hookup ratios, while the overbuilt midsection delivers instant and consistent power.  SHAMSHIR’s powerful 6'9" blank also matches a wide variety of light-rig applications, making it an effective option for finesse presentations in weeded areas and complex highland reservoirs filled with standing timber and stumps.</v>
       </c>
+      <c r="AH117" t="str">
+        <v/>
+      </c>
+      <c r="AI117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -12963,6 +13590,12 @@
       <c r="AG118" t="str">
         <v>The Bait Finesse Special (BFS) is a light-action model engineered for advanced bait finesse techniques with effortless control. Designed to search structure efficiently while maintaining constant contact, it delivers excellent agility and pinpoint casting accuracy when targeting shoreline cover. An extremely sensitive tip section excels at delicate presentations, including small rubber jigs, jighead rigs, and insect-style lures, allowing precise shaking and subtle lure manipulation. This refined control makes it ideal for high-pressure situations that demand delicate execution. Featuring an ultra-lightweight, high-balance blank, this model offers direct, intuitive feedback that enhances bite detection and hook-up efficiency, making it a versatile and confidence-inspiring bait finesse tool.</v>
       </c>
+      <c r="AH118" t="str">
+        <v/>
+      </c>
+      <c r="AI118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -13064,6 +13697,12 @@
       <c r="AG119" t="str">
         <v>A foundational model in the LEVANTE lineup, the RUN&amp;GUNNING is designed for long distance rapid-fire searches with treble hook baits and fast-moving lures. Despite its 7’1” length, the X-Graphite System provides light, agile handling. Its extended casting range delivers a major advantage with crankbaits, spinnerbaits, vibrating jigs, and bladed jigs, allowing anglers to extract bites from large areas quickly and effectively. By eliminating the sluggishness often associated with longer rods, this model offers a sharp and responsive feel and intuitive control, making it ideal for aggressive run-and-gun strategies.</v>
       </c>
+      <c r="AH119" t="str">
+        <v/>
+      </c>
+      <c r="AI119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -13165,6 +13804,12 @@
       <c r="AG120" t="str">
         <v>The DIABLO-LV is designed for confident power fishing around vegetation such as weeds and reeds. It excels with spinnerbaits, chatterbaits, swim jigs, and slow-moving presentations, while also supporting Texas rigs and jigs for cover-focused fishing. The X-Graphite blank enhances sensitivity, comfort and performance during cover and bottom contact, while the 7’2” length enables long-distance casting and precise depth control with medium to heavy lures. Heightened sensitivity allows anglers to detect bites instantly and unleash the DIABLO’s power, delivering fearsome hooksets and extracting fish from cover with ease.</v>
       </c>
+      <c r="AH120" t="str">
+        <v/>
+      </c>
+      <c r="AI120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -13266,6 +13911,12 @@
       <c r="AG121" t="str">
         <v>The Bait Finesse Special (BFS) is a light-action model engineered for advanced bait finesse techniques with effortless control. Designed to search structure efficiently while maintaining constant contact, it delivers excellent agility and pinpoint casting accuracy when targeting shoreline cover. An extremely sensitive tip section excels at delicate presentations, including small rubber jigs, jighead rigs, and insect-style lures, allowing precise shaking and subtle lure manipulation. This refined control makes it ideal for high-pressure situations that demand delicate execution. Featuring an ultra-lightweight, high-balance blank, this model offers direct, intuitive feedback that enhances bite detection and hook-up efficiency, making it a versatile and confidence-inspiring bait finesse tool.</v>
       </c>
+      <c r="AH121" t="str">
+        <v/>
+      </c>
+      <c r="AI121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -13367,6 +14018,12 @@
       <c r="AG122" t="str">
         <v>The RUN &amp; GUNNING spec-L is a versatile model that expands lure and technique compatibility while delivering enhanced power and responsiveness. Featuring a 6’10” medium-fast taper, it offers a crisp and precise feel paired with strong torque. Designed for long-distance casting and fast-moving lures, it handles everything from the GIANT DOG-X and POPMAX topwaters to buzzbaits, spinnerbaits, vibration baits, crankbaits, and the IxI series. Its versatility makes it ideal for covering water efficiently.  Built for anglers who favor an active run-and-gun style, this rod delivers comfort, control, and adaptability across a wide range of moving bait applications.</v>
       </c>
+      <c r="AH122" t="str">
+        <v/>
+      </c>
+      <c r="AI122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -13468,6 +14125,12 @@
       <c r="AG123" t="str">
         <v>The POWER FINESSE rod is built to dominate light-cover situations using lightweight rigs such as small rubber jigs, light Texas rigs, Neko rigs, and drop shots. Engineered to extract quality fish from cover without sacrificing finesse sensitivity. The ultra-sensitive tip detects even the lightest bites, translating feedback into fast, decisive hooksets. Superior sensitivity from the X-Graphite System allows anglers to clearly read bottom composition and structure transitions. Balanced with a responsive belly and strong butt section, this rod also handles light moving baits such as 1/4 oz spinnerbaits and small crankbaits with ease. It is a true power finesse platform for pressured fish and demanding conditions.</v>
       </c>
+      <c r="AH123" t="str">
+        <v/>
+      </c>
+      <c r="AI123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -13569,6 +14232,12 @@
       <c r="AG124" t="str">
         <v>The ELSEIL-LV channels the storied DNA of the ELSEIL into the LEVANTE’s X-Graphite System to bring this fast-moving special to a new generation of anglers. It excels with mid-weight moving baits such as chatterbaits, spinnerbaits, vibrations, and crankbaits, enabling aggressive, pinpoint approaches to dissect productive areas quickly.  Its highly responsive tip section also allows precise pitching of light Texas rigs and high-density weightless worms into light cover, expanding its versatility beyond traditional moving bait roles. The sharp swing feel, high sensitivity, and long-distance accuracy—combined with lightweight handling that belies its length—make this rod an excellent choice for anglers who demand coverage and control.</v>
       </c>
+      <c r="AH124" t="str">
+        <v/>
+      </c>
+      <c r="AI124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -13670,6 +14339,12 @@
       <c r="AG125" t="str">
         <v>A bottom contact powerhouse focused on techniques that demand uncompromising hookset performance, the PERFECT PITCH roams heavy cover in pursuit of lurking monsters. From football jigs and Texas rigs to chatterbaits, swim jigs, and big spinnerbaits worked over weedy bottoms, the F7-73LV excels in high-power, high-pressure scenarios. The responsive, high-resolution tip section and high-tension belly enabled by the blank’s X-Graphite construction deliver exquisite tip control and sensitivity, detecting even tentative bites. That feedback is immediately translated into decisive hooksets, driven home by a powerful butt section capable of taking the fight to big bass. Despite its formidable power, PERFECT PITCH maintains superb reel-mounted balance, delivering light, agile handling for knockout hooksets.</v>
       </c>
+      <c r="AH125" t="str">
+        <v/>
+      </c>
+      <c r="AI125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -13771,6 +14446,12 @@
       <c r="AG126" t="str">
         <v>A foundational model in the LEVANTE lineup, the RUN&amp;GUNNING is designed for long distance rapid-fire searches with treble hook baits and fast-moving lures. Despite its 7’1” length, the X-Graphite System provides light, agile handling. Its extended casting range delivers a major advantage with crankbaits, spinnerbaits, vibrating jigs, and bladed jigs, allowing anglers to extract bites from large areas quickly and effectively. By eliminating the sluggishness often associated with longer rods, this model offers a sharp and responsive feel and intuitive control, making it ideal for aggressive run-and-gun strategies.</v>
       </c>
+      <c r="AH126" t="str">
+        <v/>
+      </c>
+      <c r="AI126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -13872,6 +14553,12 @@
       <c r="AG127" t="str">
         <v>The ENFORCER is the LEVANTE’s flagship deep-water spinning rod developed through decades of U.S. tournament experience.  Born to explore the unknown depths through long-distance approaches or vertical drops, the ENFORCER is engineered to handle everything from traditional tubes to swing-heads, heavy drop shots, free rigs, high-density soft plastics, and next-generation bottom swimmers like the DARK SLEEPER. The rod’s heightened feedback detects tentative bites and its wellspring of power drives thicker-gauge hooks home to own the fight. Powered by an X-Graphite blank, the ENFORCER delivers crisply responsive performance, overwhelming torque, and fatigue-free handling, making it an essential spinning platform for serious anglers.</v>
       </c>
+      <c r="AH127" t="str">
+        <v/>
+      </c>
+      <c r="AI127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -13973,6 +14660,12 @@
       <c r="AG128" t="str">
         <v>The DIABLO-LV is designed for confident power fishing around vegetation such as weeds and reeds. It excels with spinnerbaits, chatterbaits, swim jigs, and slow-moving presentations, while also supporting Texas rigs and jigs for cover-focused fishing. The X-Graphite blank enhances sensitivity, comfort and performance during cover and bottom contact, while the 7’2” length enables long-distance casting and precise depth control with medium to heavy lures. Heightened sensitivity allows anglers to detect bites instantly and unleash the DIABLO’s power, delivering fearsome hooksets and extracting fish from cover with ease.</v>
       </c>
+      <c r="AH128" t="str">
+        <v/>
+      </c>
+      <c r="AI128" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -14074,6 +14767,12 @@
       <c r="AG129" t="str">
         <v>The ELSEIL-LV channels the storied DNA of the ELSEIL into the LEVANTE’s X-Graphite System to bring this fast-moving special to a new generation of anglers. It excels with mid-weight moving baits such as chatterbaits, spinnerbaits, vibrations, and crankbaits, enabling aggressive, pinpoint approaches to dissect productive areas quickly.  Its highly responsive tip section also allows precise pitching of light Texas rigs and high-density weightless worms into light cover, expanding its versatility beyond traditional moving bait roles. The sharp swing feel, high sensitivity, and long-distance accuracy—combined with lightweight handling that belies its length—make this rod an excellent choice for anglers who demand coverage and control.</v>
       </c>
+      <c r="AH129" t="str">
+        <v/>
+      </c>
+      <c r="AI129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -14175,6 +14874,12 @@
       <c r="AG130" t="str">
         <v>The F5.1/2-74LV SLEEPER CONTACT is a bottom-contact specialist built to maximize bite-inducing performance in the depths. Designed for delicately crawling lures such as the DARK SLEEPER and SLEEPER CRAW, rubber jigs, Texas rigs, free rigs, and high-density worms along the bottom, it enhances precise obstacle avoidance and retrieve control with heightened sensitivity. Its 7’4” blank delivers exceptional long-distance casting, expanding effective coverage beyond standard competition rods. It also performs effortlessly with deep crankbaits and swimbait applications. The LEVANTE’s advanced X-Graphite System minimizes blank twist and enhances both cast distance and accuracy, allowing pinpoint precision. Even when faced with challenging bottom structure, the SLEEPER CONTACT is an intuitive extension of the angler, delivering crisp handling and minute control to coax the most challenging deep bites.</v>
       </c>
+      <c r="AH130" t="str">
+        <v/>
+      </c>
+      <c r="AI130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -14276,6 +14981,12 @@
       <c r="AG131" t="str">
         <v>MEGALATHAN is a high-power battle rod built for extreme angling applications. Developed by Project ZERO, led by Yuki Ito with direct input from U.S. tournament professionals, this formidable monster-hunter delivers world-class torque and crushing power, dominating big bait scenarios. Designed to cover the full spectrum of technical big-game applications—including oversized swimbaits; pitching, flipping, and punching into heavy cover; and magnum bait games up to 6 oz— MEGALATHAN meets the demands of tomorrow’s trophy anglers. To challenge kaiju-class targets, it is equipped with robust double-footed guides and double-wrapped for maximum durability. Despite its immense power, MEGALATHAN exhibits an exquisite rod balance that minimizes fatigue even during consecutive days of relentless big-game fishing. A new-generation weapon that delivers monster-class power with surprising comfort and control.</v>
       </c>
+      <c r="AH131" t="str">
+        <v/>
+      </c>
+      <c r="AI131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -14377,6 +15088,12 @@
       <c r="AG132" t="str">
         <v>The SUPER FINESSE is designed for technical long-distance finesse fishing. It excels at subtle shaking of finesse rigs and pinpoint insect-style lure presentations while maintaining distance from wary fish. Despite its light action, the midsection is engineered with higher tension characteristics, enabling advanced finesse plugging and technical control of finesse hard lures. Refined to target clever, pressured fish under tough conditions, this is the most finesse-oriented rod in the LEVANTE series built for professional-level finesse fishing techniques.</v>
       </c>
+      <c r="AH132" t="str">
+        <v/>
+      </c>
+      <c r="AI132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -14478,6 +15195,12 @@
       <c r="AG133" t="str">
         <v>The ENFORCER is the LEVANTE’s flagship deep-water spinning rod developed through decades of U.S. tournament experience.  Born to explore the unknown depths through long-distance approaches or vertical drops, the ENFORCER is engineered to handle everything from traditional tubes to swing-heads, heavy drop shots, free rigs, high-density soft plastics, and next-generation bottom swimmers like the DARK SLEEPER. The rod’s heightened feedback detects tentative bites and its wellspring of power drives thicker-gauge hooks home to own the fight. Powered by an X-Graphite blank, the ENFORCER delivers crisply responsive performance, overwhelming torque, and fatigue-free handling, making it an essential spinning platform for serious anglers.</v>
       </c>
+      <c r="AH133" t="str">
+        <v/>
+      </c>
+      <c r="AI133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -14579,6 +15302,12 @@
       <c r="AG134" t="str">
         <v>The SUPER FINESSE is designed for technical long-distance finesse fishing. It excels at subtle shaking of finesse rigs and pinpoint insect-style lure presentations while maintaining distance from wary fish. Despite its light action, the midsection is engineered with higher tension characteristics, enabling advanced finesse plugging and technical control of finesse hard lures. Refined to target clever, pressured fish under tough conditions, this is the most finesse-oriented rod in the LEVANTE series built for professional-level finesse fishing techniques.</v>
       </c>
+      <c r="AH134" t="str">
+        <v/>
+      </c>
+      <c r="AI134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -14680,6 +15409,12 @@
       <c r="AG135" t="str">
         <v>The BFS Spec-UL is a high-performance bait finesse rod designed to bring ultra-light techniques to life with precision and control. Tuned specifically for topwater applications, it delivers crisp, rhythmic action that allows lures like the DOG-X series and POPX to perform at their full potential. Its slow-taper design enables aggressive walking actions, expanded darting range, and controlled lure turns exceeding 180 degrees, while also excelling at low-trajectory casting of small jigs and weightless soft plastics. This allows anglers to accurately target overhanging cover with bait finesse efficiency traditionally reserved for spinning gear. Built on the X-Graphite System, the BFS Spec-UL features a reinforced butt section capable of handling unexpected big fish from light cover. It delivers a refined, ultra-light bait finesse experience that exudes confidence and control.</v>
       </c>
+      <c r="AH135" t="str">
+        <v/>
+      </c>
+      <c r="AI135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -14781,6 +15516,12 @@
       <c r="AG136" t="str">
         <v>The MIYAKODA SPECIAL is a high-spec spinning rod forged on the demanding waters of Miyakoda River Dam near the Megabass headquarters. Known for its dense standing timber and complex rock formations, this tough reservoir has long served as a proving ground for many iconic Megabass designs.  The MIYAKODA excels at threading rigs through tight gaps in gnarly cover, delivering natural free rig and small rubber jig falls, discerning subtle bite signals and converting them into decisive hooksets, and hauling fish clear of cover. Enabling repeated, pinpoint approaches to targets holding at multiple depth ranges, the responsive tip is built to detect and capture tough fall-bites with confidence.  The high-tension midsection maintains excellent hookset performance even on deep-range bites, while the rod’s torque-rich power brings aggressive finesse cover games to life.</v>
       </c>
+      <c r="AH136" t="str">
+        <v/>
+      </c>
+      <c r="AI136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -14882,6 +15623,12 @@
       <c r="AG137" t="str">
         <v>A foundational model in the LEVANTE lineup, the RUN&amp;GUNNING is designed for long distance rapid-fire searches with treble hook baits and fast-moving lures. Despite its 7’1” length, the X-Graphite System provides light, agile handling. Its extended casting range delivers a major advantage with crankbaits, spinnerbaits, vibrating jigs, and bladed jigs, allowing anglers to extract bites from large areas quickly and effectively. By eliminating the sluggishness often associated with longer rods, this model offers a sharp and responsive feel and intuitive control, making it ideal for aggressive run-and-gun strategies.</v>
       </c>
+      <c r="AH137" t="str">
+        <v/>
+      </c>
+      <c r="AI137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -14983,6 +15730,12 @@
       <c r="AG138" t="str">
         <v>The RUN &amp; GUNNING spec-L is a versatile model that expands lure and technique compatibility while delivering enhanced power and responsiveness. Featuring a 6’10” medium-fast taper, it offers a crisp and precise feel paired with strong torque. Designed for long-distance casting and fast-moving lures, it handles everything from the GIANT DOG-X and POPMAX topwaters to buzzbaits, spinnerbaits, vibration baits, crankbaits, and the IxI series. Its versatility makes it ideal for covering water efficiently.  Built for anglers who favor an active run-and-gun style, this rod delivers comfort, control, and adaptability across a wide range of moving bait applications.</v>
       </c>
+      <c r="AH138" t="str">
+        <v/>
+      </c>
+      <c r="AI138" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -15084,6 +15837,12 @@
       <c r="AG139" t="str">
         <v>A swimbait rod with incredible versatility, the F7.1/2-76LV is purpose-built for the MAGDRAFT series. From the everyday 5in and 6in sizes, to the trophy-targeting 7in and 8in models, the blank’s proprietary X-Graphite construction adapts to load and brings forth a seemingly endless reservoir of torque and power. This translates into stratospheric long-distance casts and unforgiving hooksets. At the same time, the blank’s high torsional rigidity, which limits lost energy and blank wobble, supports crisp, high-precision pitching—accurately sending jigs through pinpoint holes in heavy cover. The MAGDRAFT SPECIAL fully exploits its massive torque to excel in power applications, including slow-rolling oversized spinnerbaits, super-deep cranking, and technical manipulation of glide baits. Its smooth and supple blank absorbs unexpected, aggressive strikes, while its formidable lifting power overwhelms trophies, bringing hard-won bites to the scales.</v>
       </c>
+      <c r="AH139" t="str">
+        <v/>
+      </c>
+      <c r="AI139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -15185,6 +15944,12 @@
       <c r="AG140" t="str">
         <v>Born from decades of tournament competition and feedback from jerkbait specialists in the US and Japan, this rod is engineered to take Megabass’ legendary jerkbaits to new heights. The regular taper is painstakingly fine-tuned to provide a forgiving cushion and responsive spring-back that enhances rhythm and control. Designed to maximize the darting action of jerkbaits such as the ONETEN, ONETEN Jr., VISION95, and X-80, it converts slack line into crisp, controlled movement that brings lures to bite-inducing life. Oversized guides enable dynamic adjustments to line tension to quickly adapt jerkbait action and cadence to changing bite conditions.  The torque-rich blank also performs well with medium to large topwaters, crankbaits, spinnerbaits, and vibration baits, delivering solid hook-up performance during aggressive strikes.</v>
       </c>
+      <c r="AH140" t="str">
+        <v/>
+      </c>
+      <c r="AI140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -15286,6 +16051,12 @@
       <c r="AG141" t="str">
         <v>Born from decades of tournament competition and feedback from jerkbait specialists in the US and Japan, this rod is engineered to take Megabass’ legendary jerkbaits to new heights. The regular taper is painstakingly fine-tuned to provide a forgiving cushion and responsive spring-back that enhances rhythm and control. Designed to maximize the darting action of jerkbaits such as the ONETEN, ONETEN Jr., VISION95, and X-80, it converts slack line into crisp, controlled movement that brings lures to bite-inducing life. Oversized guides enable dynamic adjustments to line tension to quickly adapt jerkbait action and cadence to changing bite conditions.  The torque-rich blank also performs well with medium to large topwaters, crankbaits, spinnerbaits, and vibration baits, delivering solid hook-up performance during aggressive strikes.</v>
       </c>
+      <c r="AH141" t="str">
+        <v/>
+      </c>
+      <c r="AI141" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -15387,6 +16158,12 @@
       <c r="AG142" t="str">
         <v>The MIYAKODA SPECIAL is a high-spec spinning rod forged on the demanding waters of Miyakoda River Dam near the Megabass headquarters. Known for its dense standing timber and complex rock formations, this tough reservoir has long served as a proving ground for many iconic Megabass designs.  The MIYAKODA excels at threading rigs through tight gaps in gnarly cover, delivering natural free rig and small rubber jig falls, discerning subtle bite signals and converting them into decisive hooksets, and hauling fish clear of cover. Enabling repeated, pinpoint approaches to targets holding at multiple depth ranges, the responsive tip is built to detect and capture tough fall-bites with confidence.  The high-tension midsection maintains excellent hookset performance even on deep-range bites, while the rod’s torque-rich power brings aggressive finesse cover games to life.</v>
       </c>
+      <c r="AH142" t="str">
+        <v/>
+      </c>
+      <c r="AI142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -15488,6 +16265,12 @@
       <c r="AG143" t="str">
         <v>The reengineered F3-611LVS WHIPSNAKE expands global usability through refined blank engineering and iterative performance-tuning. The standard-setting, versatile WHIPSNAKE is designed to handle the full range of light-rig applications, including jighead rigs, drop shots, and Neko rigs. Its finely tuned tip section delivers exceptional precision and control across all finesse presentations, while the high-tension midsection ensures decisive hooksets and one-sided fights. A reinforced butt section generates upgraded torque to quickly lift and control big bass, elevating every section of the X-Graphite blank to the next performance tier. The result is a stress-free spinning platform that redefines the global standard for competitive spinning techniques.</v>
       </c>
+      <c r="AH143" t="str">
+        <v/>
+      </c>
+      <c r="AI143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -15589,6 +16372,12 @@
       <c r="AG144" t="str">
         <v>The ELSEIL-LV channels the storied DNA of the ELSEIL into the LEVANTE’s X-Graphite System to bring this fast-moving special to a new generation of anglers. It excels with mid-weight moving baits such as chatterbaits, spinnerbaits, vibrations, and crankbaits, enabling aggressive, pinpoint approaches to dissect productive areas quickly.  Its highly responsive tip section also allows precise pitching of light Texas rigs and high-density weightless worms into light cover, expanding its versatility beyond traditional moving bait roles. The sharp swing feel, high sensitivity, and long-distance accuracy—combined with lightweight handling that belies its length—make this rod an excellent choice for anglers who demand coverage and control.</v>
       </c>
+      <c r="AH144" t="str">
+        <v/>
+      </c>
+      <c r="AI144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -15690,6 +16479,12 @@
       <c r="AG145" t="str">
         <v>Based on the legendary WHIPSNAKE, the spec-L is re-tuned to handle the lighter rigs required for highly pressured fishing conditions. It is a uniquely versatile light spinning rod built for a wide range of finesse applications in global waters. Despite its light F2 power rating, it delivers a crisply solid feel thanks to the structural integrity of the X-Graphite blank, providing direct control without lag. This core Megabass rod building concept of “directivity” ensures the WHIPSNAKE spec-L acts as an intuitive extension of the angler’s body and intent, delivering controlled precision in lure presentations.  Capable of handling finesse rigs and light plugging, this universal model is one that anglers will surely reach for in tough bite situations around the world.</v>
       </c>
+      <c r="AH145" t="str">
+        <v/>
+      </c>
+      <c r="AI145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -15791,6 +16586,12 @@
       <c r="AG146" t="str">
         <v>A swimbait rod with incredible versatility, the F7.1/2-76LV is purpose-built for the MAGDRAFT series. From the everyday 5in and 6in sizes, to the trophy-targeting 7in and 8in models, the blank’s proprietary X-Graphite construction adapts to load and brings forth a seemingly endless reservoir of torque and power. This translates into stratospheric long-distance casts and unforgiving hooksets. At the same time, the blank’s high torsional rigidity, which limits lost energy and blank wobble, supports crisp, high-precision pitching—accurately sending jigs through pinpoint holes in heavy cover. The MAGDRAFT SPECIAL fully exploits its massive torque to excel in power applications, including slow-rolling oversized spinnerbaits, super-deep cranking, and technical manipulation of glide baits. Its smooth and supple blank absorbs unexpected, aggressive strikes, while its formidable lifting power overwhelms trophies, bringing hard-won bites to the scales.</v>
       </c>
+      <c r="AH146" t="str">
+        <v/>
+      </c>
+      <c r="AI146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -15892,6 +16693,12 @@
       <c r="AG147" t="str">
         <v>The POWER FINESSE rod is built to dominate light-cover situations using lightweight rigs such as small rubber jigs, light Texas rigs, Neko rigs, and drop shots. Engineered to extract quality fish from cover without sacrificing finesse sensitivity. The ultra-sensitive tip detects even the lightest bites, translating feedback into fast, decisive hooksets. Superior sensitivity from the X-Graphite System allows anglers to clearly read bottom composition and structure transitions. Balanced with a responsive belly and strong butt section, this rod also handles light moving baits such as 1/4 oz spinnerbaits and small crankbaits with ease. It is a true power finesse platform for pressured fish and demanding conditions.</v>
       </c>
+      <c r="AH147" t="str">
+        <v/>
+      </c>
+      <c r="AI147" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -15993,6 +16800,12 @@
       <c r="AG148" t="str">
         <v>Based on the legendary WHIPSNAKE, the spec-L is re-tuned to handle the lighter rigs required for highly pressured fishing conditions. It is a uniquely versatile light spinning rod built for a wide range of finesse applications in global waters. Despite its light F2 power rating, it delivers a crisply solid feel thanks to the structural integrity of the X-Graphite blank, providing direct control without lag. This core Megabass rod building concept of “directivity” ensures the WHIPSNAKE spec-L acts as an intuitive extension of the angler’s body and intent, delivering controlled precision in lure presentations.  Capable of handling finesse rigs and light plugging, this universal model is one that anglers will surely reach for in tough bite situations around the world.</v>
       </c>
+      <c r="AH148" t="str">
+        <v/>
+      </c>
+      <c r="AI148" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -16094,6 +16907,12 @@
       <c r="AG149" t="str">
         <v>Named after the legendary sword, the ZANGETSU-LV is a long-distance finesse model engineered to strike precisely and devastatingly from long range. Built for situations where anglers must keep their distance and offer baits with refined subtlety, ZANGETSU-LV delivers refined control while maintaining the sharp, decisive feel required to convert distant bites into landed fish. ZANGETSU-LV excels in mid-strolling applications and long-distance minnow presentations, allowing anglers to keep lures in the strike zone and dial in the bite. It also performs confidently with swimming jighead rigs, drop shots, and light Carolina rigs, while retaining the ability to pitch small rubber jigs and high-density weightless plastics into light cover when needed. The new X-Graphite construction provides a crisp feel with a solid, wobble-free core and highly linear rig control. ZANGETSU-LV’s torque-rich action maintains tension yet flexes smoothly under load to comfortably support long-distance casting and multi-round fights with hard-charging targets.  Refined for angling snipers who demand absolute certainty when targeting spooky fish, this rare long-distance special elevates distance, accuracy, and controllability across diverse rigs to new levels.</v>
       </c>
+      <c r="AH149" t="str">
+        <v/>
+      </c>
+      <c r="AI149" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -16195,6 +17014,12 @@
       <c r="AG150" t="str">
         <v>A swimbait rod with incredible versatility, the F7.1/2-76LV is purpose-built for the MAGDRAFT series. From the everyday 5in and 6in sizes, to the trophy-targeting 7in and 8in models, the blank’s proprietary X-Graphite construction adapts to load and brings forth a seemingly endless reservoir of torque and power. This translates into stratospheric long-distance casts and unforgiving hooksets. At the same time, the blank’s high torsional rigidity, which limits lost energy and blank wobble, supports crisp, high-precision pitching—accurately sending jigs through pinpoint holes in heavy cover. The MAGDRAFT SPECIAL fully exploits its massive torque to excel in power applications, including slow-rolling oversized spinnerbaits, super-deep cranking, and technical manipulation of glide baits. Its smooth and supple blank absorbs unexpected, aggressive strikes, while its formidable lifting power overwhelms trophies, bringing hard-won bites to the scales.</v>
       </c>
+      <c r="AH150" t="str">
+        <v/>
+      </c>
+      <c r="AI150" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -16296,6 +17121,12 @@
       <c r="AG151" t="str">
         <v>The F4-69LVS SHAMSHIR is a competition-grade spinning rod designed to meet the dynamic needs of jerkbait professionals and secure fickle bites even under brutal conditions. Built to confidently work small- to medium-sized minnows and shads such as the VISION ONETEN, ONETEN Jr., X-80, VISION95, and SHADING-X, the rod’s new X-Graphite System and fine-tuning achieve an ideal balance of absorption and spring-back blank recovery.  This specialized blank damping characteristic dramatically amplifies jerkbait darting range while enabling ergonomic, fatigue-free rod work, delivering a refined and balanced experience. The rod’s mild tip section absorbs aggressive strikes on jerkbaits and weightless stickbaits to improve hookup ratios, while the overbuilt midsection delivers instant and consistent power.  SHAMSHIR’s powerful 6'9" blank also matches a wide variety of light-rig applications, making it an effective option for finesse presentations in weeded areas and complex highland reservoirs filled with standing timber and stumps.</v>
       </c>
+      <c r="AH151" t="str">
+        <v/>
+      </c>
+      <c r="AI151" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -16397,6 +17228,12 @@
       <c r="AG152" t="str">
         <v>The ENFORCER is the LEVANTE’s flagship deep-water spinning rod developed through decades of U.S. tournament experience.  Born to explore the unknown depths through long-distance approaches or vertical drops, the ENFORCER is engineered to handle everything from traditional tubes to swing-heads, heavy drop shots, free rigs, high-density soft plastics, and next-generation bottom swimmers like the DARK SLEEPER. The rod’s heightened feedback detects tentative bites and its wellspring of power drives thicker-gauge hooks home to own the fight. Powered by an X-Graphite blank, the ENFORCER delivers crisply responsive performance, overwhelming torque, and fatigue-free handling, making it an essential spinning platform for serious anglers.</v>
       </c>
+      <c r="AH152" t="str">
+        <v/>
+      </c>
+      <c r="AI152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -16498,6 +17335,12 @@
       <c r="AG153" t="str">
         <v>MEGALATHAN is a high-power battle rod built for extreme angling applications. Developed by Project ZERO, led by Yuki Ito with direct input from U.S. tournament professionals, this formidable monster-hunter delivers world-class torque and crushing power, dominating big bait scenarios. Designed to cover the full spectrum of technical big-game applications—including oversized swimbaits; pitching, flipping, and punching into heavy cover; and magnum bait games up to 6 oz— MEGALATHAN meets the demands of tomorrow’s trophy anglers. To challenge kaiju-class targets, it is equipped with robust double-footed guides and double-wrapped for maximum durability. Despite its immense power, MEGALATHAN exhibits an exquisite rod balance that minimizes fatigue even during consecutive days of relentless big-game fishing. A new-generation weapon that delivers monster-class power with surprising comfort and control.</v>
       </c>
+      <c r="AH153" t="str">
+        <v/>
+      </c>
+      <c r="AI153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -16599,6 +17442,12 @@
       <c r="AG154" t="str">
         <v>The MIYAKODA SPECIAL is a high-spec spinning rod forged on the demanding waters of Miyakoda River Dam near the Megabass headquarters. Known for its dense standing timber and complex rock formations, this tough reservoir has long served as a proving ground for many iconic Megabass designs.  The MIYAKODA excels at threading rigs through tight gaps in gnarly cover, delivering natural free rig and small rubber jig falls, discerning subtle bite signals and converting them into decisive hooksets, and hauling fish clear of cover. Enabling repeated, pinpoint approaches to targets holding at multiple depth ranges, the responsive tip is built to detect and capture tough fall-bites with confidence.  The high-tension midsection maintains excellent hookset performance even on deep-range bites, while the rod’s torque-rich power brings aggressive finesse cover games to life.</v>
       </c>
+      <c r="AH154" t="str">
+        <v/>
+      </c>
+      <c r="AI154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -16700,6 +17549,12 @@
       <c r="AG155" t="str">
         <v>The F5.1/2-74LV SLEEPER CONTACT is a bottom-contact specialist built to maximize bite-inducing performance in the depths. Designed for delicately crawling lures such as the DARK SLEEPER and SLEEPER CRAW, rubber jigs, Texas rigs, free rigs, and high-density worms along the bottom, it enhances precise obstacle avoidance and retrieve control with heightened sensitivity. Its 7’4” blank delivers exceptional long-distance casting, expanding effective coverage beyond standard competition rods. It also performs effortlessly with deep crankbaits and swimbait applications. The LEVANTE’s advanced X-Graphite System minimizes blank twist and enhances both cast distance and accuracy, allowing pinpoint precision. Even when faced with challenging bottom structure, the SLEEPER CONTACT is an intuitive extension of the angler, delivering crisp handling and minute control to coax the most challenging deep bites.</v>
       </c>
+      <c r="AH155" t="str">
+        <v/>
+      </c>
+      <c r="AI155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -16801,6 +17656,12 @@
       <c r="AG156" t="str">
         <v>Named after the legendary sword, the ZANGETSU-LV is a long-distance finesse model engineered to strike precisely and devastatingly from long range. Built for situations where anglers must keep their distance and offer baits with refined subtlety, ZANGETSU-LV delivers refined control while maintaining the sharp, decisive feel required to convert distant bites into landed fish. ZANGETSU-LV excels in mid-strolling applications and long-distance minnow presentations, allowing anglers to keep lures in the strike zone and dial in the bite. It also performs confidently with swimming jighead rigs, drop shots, and light Carolina rigs, while retaining the ability to pitch small rubber jigs and high-density weightless plastics into light cover when needed. The new X-Graphite construction provides a crisp feel with a solid, wobble-free core and highly linear rig control. ZANGETSU-LV’s torque-rich action maintains tension yet flexes smoothly under load to comfortably support long-distance casting and multi-round fights with hard-charging targets.  Refined for angling snipers who demand absolute certainty when targeting spooky fish, this rare long-distance special elevates distance, accuracy, and controllability across diverse rigs to new levels.</v>
       </c>
+      <c r="AH156" t="str">
+        <v/>
+      </c>
+      <c r="AI156" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -16902,6 +17763,12 @@
       <c r="AG157" t="str">
         <v>The BFS Spec-UL is a high-performance bait finesse rod designed to bring ultra-light techniques to life with precision and control. Tuned specifically for topwater applications, it delivers crisp, rhythmic action that allows lures like the DOG-X series and POPX to perform at their full potential. Its slow-taper design enables aggressive walking actions, expanded darting range, and controlled lure turns exceeding 180 degrees, while also excelling at low-trajectory casting of small jigs and weightless soft plastics. This allows anglers to accurately target overhanging cover with bait finesse efficiency traditionally reserved for spinning gear. Built on the X-Graphite System, the BFS Spec-UL features a reinforced butt section capable of handling unexpected big fish from light cover. It delivers a refined, ultra-light bait finesse experience that exudes confidence and control.</v>
       </c>
+      <c r="AH157" t="str">
+        <v/>
+      </c>
+      <c r="AI157" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -17003,6 +17870,12 @@
       <c r="AG158" t="str">
         <v>The SUPER FINESSE is designed for technical long-distance finesse fishing. It excels at subtle shaking of finesse rigs and pinpoint insect-style lure presentations while maintaining distance from wary fish. Despite its light action, the midsection is engineered with higher tension characteristics, enabling advanced finesse plugging and technical control of finesse hard lures. Refined to target clever, pressured fish under tough conditions, this is the most finesse-oriented rod in the LEVANTE series built for professional-level finesse fishing techniques.</v>
       </c>
+      <c r="AH158" t="str">
+        <v/>
+      </c>
+      <c r="AI158" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -17104,6 +17977,12 @@
       <c r="AG159" t="str">
         <v>The RUN &amp; GUNNING spec-L is a versatile model that expands lure and technique compatibility while delivering enhanced power and responsiveness. Featuring a 6’10” medium-fast taper, it offers a crisp and precise feel paired with strong torque. Designed for long-distance casting and fast-moving lures, it handles everything from the GIANT DOG-X and POPMAX topwaters to buzzbaits, spinnerbaits, vibration baits, crankbaits, and the IxI series. Its versatility makes it ideal for covering water efficiently.  Built for anglers who favor an active run-and-gun style, this rod delivers comfort, control, and adaptability across a wide range of moving bait applications.</v>
       </c>
+      <c r="AH159" t="str">
+        <v/>
+      </c>
+      <c r="AI159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -17205,6 +18084,12 @@
       <c r="AG160" t="str">
         <v>The F3.1/2-70LVS SHAKYHEAD, a veteran of the U.S. tournament scene, has been refined and updated with the latest X-Graphite engineering technology for a new generation of anglers. Preserving the unyielding ethos and fast-action heritage of its predecessors, the new SHAKYHEAD is a master rig manipulator built to coax even the wariest of feeders.  SHAKYHEAD delivers precise control, strong hookset and fish-fighting performance, and excels in its namesake shaky head, FFS mid-strolling and deep drop-shot applications. The powerful blank also supports cover finesse fishing, confidently pitching finesse rigs and small jigs into cover for high-percentage bites, providing a trusted weapon to podium-bound anglers.</v>
       </c>
+      <c r="AH160" t="str">
+        <v/>
+      </c>
+      <c r="AI160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -17306,6 +18191,12 @@
       <c r="AG161" t="str">
         <v>The F3.1/2-70LVS SHAKYHEAD, a veteran of the U.S. tournament scene, has been refined and updated with the latest X-Graphite engineering technology for a new generation of anglers. Preserving the unyielding ethos and fast-action heritage of its predecessors, the new SHAKYHEAD is a master rig manipulator built to coax even the wariest of feeders.  SHAKYHEAD delivers precise control, strong hookset and fish-fighting performance, and excels in its namesake shaky head, FFS mid-strolling and deep drop-shot applications. The powerful blank also supports cover finesse fishing, confidently pitching finesse rigs and small jigs into cover for high-percentage bites, providing a trusted weapon to podium-bound anglers.</v>
       </c>
+      <c r="AH161" t="str">
+        <v/>
+      </c>
+      <c r="AI161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -17407,6 +18298,12 @@
       <c r="AG162" t="str">
         <v>The DIABLO-LV is designed for confident power fishing around vegetation such as weeds and reeds. It excels with spinnerbaits, chatterbaits, swim jigs, and slow-moving presentations, while also supporting Texas rigs and jigs for cover-focused fishing. The X-Graphite blank enhances sensitivity, comfort and performance during cover and bottom contact, while the 7’2” length enables long-distance casting and precise depth control with medium to heavy lures. Heightened sensitivity allows anglers to detect bites instantly and unleash the DIABLO’s power, delivering fearsome hooksets and extracting fish from cover with ease.</v>
       </c>
+      <c r="AH162" t="str">
+        <v/>
+      </c>
+      <c r="AI162" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -17508,6 +18405,12 @@
       <c r="AG163" t="str">
         <v>The Bait Finesse Special (BFS) is a light-action model engineered for advanced bait finesse techniques with effortless control. Designed to search structure efficiently while maintaining constant contact, it delivers excellent agility and pinpoint casting accuracy when targeting shoreline cover. An extremely sensitive tip section excels at delicate presentations, including small rubber jigs, jighead rigs, and insect-style lures, allowing precise shaking and subtle lure manipulation. This refined control makes it ideal for high-pressure situations that demand delicate execution. Featuring an ultra-lightweight, high-balance blank, this model offers direct, intuitive feedback that enhances bite detection and hook-up efficiency, making it a versatile and confidence-inspiring bait finesse tool.</v>
       </c>
+      <c r="AH163" t="str">
+        <v/>
+      </c>
+      <c r="AI163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -17610,7 +18513,10 @@
         <v>The best rod for shore-based distance games and wading games with the MEGADOG (130g). This long distance big plugging special can easily control 100g plus lures. The unique setup utilizing large diameter #8 guides makes for smooth contact with super thick 60lb plus leader, promising stress-free big plugging and distance games. For open water casting this universal rod can be used for all domestic lure targets. For overseas fishing, it’s perfect for 30kg class freshwater giants such as barramundi and murray cod, as well as striper, papuan bass, dorado, and mahseer. In Japan it excels against such targets as the Japanese huchen and Japanese lates. This rod combines high shaft rigidity that handles heavyweight lure casting along with flexibility that absorbs violent charges and head shaking, reducing lost bites. Targets: bass, sea bass, catfish, rockfish, large blue fish, Japanese huchens, Japanese lates, barramundi, Nile perch, Papuan bass, murray cod, dorado, striper, mahseer, yellowcheek * The photograph is a prototype.</v>
       </c>
       <c r="AH164" t="str">
-        <v>カーボン70%　グラス30％</v>
+        <v>Other.1: カーボン70%　グラス30％</v>
+      </c>
+      <c r="AI164" t="str">
+        <v/>
       </c>
     </row>
     <row r="165">
@@ -17714,7 +18620,10 @@
         <v>The VKC-66XH-3 is designed for long distance casts into the vast open waters and easy power to deploy magnum-sized lures in the 100+g class, enabling anglers to approach targets lurking in the distance. It is also suitable for boat cover games where you face off against big predators around vegetation. The nano-matrix composite shaft provides overwhelming torque and control to dominate the powerful pull of monster fish and bring them in for a sure landing. The VKC-66XH-3 is a super-strong shaft with amazing long castability and high power, delivering high fishing performance in fields all over the world.</v>
       </c>
       <c r="AH165" t="str">
-        <v>カーボン60％　グラス40％</v>
+        <v>Other.1: カーボン60％　グラス40％</v>
+      </c>
+      <c r="AI165" t="str">
+        <v/>
       </c>
     </row>
     <row r="166">
@@ -17818,7 +18727,10 @@
         <v>The much-awaited light plugging special from the world expedition series. This model has the exceptional mobility needed to lure targets out in close combat using topwaters and minnows. This 5’8” length rod excels in accuracy, allowing pinpoint targeting. The torquey lifting power of the butt section is a match for any powerful target fish, allowing for thrilling fights. The VKC-58ML-4 has global versatility, whether approaching bass in light cover, engaging in close combat from boat, sea bass fishing in and around structures, trout games in small to medium rivers, light games in mangrove areas, canoe fishing, or floater games. Megabass’ unique low elasticity carbon and glass hybrid construction combines the delicate touch needed to cast a 3g lure, while retaining the power needed to cast a 30g lure, resulting in the creation of this sensational next-generation versatile shaft. Targets: bass, trout, seabass, light rockfish, blackhead seabream, bigeye trevally, mangrove jack, golden mandarin fish, rock flagtail * The photograph is a prototype.</v>
       </c>
       <c r="AH166" t="str">
-        <v>カーボン85%　グラス15％</v>
+        <v>Other.1: カーボン85%　グラス15％</v>
+      </c>
+      <c r="AI166" t="str">
+        <v/>
       </c>
     </row>
     <row r="167">
@@ -17922,7 +18834,10 @@
         <v>From wading to boat fishing and beyond, the versatility and control of the 78H-4 leaves past multi-piece rods in the dust. This 7’8” big bait rod gives plenty of headroom against giant targets. Having this amount of power in a mobile form factor means having a powerful weapon which you can use to continually challenge your personal records. The VKC-78H-4 can handle any lure under 120g. The incredible power counteracts heavy resistance, dramatically increasing monster encounters. The smaller diameter #6 guides compared to the VKC-711XH-4 makes it well suited for pinpoint casting of rubber jigs, heavy Texas rigs, and the fine control of bottom lures. This high-power multi-performance shaft inherits its blank performance from the legendary monster hunting rod the F7-76RDti WHITE PYTHON with a high-level fusion of mobility and attacking power derived from the four-piece portable construction that allows for the vast expansion of hunting grounds. Targets: bass, sea bass (big bait), catfish, rockfish, Japanese huchen, Japanese lates, barramundi, Papuan bass, murray cod, dorado, striper, mahseer, yellowcheek * The photograph is a prototype.</v>
       </c>
       <c r="AH167" t="str">
-        <v>カーボン70%　グラス30％</v>
+        <v>Other.1: カーボン70%　グラス30％</v>
+      </c>
+      <c r="AI167" t="str">
+        <v/>
       </c>
     </row>
     <row r="168">
@@ -18026,7 +18941,10 @@
         <v>ボートからの広大なオープンエリアでのロングディスタンスゲームに対応したVKC-66XH-3。100g超級のマグナムサイズルアーを楽々とフルキャストできる強靭さを備え、遥か彼方に潜むターゲットへアプローチを可能にしました。ブッシュや水生植物周りで巨大魚と対峙するボートカバーゲームにも好適。ナノマトリクスコンポジットシャフトが圧倒的なトルクと追従性をもたらし、モンスターフィッシュのパワフルな引きを受け止め、確実にランディングまで持ち込みます。驚異的な遠投性とハイパワーを誇るVKC-66XH-3は、世界中のフィールドにおいて高い釣獲性能を発揮するスーパーストロングシャフトです。</v>
       </c>
       <c r="AH168" t="str">
-        <v>カーボン60％グラス40％</v>
+        <v>Other.1: カーボン60％グラス40％</v>
+      </c>
+      <c r="AI168" t="str">
+        <v/>
       </c>
     </row>
     <row r="169">
@@ -18130,7 +19048,10 @@
         <v>A must-have rod for worldwide freshwater boat fishing. With solid control and ample power, the tenacious high torque construction far surpasses that of normal bass rods. The power that allows for easy lifting beyond 10kg at an angle of 60 degrees puts it on par with the Power Force F7 of the Original Destroyer series. You can easily cast 50g (2oz) bait such as the i-SLIDE 187R and BIG-M series, while retaining the flexibility to easily control small ¼oz lures to 70g (2.5oz) lures such as the BIG SLAP and MEGADOG. The wide scope of performance gives a powerful new sense of usability to this bass rod. This long grip model is perfect for big bait casting and fighting monster fish. Targets: bass, catfish, sea bass (big bait), rockfish (boat), peacock bass, pike, barramundi, arowana, striper, mahseer * The photograph is a prototype.</v>
       </c>
       <c r="AH169" t="str">
-        <v>カーボン80%　グラス20％</v>
+        <v>Other.1: カーボン80%　グラス20％</v>
+      </c>
+      <c r="AI169" t="str">
+        <v/>
       </c>
     </row>
     <row r="170">
@@ -18234,7 +19155,10 @@
         <v>We have realized a four-piece rod with the overwhelming power to pull out snakehead from super heavy cover, algae and all. For a convenient, portable four-piece rod, the VKC-80XXH-4 provides world class levels of power. The fact that it realizes a weight and rod balance rivaling that of a one-piece snakehead rod is simply astonishing. This monster hunter rod is one of the few in the world that can go toe to toe with 50kg plus beasts such as arapaima, piraiba, giant catfish, and Nile perch. The exceptional portability makes it easy to quickly act on new information, making you extremely mobile, and able to immediately unleash the destructive power upon arrival to the target area. This model has the power hidden within to monster hunt in the great unknown. Targets: bass, snakehead, large catfish, large rockfish, octopus, Japanese lates, barramundi, Nile perch, arapaima, mbenga, alligator gar, sharks, rays * The photograph is a prototype.</v>
       </c>
       <c r="AH170" t="str">
-        <v>カーボン70%　グラス30％</v>
+        <v>Other.1: カーボン70%　グラス30％</v>
+      </c>
+      <c r="AI170" t="str">
+        <v/>
       </c>
     </row>
     <row r="171">
@@ -18338,7 +19262,10 @@
         <v>The versatile 68M shaft is able to utilize all bass lures has been toughened up even further to earn its place in the Valkyrie series. This powerful new shaft has plentiful torque and recovery that’s a step ahead of the pack, making contact with even more game fish possible. The unique hybrid construction of low elasticity carbon and glass allows for instant, overwhelming load-bearing ability against world class targets. With a lifting angle of 60 degrees, it can easily handle over 8kg, exhibiting a toughness that would put it on par with the Power Force F6 from the Original Destroyer series. This masterpiece is of course well suited for bass fishing, but also for everyday angling scenarios. Targets: bass, catfish, sea bass (boat), rockfish (boat), peacock bass, perch, zander, arowana, giant snakehead, barramundi * The photograph is a prototype.</v>
       </c>
       <c r="AH171" t="str">
-        <v>カーボン85%　グラス15％</v>
+        <v>Other.1: カーボン85%　グラス15％</v>
+      </c>
+      <c r="AI171" t="str">
+        <v/>
       </c>
     </row>
     <row r="172">
@@ -18442,7 +19369,10 @@
         <v>The flagship model of World Expedition spinning, equipped with an extension shaft allowing for a length change between 8’8” and 9’6”. From wading games to surf games to shore jigging, this new rod handles it all with ease. The VKS-88-96MH-5.5 has the overwhelming super long distance castability to deliver lures to areas that were impossible to reach under headwinds and crosswinds with bait models. This special function rod has a focus on flight distance and excels at targeting large fish in wide open areas. It’s perfectly suited for experts who can perform delicate adjustments based on drag. It’s perfect for high level power games against seabass and large blue fish, and it performs well against Japanese huchen and Japanese lates as well. Overseas, king salmon and taimen are along the target fish that this rod can catch with certainty. The amazing power from this multi-piece spinning rod allows it to handle 70g class lures such as the BIG SLAP and MEGADOG180 with ease. Adjusting the length of the rod at your destination will allow you to adapt to a wider range of fields and situations. Targets: sea bass, large blue fish, flatfish, large rockfish, Japanese lates, Japanese huchen, king salmon, taimen * The photograph is a prototype.</v>
       </c>
       <c r="AH172" t="str">
-        <v>カーボン75%　グラス25％</v>
+        <v>Other.1: カーボン75%　グラス25％</v>
+      </c>
+      <c r="AI172" t="str">
+        <v/>
       </c>
     </row>
     <row r="173">
@@ -18546,7 +19476,10 @@
         <v>This high rigidity long shaft model bumps up the power specs of the 610ML-4 to a new level. It has the power performance to control fast moving lures at will, along with the versatility to handle most shore-based saltwater lures such as metal type lures up to 40g. The exceptional long distance castability solidifies the 610ML-4 as an all-rounder spinning rod perfect for all types of harbor plugging. This exciting spinning model is well suited for reef fishing, boat fishing (seabass, Japanese Spanish mackerel, Japanese amberjack), river fishing for cherry salmon and large rainbow trout, or long distance plugging for Japanese huchen and bass. Targets: trout, sea bass, Japanese Spanish mackerel, small blue fish, large bigeye trevally, blackhead seabream, pike, zander, golden mandarin fish, striper, peacock, arowana, mahseer * The photograph is a prototype.</v>
       </c>
       <c r="AH173" t="str">
-        <v>カーボン85%　グラス15％</v>
+        <v>Other.1: カーボン85%　グラス15％</v>
+      </c>
+      <c r="AI173" t="str">
+        <v/>
       </c>
     </row>
     <row r="174">
@@ -18650,7 +19583,10 @@
         <v>The VKC-61XH-3 is designed to handle magnum size lures in the 100g class. The compact 6ft 1in shaft provides excellent accuracy and precise rod work. The VKC-61XH-3 is ideal for fishing in close quarters in and around structure or boat casting from a low deck. The strong yet flexible blanks capture the powerful rush of monster fish and confidently absorb violent head shakes to thoroughly dominate the fight. This is a mobile monster hunting weapon that combines high maneuverability and overwhelming power to conquer the monsters of the world.</v>
       </c>
       <c r="AH174" t="str">
-        <v>カーボン60％　グラス40％</v>
+        <v>Other.1: カーボン60％　グラス40％</v>
+      </c>
+      <c r="AI174" t="str">
+        <v/>
       </c>
     </row>
     <row r="175">
@@ -18754,7 +19690,10 @@
         <v>There is no better rod with which to target fish under 3kg using small to medium plugs under 20g. The new Nano Matrix Composite Shaft construction makes hookups easy and reduces lost bites. The blank doesn’t have the dullness of past glass composite rods, and rather features a sharp feel with excellent castability and accuracy. It’s easy to make pinpoint casts along bushes and under overhangs. This rod is not only well suited for bass fishing, but also performs light-plugging in harbor areas, boat-based sea bass fishing, reefs, and river trout games all at a high level. Targets: bass, trout, sea bass, small blue fish, blackhead seabream, perch, zander, golden mandarin fish, arowana * The photograph is a prototype.</v>
       </c>
       <c r="AH175" t="str">
-        <v>カーボン85%　グラス15％</v>
+        <v>Other.1: カーボン85%　グラス15％</v>
+      </c>
+      <c r="AI175" t="str">
+        <v/>
       </c>
     </row>
     <row r="176">
@@ -18857,6 +19796,12 @@
       <c r="AG176" t="str">
         <v/>
       </c>
+      <c r="AH176" t="str">
+        <v/>
+      </c>
+      <c r="AI176" t="str">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -18958,6 +19903,12 @@
       <c r="AG177" t="str">
         <v/>
       </c>
+      <c r="AH177" t="str">
+        <v/>
+      </c>
+      <c r="AI177" t="str">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -19059,6 +20010,12 @@
       <c r="AG178" t="str">
         <v/>
       </c>
+      <c r="AH178" t="str">
+        <v/>
+      </c>
+      <c r="AI178" t="str">
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -19160,6 +20117,12 @@
       <c r="AG179" t="str">
         <v>４‘２“という、特別なショートシャフトモデルは、「エクストリーム クライマー」の名に相応しく、最上流の源流域を目指すスペシャリストの遡行で確実に結果を出すべく、ITO Enginneringテクノロジーが強力にサポート。テイクバックが効かず隙間のような狭スペースしか取れない険しい渓相や、川面をオーバーハングして覆うブッシュ等が占めるようなクローズド・フィールド、大岩の合間を縫うように流れる水量の少ない源流域など、従来のトラウトロッドでは攻めあぐねる超接近戦が要求されるフィールドにも躊躇なく精緻にルアーを打ち込み、渓魚を反応させ、確実にランディングに持ち込むスペシャル・レングスモデルです。 2gに満たない超小型ミノーやGH春蝉のようなミニマムなルアーを的確に飛ばし、繊細なルアーアクションを引き出し存分に扱いきることが出来ます。 見た目は繊細ながら、ブランクスが動的に発揮するパワーとパフォーマンスのギャップには、目を見張るものがあります。尺上のイワナやヤマメに臆すことなく挑める、キリリとした芯の強さを内包する、GREATHUNTINGだからこそ具現化できた、次代のウルトラファインシャフトです。４‘２“のショートシャフトとは思えない、常識を逸するロングディスタンス・キャスタビリティを発揮できるのも魅力。遡行中に遭遇する突如として開けたエリアや、警戒心の高い居着き鱒に対してロングアプローチしたい時も、優れたシューティングパフォーマンスを発揮します。</v>
       </c>
+      <c r="AH179" t="str">
+        <v/>
+      </c>
+      <c r="AI179" t="str">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -19261,6 +20224,12 @@
       <c r="AG180" t="str">
         <v>本流トラウトを制するためのミドルレングス・バーサタイルモデル。 長良川本流・中流域から上流域を主戦場に尺クラスのアマゴ、そして本流の王者サツキマスを狙い撃つために設計した、6.8ftという絶妙なロッドレングス。現地から導き出した長過ぎず、短過ぎないスペシャルブランクスは、ラン＆ガン性能、キャスタビリティ、ルアーの卓越した操作性を高次元で融合。本流の流芯越しへと確実にルアーを送り込めるロングディスタンス・キャスト性能と、ピンスポットを正確に打ち抜くプレシージョン性能、ミノーコントロールにおける軽快で快適な取り回しを高次で両立。5～10cmクラスのミノーイングを中心に、トゥイッチ、ジャーク、ドリフト釣法まで幅広く対応し、淵・瀬・開きといった本流のあらゆるシチュエーションを一本で網羅します。 アマゴ、サツキマス特有の鋭く重たいヘッドシェイクを確実にいなし、特別に調律された、曲げて獲るためのトルクフルなカスタムブランクスは、当地域特有の電光石火のバイトで生じる不用意な弾きを抑え、ランディング時のバラシも大幅に軽減させています。長良川水系などに挑むエキスパートのために特別に受注製作する、スペシャルファンクションモデルです。</v>
       </c>
+      <c r="AH180" t="str">
+        <v/>
+      </c>
+      <c r="AI180" t="str">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -19362,6 +20331,12 @@
       <c r="AG181" t="str">
         <v>The WHIP TWITCH offers the versatility to target Yamame, Iwana, Rainbow and Brown trout in a wide variety of fields. From small minnows to heavier offerings, the high modulus blank delivers crisp feel and whip-quick recovery, allowing for long, accurate casts and precise angler action. Subtle tip is able to handle lighter presentations, without the wobbling tip-shake that often accompanies casts and rod work with lower-grade carbon builds.  Muscular blanks take the fight to large Trout, with a torque and lifting power that belies its thin design.  The WHIP TWITCH is the perfect size to balance distance and accuracy in tight spaces, offering a wide-ranging versatility that will earn its keep on countless climbs.</v>
       </c>
+      <c r="AH181" t="str">
+        <v/>
+      </c>
+      <c r="AI181" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -19463,6 +20438,12 @@
       <c r="AG182" t="str">
         <v>Ultra-compact, ultra-lightweight baitcasting model was designed to the exacting requirements of climber and trout specialist Masakazu Fukuyama. 4-piece construction collapses to a compact 15 inches, allowing for easy storage for day climbs or week-long excursions. Aggressive 4’8” overall length is ideal for tight quarters navigating along rocks, or through thick brush surrounding promising pockets.  Built for compact casts with quick wrist-action, the 484 excels in pinpoint accuracy where full motion casts are difficult to execute. GREAT HUNTING is designed for precise control of ultralight lures, with a forgiving tip section that smoothly transitions into a strong butt section.</v>
       </c>
+      <c r="AH182" t="str">
+        <v/>
+      </c>
+      <c r="AI182" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -19564,6 +20545,12 @@
       <c r="AG183" t="str">
         <v>The KAMLOOPS STINGER is Yuki Ito’s personal model. Designed for a long distance approach in highly-pressured fields, upstream casts, and long drifts while wading, the 6’7” length allows the angler to maintain distance and cover wider areas to trigger elusive bites. With a high frame K-Guide stripper guide, the GREAT HUNTING’s original guide setting delivers the casting performance of a traditional 7’ model in a shorter frame, for increased efficiency.  Tip section is equipped with STINGER TIP technology, an advance first developed for the Destroyer and Hedge Hog series to capture subtle short bites. The KAMLOOP’s blank is finished with YOLOY™ to add an additional layer of protection against scratches and damage that can occur in the wilderness.</v>
       </c>
+      <c r="AH183" t="str">
+        <v/>
+      </c>
+      <c r="AI183" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -19665,6 +20652,12 @@
       <c r="AG184" t="str">
         <v>5.2ftレングスと、1ランク上のパワーが、「エクストリームクライマー」の対応領域を拡大。水量の多い河川や、深い淵が連続するエリア、アングラーの立ち位置と水面までの高低差が大きい渓相など、一般的な渓流用ロッドではパワー不足を感じてしまうフィールドにおいて存分に威力を発揮。テクニカルなパワーゲームアプローチを可能にします。 多様な渓相に対応し、様々なアプローチに対するシームレスな拡張性こそが、このロッドの魅力です。使用ルアーのサイズと狙うターゲットのサイズにきわめてバーサタイルに対応。強い流れでも、流速が生む水流抵抗にも負けないブランクス・テンションをいかんなく発揮し、ルアーの緻密なコントロールを軽快にこなします。 深渕に潜む尺上はもちろん、50㎝を超えるワイルドレインボーやブラウンの強烈な引きを果敢にいなし、確実に手中に収めることができる、新感覚のパワーモデルです。</v>
       </c>
+      <c r="AH184" t="str">
+        <v/>
+      </c>
+      <c r="AI184" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -19766,6 +20759,12 @@
       <c r="AG185" t="str">
         <v>Fully parabolic blank in 5’1” flip-shot length allows for technical casts in tight spaces, and maximal enjoyment throughout the fight.  Smooth-bending design allows for effortless accuracy and distance, even with light weight lures. High-precision Spigot Ferrule Joint System transfers load along the blank with a natural bend curve, virtually eliminated the flat points traditionally associated with multi-piece rods. Collapsed size of 16 inches answers backpackers’ call to challenge mountain streams at the highest level. The Extream Climber 514 is an advanced model built to target those Yamame and large Iwana navigating towards the upper basins in the farthest reaches.</v>
       </c>
+      <c r="AH185" t="str">
+        <v/>
+      </c>
+      <c r="AI185" t="str">
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -19867,6 +20866,12 @@
       <c r="AG186" t="str">
         <v>強い流れの中流域や本流域において、予期せぬ70cmクラスの大型鱒とも堂々と渡り合える、パワーベイトフィネスゲームモデルの真骨頂。 従来の中～本流域トラウトロッドでは怯んでいた、絞られた瀬落ちや急瀬、強い流れが連続するような渓相で、ピンポイントに潜む大型鱒を狙い撃ち、確実にフックセットに持ち込み、流れに乗らせることなく浮かせ、確実にランディングに持ち込むための底知れぬパワーを発揮する、新次元のハイトルクモデルです。 GH52 BATAFRYやGH64 HUMPBACK などの重量級ヘヴィシンキングミノー、GH95やGH110など、中～本流域でのレギュラーミノー全般を幅広く使いこなし、強い流れの中でも水流抵抗に力負けしない軽快な操作性と緻密なレンジキープ性能を発揮。 大型鱒族と対峙するグレートハンターに大きなアドバンテージをもたらし、会心の一撃を繰出していただくために特別に製作する、会心のパワーゲームシャフトです。</v>
       </c>
+      <c r="AH186" t="str">
+        <v/>
+      </c>
+      <c r="AI186" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -19967,6 +20972,12 @@
       </c>
       <c r="AG187" t="str">
         <v>5.5ftというショートレングスで尺上から60cmクラスの大型鱒を積極的に狙って獲りにいく、稀代のスペシャルファンクション・モデルです。 背後にブッシュや岩盤壁が迫るような狭い立ち位置から、狡猾な大型鱒が潜むピンスポットへのテクニカルなシューティングゲームを展開。ロッドの溜めが活かしにくい近距離戦でも、ターゲットをスポットから即座に引き剥がし、大型魚の体力を奪い取るように作用するハイトルク・ブランクは、従来の短尺トラウトロッドの標準的釣力の概念を覆してしまう、曲げるほどに溢れるパワーを発揮。 GH44  BATAFRY等とベストフィットするロッドアクションは、ヘヴィウエイテッドミノーを複雑な流れに打ち込み、一層下のレンジでも流れに負けない果敢なトゥイッチ＆ジャークを頻繁に繰出しながら、的確なストライクレンジを緻密に探っていける、軽快で快適な操作性を有しています。</v>
+      </c>
+      <c r="AH187" t="str">
+        <v/>
+      </c>
+      <c r="AI187" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/GearSage-client/pkgGear/data_raw/megabass_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/megabass_rod_import.xlsx
@@ -455,7 +455,7 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H2" t="str">
         <v>images/megabass_rods/ASL7117X_main.jpg</v>
@@ -490,7 +490,7 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H3" t="str">
         <v>images/megabass_rods/TS79X_main.jpg</v>
@@ -525,7 +525,7 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H4" t="str">
         <v>images/megabass_rods/F7-72XTZ_main.jpg</v>
@@ -560,7 +560,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v>images/megabass_rods/F1-60XP_main.jpg</v>
@@ -595,7 +595,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H6" t="str">
         <v>images/megabass_rods/ASL6401XS_main.jpg</v>
@@ -630,7 +630,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H7" t="str">
         <v>images/megabass_rods/F0.1_2st-62XTS_main.jpg</v>
@@ -665,7 +665,7 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H8" t="str">
         <v>images/megabass_rods/F5.1_2-68ti_main.jpg</v>
@@ -700,7 +700,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H9" t="str">
         <v>images/megabass_rods/GH93-2MS_main.jpg</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H10" t="str">
         <v>images/megabass_rods/GHBF511-4L_main.jpg</v>
@@ -770,7 +770,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H11" t="str">
         <v>images/megabass_rods/F4.1_2-71X_main.jpg</v>
@@ -805,7 +805,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H12" t="str">
         <v>images/megabass_rods/F9-711LV_main.jpg</v>
@@ -840,7 +840,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H13" t="str">
         <v>images/megabass_rods/VKC-711XH-4_main.jpg</v>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H14" t="str">
         <v>images/megabass_rods/GHT610-M_main.jpg</v>
@@ -910,7 +910,7 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H15" t="str">
         <v>images/megabass_rods/GHBF42-4UL_main.jpg</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>ROD</v>
+        <v/>
       </c>
       <c r="H16" t="str">
         <v>images/megabass_rods/GH62-4ML-XG_main.jpg</v>
@@ -1179,7 +1179,7 @@
         <v>High power versatile model from the boat or shore, heavy cover and any depth. Advances is speedy searching capability. Application include Bigbait, heavy weight spinnerbait, wild header, large crank such as Granade and big crank. Transform angler's arm to lethal weapon. Flagship model of ARMS series. * The photograph is a prototype.</v>
       </c>
       <c r="AH2" t="str">
-        <v>Other.1: オフセットハンドル</v>
+        <v>オフセットハンドル</v>
       </c>
       <c r="AI2" t="str">
         <v/>
@@ -2035,10 +2035,10 @@
         <v>This super strong shaft is a step above the TS78X+, and is capable of fully casting super heavyweight lures. It easily accommodates 30-35 cm class big bait, swimbait, and magnum-sized spoons. The overwhelming torsional rigidity and load bearing strength of the DNA graphite will never give in to the monstrous foes you encounter.</v>
       </c>
       <c r="AH10" t="str">
-        <v>Other.2: オフセットハンドル</v>
+        <v/>
       </c>
       <c r="AI10" t="str">
-        <v/>
+        <v>オフセットハンドル</v>
       </c>
     </row>
     <row r="11">
@@ -2142,10 +2142,10 @@
         <v>Anglers in pursuit of the catch of a lifetime demand equipment that performs at the highest-level day in and day out, allowing anglers to maximize slim bite windows and scarce opportunities to land those record-class fish. Megabass gladly accepted this challenge, developing a rod built purely for the baits, techniques, control, and power to land the next world record. For the TS78X, we started from scratch, discarding the design and production concepts behind past bass rods. For the material, we utilized the DNA-SLX graphite system developed for battling tuna, yielding a high-torque blank that is the embodiment of sheer power. This blank can fully cast 200g+ big baits, combined with the lifting-power to pull 20+ pound trophies from the depths. Featuring double-footed guides, each foot is carefully double-wrapped, improving durability, and protecting the blank from any possible damage the metal could exact under extra-heavy load. The TS78X has a special hood that locks the reel in place, securing another key component that will determine the outcome of the fight. The taper action is fast. Despite being such a powerful rod, it is equipped with a surprisingly sensitive tip, allowing for a wider-range of rod work to impart action to giant baits. Taking bank anglers and storage during transport into consideration, the TS-78X is built with a heavy-duty grip-joint. This allows the rod to be taken apart for trips, without sacrificing any strength or durability.</v>
       </c>
       <c r="AH11" t="str">
-        <v>Other.2: オフセットハンドル</v>
+        <v/>
       </c>
       <c r="AI11" t="str">
-        <v/>
+        <v>オフセットハンドル</v>
       </c>
     </row>
     <row r="12">
@@ -2249,10 +2249,10 @@
         <v>While the TS78X is made purely to catch world record fish, the TS77X CASINO has a more reserved design. Made for anglers who pursue their dreams using more than giant baits, the TS77X highly for super-deep crankbaits and magnum spoons. The all double-footed guide system is perfectly reinforced with double wrapping, for powerful control and long-term durability. These tough specifications were created with battles against 70 cm + class monsters in mind.</v>
       </c>
       <c r="AH12" t="str">
-        <v>Other.2: オフセットハンドル</v>
+        <v/>
       </c>
       <c r="AI12" t="str">
-        <v/>
+        <v>オフセットハンドル</v>
       </c>
     </row>
     <row r="13">
@@ -2463,10 +2463,10 @@
         <v>The “Man of the Heavens” was born with the sole purpose of targeting world records. This ultra-strong shaft can fully cast giant, 40 cm+ bait. The tip section features exquisite tension derived through extensive field testing. It stands up superbly to pulling resistance, and allows for the user to freely control giant bait. The destructive torque of the TS82X lets you instantly pierce the jaws of monster fish with thick hooks and bring them under your control with overwhelming power.</v>
       </c>
       <c r="AH14" t="str">
-        <v>Other.2: オフセットハンドル</v>
+        <v/>
       </c>
       <c r="AI14" t="str">
-        <v/>
+        <v>オフセットハンドル</v>
       </c>
     </row>
     <row r="15">
@@ -2784,10 +2784,10 @@
         <v>While using 20-30 cm long and heavy big bait to target deep zones, the ability of the TS78X+ to instantaneously lift hooked monsters to the surface is breathtaking. It is highly suited for large cranks and heavyweight Alabama rigs.</v>
       </c>
       <c r="AH17" t="str">
-        <v>Other.2: オフセットハンドル</v>
+        <v/>
       </c>
       <c r="AI17" t="str">
-        <v/>
+        <v>オフセットハンドル</v>
       </c>
     </row>
     <row r="18">
@@ -2891,10 +2891,10 @@
         <v>The TRIZA DRAGOON is equipped with the “Exclusive Tip.” The customization patterns include the ① “Regular Taper” tip and the ② “Fast Taper” tip which allow for a wide array of fishing methods. The ① “Regular Taper” tip is perfect for powerful fishing using big baits and swim baits. It realizes high torque games that far surpass what past multi-piece rods were capable of. The ② “Fast Taper” tip turns the DRAGOON into a jig and Texas rod that’s expertly suited for striking at heavy cover. The unique design of the tip effectively transmits power to the second belly section, generating the tension needed for jig and worm fishing, as well as achieving excellent sensitivity and vibration transmission characteristics. With one base rod, the DRAGOON transforms to excel at many different applications. * The photograph is a prototype.</v>
       </c>
       <c r="AH18" t="str">
-        <v>Other.2: エクスクルーシブティップ対応モデル</v>
+        <v/>
       </c>
       <c r="AI18" t="str">
-        <v/>
+        <v>エクスクルーシブティップ対応モデル</v>
       </c>
     </row>
     <row r="19">
@@ -2998,10 +2998,10 @@
         <v>Using cutting edge processes, Megabass finesse rod technology has been incorporated into a multi-piece rod. The TRIZA’s unique Triangle construction has created yet another masterpiece rod. That rod is the HIBALI. This extra fine spinning rod is designed for delicate, thrilling approaches with super lightweight finesse rigs. The HIBALI’s unique fine tip makes extreme delicate shaking possible, and the precision tip section has been designed to reliably hook even the gentlest of short bites. Despite being a delicate shaft, the three-piece Triangle construction exhibits astonishing torque and rigidity from the belly section through the butt section, allowing you to comfortably handle surprise attacks from big fish. This completely new finesse shaft not only surpasses the performance of past three-piece shafts but exceeds the performance of previous one piece ultralight rods. The HIBALI has arrived. * The photograph is a prototype.</v>
       </c>
       <c r="AH19" t="str">
-        <v>Other.2: エクスクルーシブティップ対応モデル</v>
+        <v/>
       </c>
       <c r="AI19" t="str">
-        <v/>
+        <v>エクスクルーシブティップ対応モデル</v>
       </c>
     </row>
     <row r="20">
@@ -3105,10 +3105,10 @@
         <v>The TRIZA’s much anticipated finesse function model, the YAMASEMI, is a light action game rod that vastly expands the world of light games. The ① “Fast” tip customization using tubular carbon exhibits delicate, high sensitivity, performance finesse bass fishing using small rubber jigs and jig heads. It’s well suited for not only bass fishing, but also expands the stage to saltwater mebaru games. The ② “Solid” tip customization allows for high performance down shot bass fishing. It’s well suited for insect pattern fishing and professional competitive finesse games comparable to that achieved with tournament rods. It’s well suited not only for bass fishing but expands the stage to saltwater aji games as well. * The photograph is a prototype.</v>
       </c>
       <c r="AH20" t="str">
-        <v>Other.2: エクスクルーシブティップ対応モデル</v>
+        <v/>
       </c>
       <c r="AI20" t="str">
-        <v/>
+        <v>エクスクルーシブティップ対応モデル</v>
       </c>
     </row>
     <row r="21">
@@ -3212,10 +3212,10 @@
         <v>The SPARNA is a versatile, light model that excels at the long-distance casting and control of shads, mini cranks, middleweight topwaters, and long-distance bait finesse. The sharp, super lightweight, high elasticity shaft gives a great casting feel with lightweight lures and has extreme accuracy for pinpoint attacks thank to the stable Triangle construction. The overwhelmingly high sensitivity blows past multi-joint rods out of water and transmits information about the position of the lure and the surrounding environment clearly back to the hands of the angler through the natural wood reel seat. This new light action special rod features superbly accurate control and sensitivity. * The photograph is a prototype.</v>
       </c>
       <c r="AH21" t="str">
-        <v>Other.2: エクスクルーシブティップ対応モデル</v>
+        <v/>
       </c>
       <c r="AI21" t="str">
-        <v/>
+        <v>エクスクルーシブティップ対応モデル</v>
       </c>
     </row>
     <row r="22">
@@ -4282,7 +4282,7 @@
         <v>徹底的にフィネスゲームを極めた「喰わせ」のスペシャリスト。操作性、感度をかつてなき極限まで高めた6’4”のブランクスはまさにARMS。バットからティップまですべてのセクションが腕の延長となってアングラーの意思をスムーズに伝達。水中のルアーを意のままにアクションさせます。フィネスロッドの常識を覆す究極のロッド、ASL6401XSが新たなフィネスゲームの扉を開きます。 ※価格はオプションの内容により異なります。</v>
       </c>
       <c r="AH31" t="str">
-        <v>Other.1: End Blancer Material : MARBLE WOOD</v>
+        <v>End Blancer Material : MARBLE WOOD</v>
       </c>
       <c r="AI31" t="str">
         <v/>
@@ -4389,7 +4389,7 @@
         <v>卓越したキャストフィールと軽快な操作感を併せ持つ、次世代マルチスピニングロッド。ライトリグはもちろんタイニープラグまでをディスタンスに関係なく緻密に操作可能。長さを感じさせないロッドバランスと強靭なバットパワーが、鋭く攻撃的なフィネスゲームを展開。6’7”という絶妙なシャフトレングスから生まれるハイトルクがビッグフィッシュを確実にランディングに持ち込みます。 ※価格はオプションの内容により異なります。</v>
       </c>
       <c r="AH32" t="str">
-        <v>Other.1: End Blancer Material : MAHOGANY WOOD</v>
+        <v>End Blancer Material : MAHOGANY WOOD</v>
       </c>
       <c r="AI32" t="str">
         <v/>
@@ -4496,7 +4496,7 @@
         <v>メガバス・スピニングロッドの名竿、F3-610XSの操作性や軽量感はそのままに、長さを2インチアップ。ティップまで一貫した張りを持たせたASL7003XSは、軽量リグの一点シェイクとライトプラッギングという、相反するメソッドを両立。アームズスーパーレジェーラ・スピニングのフラッグシップシャフトとして次世代のバーサタリティアプローチを実現します。 ※価格はオプションの内容により異なります。</v>
       </c>
       <c r="AH33" t="str">
-        <v>Other.1: End Blancer Material : TEAK WOOD</v>
+        <v>End Blancer Material : TEAK WOOD</v>
       </c>
       <c r="AI33" t="str">
         <v/>
@@ -4817,7 +4817,7 @@
         <v>Like its namesake, ANACONDA is built to overwhelm record-class targets with relentless torque and power.  Ideally suited for punching and frogging in super heavy cover areas, long distance games with big swimbaits, and approaches with magnum baits up to 7 oz., ANACONDA is ready to take the fight to bass fishing destinations around the world.  ANACONDA is a full-contact, extra-heavy rod that sends big baits to the farthest reaches with ease, boldly challenging monsters used to lurking just out of reach. X10 blanks are strong and lightweight, enabling superb balance to reduce angler fatigue on the frontlines.</v>
       </c>
       <c r="AH36" t="str">
-        <v>Other.1: オフセットハンドル</v>
+        <v>オフセットハンドル</v>
       </c>
       <c r="AI36" t="str">
         <v/>
@@ -9418,7 +9418,7 @@
         <v>This is Yuki Ito's special game rod for targeting wide-eyed amago, also known as "tanabira," which roam the currents of Kiso, Shinshu. Tailor-made by MPW (Megabass Performance Works) to Ito’s exacting specifications, the GHBF511-4L features super high-density Ivory Rosewood for its "precise lure management," "continuous high-speed snap work," and "instantaneous bite detection (hand sensitivity)" to target and capture the elusive tanabira. The rod is designed with a tip-down balance for a twitch-heavy technique and is set to larger and stronger stream specifications. Standing in the current that nurtures the tanabira, the rod comfortably enables twitching of heavy sinking minnows such as the GH65 day after day. It is specially geared for reaction fishing to trigger bites in tight windows, deliver lightning hooksets, and unleash the power needed to pull trophies from the strong current. The torquey shaft of the "Tanabira Special" delivers a wider power range and precision control to allow anglers to approach diverse waters with dynamic confidence.</v>
       </c>
       <c r="AH79" t="str">
-        <v>Other.1: Handle Type : SHORT</v>
+        <v>Handle Type : SHORT</v>
       </c>
       <c r="AI79" t="str">
         <v/>
@@ -9525,7 +9525,7 @@
         <v>GHBF53-3UL is a versatile model at the core of the HUNTSMAN series, designed with a stronger power matrix than the GHBF48-3UL to cover faster currents and larger fish. Bringing high controllability to heavier sinking minnows, it performs comfortable continuous twitching in strong currents even with lures that have a lot of pulling resistance. The intuitive control and ergonomic fit become an extension of the arm, enabling active casts with a snap of the wrist. A strong butt section with high torque handles not only big native trout, but also rockfish over 40 cm. With stress-free ergonomics, smooth castability, and the capability to bring a wider range of lure weights to life, the GHBF53-3UL is built for repeated backcountry excursions.</v>
       </c>
       <c r="AH80" t="str">
-        <v>Other.1: Handle Type : SHORT</v>
+        <v>Handle Type : SHORT</v>
       </c>
       <c r="AI80" t="str">
         <v/>
@@ -9632,7 +9632,7 @@
         <v>GHBF60-4L is a long-distance model designed to bring the fight not only to headwaters, but also larger streams. The high-density wood and longer grip shift the rod’s balance point to a tip-up posture, enabling sharp upward twitch work in shallow areas and comfortable wrist casts. The unique rifle-back form of the grip encourages a fighting stance that allows the angler to lock his/her wrist to the end of the handle when interacting with monster fish. Delicate fast tip action is the result of the pursuit of precise lure control. The belly and butt sections, designed with a unique variable matrix to produce high torque, provide the power to pull 60 cm class rainbows from strong currents. This is a power-playing model for native trout games, tested and released after repeated encounters with large silvered amago, enoha, wild rainbows and browns.</v>
       </c>
       <c r="AH81" t="str">
-        <v>Other.1: Handle Type : MIDDLE</v>
+        <v>Handle Type : MIDDLE</v>
       </c>
       <c r="AI81" t="str">
         <v/>
@@ -9739,7 +9739,7 @@
         <v>The GHBF48-3UL is a compact model for remote headwaters that often require climbing to access. The HUNTSMAN's modern shaft feels like an extension of your arm, allowing you to comfortably deploy lure offerings from all positions and angles. Its compact castability enables aggressive approaches to key areas even when it is difficult to secure a foothold or traditional backswing space. The butt section, displaying a tautness that is unimaginable from such a slim blank, provides the crisp backbone for twitching, while the high-tension belly section precisely controls the bite and fight of mountain stream fish. The rod has a powerful lifting ability that exceeds the standard of an ultralight rod, allowing anglers to tackle upper-class fish from high footholds with confidence.</v>
       </c>
       <c r="AH82" t="str">
-        <v>Other.1: Handle Type : SHORT</v>
+        <v>Handle Type : SHORT</v>
       </c>
       <c r="AI82" t="str">
         <v/>
@@ -10488,7 +10488,7 @@
         <v>If you’re looking to deploy 1/16oz. ultra-light rigs with more distance, accuracy and control than ever before, the F2.1/2-77XS ZANGETSU is the answer. This deadly long-distance caster leverages the unique properties of the blank’s 5D graphite system to generate full-torque flexibility. Engineered to load deeply in the cast--even with light rigs--ZANGETSU unleashes angler energy to deploy light offerings to the farthest reaches. This unique ability is adapted from the COOKAI, a distance-defying surfcasting rod powered by a saltwater-tuned 5D graphite system. ZANGETSU’s leading-edge blanks and unique guide settings transmit the subtle motion of lures and rigs to your hand with intuitive clarity, offering excellent handling of light rigs and small shad plugs alike. Crafted with particular attention to the blank’s surface hardness, ZANGETSU delivers surprising sensitivity, securing subtle bites in harsh winter and early spring with a sure sweep hookset.</v>
       </c>
       <c r="AH89" t="str">
-        <v>Other.1: オフセットハンドル</v>
+        <v>オフセットハンドル</v>
       </c>
       <c r="AI89" t="str">
         <v/>
@@ -11237,7 +11237,7 @@
         <v>The storied SEVENELEVEN is one of the founding Destroyer® models that has proudly stood the test of time for over a quarter-century. Early friends of Yuki Ito, the Randy Blaukat and the late Aaron Martens, both factored heavily in design and development and relied on the SEVENELEVEN to compete in tournaments across the US. The SEVENELEVEN entered the scene with what was at the time one of the longest rods in tournament regulation. It excelled in close combat with light Texas rigs or jigs in shore cover, contributed as a limit maker with small to medium-sized search baits in wide shallow areas, and dredged kickers from the depths cranking. This tournament-born weapon builds on its legacy with the latest Megabass rod building expertise to power the legends of tomorrow.</v>
       </c>
       <c r="AH96" t="str">
-        <v>Other.1: オフセットハンドル</v>
+        <v>オフセットハンドル</v>
       </c>
       <c r="AI96" t="str">
         <v/>
@@ -11772,7 +11772,7 @@
         <v>The KIRISAME BAIT STRATEGIST brings the delicate finesse tactics previously relegated to spinning tackle to the world of high-performance multi-piece baitcasting, expanding the adventure angler’s toolkit to meet tomorrow’s challenges. The latest 5D graphite system not only results in a lighter, stronger and more sensitive shaft, but most importantly, delivers the kind of silky-smooth load transfer required of light-line applications. Boasting an extended shaft with exquisite balance, the 7'3" length offers nimbly intuitive handling comparable to a traditional 6'3" class rod. The ergonomic carbon fiber grip dials up angler feel, transmitting even the slightest vibrations captured by the Fst-73X’s solid carbon Stinger Tip. The KIRISAME BAIT STRATEGIST is made to deliver your favorite finesse spinning approaches in a baitcasting form factor, enabling a new dimension of angler approach. Convenient 3-piece construction with grip joint for easy transport on your next adventure.</v>
       </c>
       <c r="AH101" t="str">
-        <v>Other.1: オフセットハンドル</v>
+        <v>オフセットハンドル</v>
       </c>
       <c r="AI101" t="str">
         <v/>
@@ -12200,7 +12200,7 @@
         <v>The bank-fishing special, F7.1/2-90X ICBM, is a super long-distance weapon developed for the trophy-hunting anglers lining the shores of Lake Biwa. The 9' shaft harnesses the potential of 5-D GRAPHITE, displaying furious energy to unleash moon-shot casts and uncanny sensitivity to develop sonar-like maps with each bottom-contacting retrieve. The ICBM stands above other rods in its class, delivering an intuitive feel that belies its daunting length.</v>
       </c>
       <c r="AH105" t="str">
-        <v>Other.1: オフセットハンドル</v>
+        <v>オフセットハンドル</v>
       </c>
       <c r="AI105" t="str">
         <v/>
@@ -13056,7 +13056,7 @@
         <v>MEGALATHAN is a high-power battle rod built for extreme angling applications. Developed by Project ZERO, led by Yuki Ito with direct input from U.S. tournament professionals, this formidable monster-hunter delivers world-class torque and crushing power, dominating big bait scenarios. Designed to cover the full spectrum of technical big-game applications—including oversized swimbaits; pitching, flipping, and punching into heavy cover; and magnum bait games up to 6 oz— MEGALATHAN meets the demands of tomorrow’s trophy anglers. To challenge kaiju-class targets, it is equipped with robust double-footed guides and double-wrapped for maximum durability. Despite its immense power, MEGALATHAN exhibits an exquisite rod balance that minimizes fatigue even during consecutive days of relentless big-game fishing. A new-generation weapon that delivers monster-class power with surprising comfort and control.</v>
       </c>
       <c r="AH113" t="str">
-        <v>Other.1: オフセットハンドル</v>
+        <v>オフセットハンドル</v>
       </c>
       <c r="AI113" t="str">
         <v/>
@@ -18513,7 +18513,7 @@
         <v>The best rod for shore-based distance games and wading games with the MEGADOG (130g). This long distance big plugging special can easily control 100g plus lures. The unique setup utilizing large diameter #8 guides makes for smooth contact with super thick 60lb plus leader, promising stress-free big plugging and distance games. For open water casting this universal rod can be used for all domestic lure targets. For overseas fishing, it’s perfect for 30kg class freshwater giants such as barramundi and murray cod, as well as striper, papuan bass, dorado, and mahseer. In Japan it excels against such targets as the Japanese huchen and Japanese lates. This rod combines high shaft rigidity that handles heavyweight lure casting along with flexibility that absorbs violent charges and head shaking, reducing lost bites. Targets: bass, sea bass, catfish, rockfish, large blue fish, Japanese huchens, Japanese lates, barramundi, Nile perch, Papuan bass, murray cod, dorado, striper, mahseer, yellowcheek * The photograph is a prototype.</v>
       </c>
       <c r="AH164" t="str">
-        <v>Other.1: カーボン70%　グラス30％</v>
+        <v>カーボン70%　グラス30％</v>
       </c>
       <c r="AI164" t="str">
         <v/>
@@ -18620,7 +18620,7 @@
         <v>The VKC-66XH-3 is designed for long distance casts into the vast open waters and easy power to deploy magnum-sized lures in the 100+g class, enabling anglers to approach targets lurking in the distance. It is also suitable for boat cover games where you face off against big predators around vegetation. The nano-matrix composite shaft provides overwhelming torque and control to dominate the powerful pull of monster fish and bring them in for a sure landing. The VKC-66XH-3 is a super-strong shaft with amazing long castability and high power, delivering high fishing performance in fields all over the world.</v>
       </c>
       <c r="AH165" t="str">
-        <v>Other.1: カーボン60％　グラス40％</v>
+        <v>カーボン60％　グラス40％</v>
       </c>
       <c r="AI165" t="str">
         <v/>
@@ -18727,7 +18727,7 @@
         <v>The much-awaited light plugging special from the world expedition series. This model has the exceptional mobility needed to lure targets out in close combat using topwaters and minnows. This 5’8” length rod excels in accuracy, allowing pinpoint targeting. The torquey lifting power of the butt section is a match for any powerful target fish, allowing for thrilling fights. The VKC-58ML-4 has global versatility, whether approaching bass in light cover, engaging in close combat from boat, sea bass fishing in and around structures, trout games in small to medium rivers, light games in mangrove areas, canoe fishing, or floater games. Megabass’ unique low elasticity carbon and glass hybrid construction combines the delicate touch needed to cast a 3g lure, while retaining the power needed to cast a 30g lure, resulting in the creation of this sensational next-generation versatile shaft. Targets: bass, trout, seabass, light rockfish, blackhead seabream, bigeye trevally, mangrove jack, golden mandarin fish, rock flagtail * The photograph is a prototype.</v>
       </c>
       <c r="AH166" t="str">
-        <v>Other.1: カーボン85%　グラス15％</v>
+        <v>カーボン85%　グラス15％</v>
       </c>
       <c r="AI166" t="str">
         <v/>
@@ -18834,7 +18834,7 @@
         <v>From wading to boat fishing and beyond, the versatility and control of the 78H-4 leaves past multi-piece rods in the dust. This 7’8” big bait rod gives plenty of headroom against giant targets. Having this amount of power in a mobile form factor means having a powerful weapon which you can use to continually challenge your personal records. The VKC-78H-4 can handle any lure under 120g. The incredible power counteracts heavy resistance, dramatically increasing monster encounters. The smaller diameter #6 guides compared to the VKC-711XH-4 makes it well suited for pinpoint casting of rubber jigs, heavy Texas rigs, and the fine control of bottom lures. This high-power multi-performance shaft inherits its blank performance from the legendary monster hunting rod the F7-76RDti WHITE PYTHON with a high-level fusion of mobility and attacking power derived from the four-piece portable construction that allows for the vast expansion of hunting grounds. Targets: bass, sea bass (big bait), catfish, rockfish, Japanese huchen, Japanese lates, barramundi, Papuan bass, murray cod, dorado, striper, mahseer, yellowcheek * The photograph is a prototype.</v>
       </c>
       <c r="AH167" t="str">
-        <v>Other.1: カーボン70%　グラス30％</v>
+        <v>カーボン70%　グラス30％</v>
       </c>
       <c r="AI167" t="str">
         <v/>
@@ -18941,7 +18941,7 @@
         <v>ボートからの広大なオープンエリアでのロングディスタンスゲームに対応したVKC-66XH-3。100g超級のマグナムサイズルアーを楽々とフルキャストできる強靭さを備え、遥か彼方に潜むターゲットへアプローチを可能にしました。ブッシュや水生植物周りで巨大魚と対峙するボートカバーゲームにも好適。ナノマトリクスコンポジットシャフトが圧倒的なトルクと追従性をもたらし、モンスターフィッシュのパワフルな引きを受け止め、確実にランディングまで持ち込みます。驚異的な遠投性とハイパワーを誇るVKC-66XH-3は、世界中のフィールドにおいて高い釣獲性能を発揮するスーパーストロングシャフトです。</v>
       </c>
       <c r="AH168" t="str">
-        <v>Other.1: カーボン60％グラス40％</v>
+        <v>カーボン60％グラス40％</v>
       </c>
       <c r="AI168" t="str">
         <v/>
@@ -19048,7 +19048,7 @@
         <v>A must-have rod for worldwide freshwater boat fishing. With solid control and ample power, the tenacious high torque construction far surpasses that of normal bass rods. The power that allows for easy lifting beyond 10kg at an angle of 60 degrees puts it on par with the Power Force F7 of the Original Destroyer series. You can easily cast 50g (2oz) bait such as the i-SLIDE 187R and BIG-M series, while retaining the flexibility to easily control small ¼oz lures to 70g (2.5oz) lures such as the BIG SLAP and MEGADOG. The wide scope of performance gives a powerful new sense of usability to this bass rod. This long grip model is perfect for big bait casting and fighting monster fish. Targets: bass, catfish, sea bass (big bait), rockfish (boat), peacock bass, pike, barramundi, arowana, striper, mahseer * The photograph is a prototype.</v>
       </c>
       <c r="AH169" t="str">
-        <v>Other.1: カーボン80%　グラス20％</v>
+        <v>カーボン80%　グラス20％</v>
       </c>
       <c r="AI169" t="str">
         <v/>
@@ -19155,7 +19155,7 @@
         <v>We have realized a four-piece rod with the overwhelming power to pull out snakehead from super heavy cover, algae and all. For a convenient, portable four-piece rod, the VKC-80XXH-4 provides world class levels of power. The fact that it realizes a weight and rod balance rivaling that of a one-piece snakehead rod is simply astonishing. This monster hunter rod is one of the few in the world that can go toe to toe with 50kg plus beasts such as arapaima, piraiba, giant catfish, and Nile perch. The exceptional portability makes it easy to quickly act on new information, making you extremely mobile, and able to immediately unleash the destructive power upon arrival to the target area. This model has the power hidden within to monster hunt in the great unknown. Targets: bass, snakehead, large catfish, large rockfish, octopus, Japanese lates, barramundi, Nile perch, arapaima, mbenga, alligator gar, sharks, rays * The photograph is a prototype.</v>
       </c>
       <c r="AH170" t="str">
-        <v>Other.1: カーボン70%　グラス30％</v>
+        <v>カーボン70%　グラス30％</v>
       </c>
       <c r="AI170" t="str">
         <v/>
@@ -19262,7 +19262,7 @@
         <v>The versatile 68M shaft is able to utilize all bass lures has been toughened up even further to earn its place in the Valkyrie series. This powerful new shaft has plentiful torque and recovery that’s a step ahead of the pack, making contact with even more game fish possible. The unique hybrid construction of low elasticity carbon and glass allows for instant, overwhelming load-bearing ability against world class targets. With a lifting angle of 60 degrees, it can easily handle over 8kg, exhibiting a toughness that would put it on par with the Power Force F6 from the Original Destroyer series. This masterpiece is of course well suited for bass fishing, but also for everyday angling scenarios. Targets: bass, catfish, sea bass (boat), rockfish (boat), peacock bass, perch, zander, arowana, giant snakehead, barramundi * The photograph is a prototype.</v>
       </c>
       <c r="AH171" t="str">
-        <v>Other.1: カーボン85%　グラス15％</v>
+        <v>カーボン85%　グラス15％</v>
       </c>
       <c r="AI171" t="str">
         <v/>
@@ -19369,7 +19369,7 @@
         <v>The flagship model of World Expedition spinning, equipped with an extension shaft allowing for a length change between 8’8” and 9’6”. From wading games to surf games to shore jigging, this new rod handles it all with ease. The VKS-88-96MH-5.5 has the overwhelming super long distance castability to deliver lures to areas that were impossible to reach under headwinds and crosswinds with bait models. This special function rod has a focus on flight distance and excels at targeting large fish in wide open areas. It’s perfectly suited for experts who can perform delicate adjustments based on drag. It’s perfect for high level power games against seabass and large blue fish, and it performs well against Japanese huchen and Japanese lates as well. Overseas, king salmon and taimen are along the target fish that this rod can catch with certainty. The amazing power from this multi-piece spinning rod allows it to handle 70g class lures such as the BIG SLAP and MEGADOG180 with ease. Adjusting the length of the rod at your destination will allow you to adapt to a wider range of fields and situations. Targets: sea bass, large blue fish, flatfish, large rockfish, Japanese lates, Japanese huchen, king salmon, taimen * The photograph is a prototype.</v>
       </c>
       <c r="AH172" t="str">
-        <v>Other.1: カーボン75%　グラス25％</v>
+        <v>カーボン75%　グラス25％</v>
       </c>
       <c r="AI172" t="str">
         <v/>
@@ -19476,7 +19476,7 @@
         <v>This high rigidity long shaft model bumps up the power specs of the 610ML-4 to a new level. It has the power performance to control fast moving lures at will, along with the versatility to handle most shore-based saltwater lures such as metal type lures up to 40g. The exceptional long distance castability solidifies the 610ML-4 as an all-rounder spinning rod perfect for all types of harbor plugging. This exciting spinning model is well suited for reef fishing, boat fishing (seabass, Japanese Spanish mackerel, Japanese amberjack), river fishing for cherry salmon and large rainbow trout, or long distance plugging for Japanese huchen and bass. Targets: trout, sea bass, Japanese Spanish mackerel, small blue fish, large bigeye trevally, blackhead seabream, pike, zander, golden mandarin fish, striper, peacock, arowana, mahseer * The photograph is a prototype.</v>
       </c>
       <c r="AH173" t="str">
-        <v>Other.1: カーボン85%　グラス15％</v>
+        <v>カーボン85%　グラス15％</v>
       </c>
       <c r="AI173" t="str">
         <v/>
@@ -19583,7 +19583,7 @@
         <v>The VKC-61XH-3 is designed to handle magnum size lures in the 100g class. The compact 6ft 1in shaft provides excellent accuracy and precise rod work. The VKC-61XH-3 is ideal for fishing in close quarters in and around structure or boat casting from a low deck. The strong yet flexible blanks capture the powerful rush of monster fish and confidently absorb violent head shakes to thoroughly dominate the fight. This is a mobile monster hunting weapon that combines high maneuverability and overwhelming power to conquer the monsters of the world.</v>
       </c>
       <c r="AH174" t="str">
-        <v>Other.1: カーボン60％　グラス40％</v>
+        <v>カーボン60％　グラス40％</v>
       </c>
       <c r="AI174" t="str">
         <v/>
@@ -19690,7 +19690,7 @@
         <v>There is no better rod with which to target fish under 3kg using small to medium plugs under 20g. The new Nano Matrix Composite Shaft construction makes hookups easy and reduces lost bites. The blank doesn’t have the dullness of past glass composite rods, and rather features a sharp feel with excellent castability and accuracy. It’s easy to make pinpoint casts along bushes and under overhangs. This rod is not only well suited for bass fishing, but also performs light-plugging in harbor areas, boat-based sea bass fishing, reefs, and river trout games all at a high level. Targets: bass, trout, sea bass, small blue fish, blackhead seabream, perch, zander, golden mandarin fish, arowana * The photograph is a prototype.</v>
       </c>
       <c r="AH175" t="str">
-        <v>Other.1: カーボン85%　グラス15％</v>
+        <v>カーボン85%　グラス15％</v>
       </c>
       <c r="AI175" t="str">
         <v/>

--- a/GearSage-client/pkgGear/data_raw/megabass_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/megabass_rod_import.xlsx
@@ -458,7 +458,7 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>images/megabass_rods/ASL7117X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/ASL7117X_main.jpg</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -493,7 +493,7 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>images/megabass_rods/TS79X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/TS79X_main.jpg</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -528,7 +528,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>images/megabass_rods/F7-72XTZ_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/F7-72XTZ_main.jpg</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -563,7 +563,7 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>images/megabass_rods/F1-60XP_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/F1-60XP_main.jpg</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -598,7 +598,7 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>images/megabass_rods/ASL6401XS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/ASL6401XS_main.jpg</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -633,7 +633,7 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>images/megabass_rods/F0.1_2st-62XTS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/F0.1_2st-62XTS_main.jpg</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -668,7 +668,7 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>images/megabass_rods/F5.1_2-68ti_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/F5.1_2-68ti_main.jpg</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>images/megabass_rods/GH93-2MS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/GH93-2MS_main.jpg</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -738,7 +738,7 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>images/megabass_rods/GHBF511-4L_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/GHBF511-4L_main.jpg</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>images/megabass_rods/F4.1_2-71X_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/F4.1_2-71X_main.jpg</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -808,7 +808,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>images/megabass_rods/F9-711LV_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/F9-711LV_main.jpg</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -843,7 +843,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>images/megabass_rods/VKC-711XH-4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/VKC-711XH-4_main.jpg</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -878,7 +878,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>images/megabass_rods/GHT610-M_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/GHT610-M_main.jpg</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>images/megabass_rods/GHBF42-4UL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/GHBF42-4UL_main.jpg</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -948,7 +948,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>images/megabass_rods/GH62-4ML-XG_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/megabass_rods/GH62-4ML-XG_main.jpg</v>
       </c>
       <c r="I16" t="str">
         <v/>
